--- a/deploy/菲律宾部署方案-v2.3-修订版.xlsx
+++ b/deploy/菲律宾部署方案-v2.3-修订版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16095" activeTab="2"/>
+    <workbookView windowWidth="22020" windowHeight="13785" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="说明与总览" sheetId="1" r:id="rId1"/>
@@ -3518,6 +3518,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3525,12 +3531,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F7FB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4020,7 +4020,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4092,13 +4092,19 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4110,20 +4116,20 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4519,7 +4525,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" spans="1:1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4529,7 +4535,7 @@
       </c>
     </row>
     <row r="4" ht="14.25" spans="1:2">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="42" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="16" t="s">
@@ -4537,7 +4543,7 @@
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:2">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="42" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="16" t="s">
@@ -4545,7 +4551,7 @@
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:2">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="42" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="16" t="s">
@@ -4553,7 +4559,7 @@
       </c>
     </row>
     <row r="7" ht="28.5" spans="1:2">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="42" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="16" t="s">
@@ -4561,7 +4567,7 @@
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:2">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="42" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="16" t="s">
@@ -4569,7 +4575,7 @@
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:2">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="42" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="16" t="s">
@@ -4577,7 +4583,7 @@
       </c>
     </row>
     <row r="10" ht="28.5" spans="1:2">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="42" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="16" t="s">
@@ -4585,7 +4591,7 @@
       </c>
     </row>
     <row r="11" ht="28.5" spans="1:2">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="42" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="16" t="s">
@@ -4593,7 +4599,7 @@
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:2">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="42" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="16" t="s">
@@ -4601,7 +4607,7 @@
       </c>
     </row>
     <row r="13" ht="28.5" spans="1:2">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="42" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="16" t="s">
@@ -4609,7 +4615,7 @@
       </c>
     </row>
     <row r="14" ht="28.5" spans="1:2">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="42" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="16" t="s">
@@ -4617,7 +4623,7 @@
       </c>
     </row>
     <row r="15" ht="71.25" spans="1:2">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="42" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="16" t="s">
@@ -4625,7 +4631,7 @@
       </c>
     </row>
     <row r="16" ht="28.5" spans="1:2">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="42" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="16" t="s">
@@ -4633,7 +4639,7 @@
       </c>
     </row>
     <row r="17" ht="14.25" spans="1:2">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="42" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="16" t="s">
@@ -4641,7 +4647,7 @@
       </c>
     </row>
     <row r="18" ht="156.75" spans="1:2">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="42" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="16" t="s">
@@ -4662,23 +4668,23 @@
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:2">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="41">
+      <c r="B21" s="43">
         <v>46293</v>
       </c>
     </row>
     <row r="22" ht="28.5" spans="1:2">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="41">
+      <c r="B22" s="43">
         <v>46288</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="1:2">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="42" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="16" t="s">
@@ -4686,7 +4692,7 @@
       </c>
     </row>
     <row r="24" ht="42.75" spans="1:2">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="42" t="s">
         <v>39</v>
       </c>
       <c r="B24" s="16" t="s">
@@ -4694,23 +4700,23 @@
       </c>
     </row>
     <row r="25" ht="14.25" spans="1:2">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="44" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="26" ht="14.25" spans="1:2">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="44" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="1:2">
-      <c r="A27" s="40" t="s">
+      <c r="A27" s="42" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="16" t="s">
@@ -4718,7 +4724,7 @@
       </c>
     </row>
     <row r="28" ht="14.25" spans="1:2">
-      <c r="A28" s="40" t="s">
+      <c r="A28" s="42" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="16" t="s">
@@ -4726,7 +4732,7 @@
       </c>
     </row>
     <row r="29" ht="14.25" spans="1:2">
-      <c r="A29" s="40" t="s">
+      <c r="A29" s="42" t="s">
         <v>49</v>
       </c>
       <c r="B29" s="16" t="s">
@@ -4734,23 +4740,23 @@
       </c>
     </row>
     <row r="30" ht="42.75" spans="1:2">
-      <c r="A30" s="40" t="s">
+      <c r="A30" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="44" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="1:2">
-      <c r="A31" s="40" t="s">
+      <c r="A31" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="42" t="s">
+      <c r="B31" s="44" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="45" t="s">
         <v>55</v>
       </c>
       <c r="B32" s="9"/>
@@ -4761,7 +4767,7 @@
       </c>
     </row>
     <row r="35" ht="28.5" spans="1:2">
-      <c r="A35" s="40" t="s">
+      <c r="A35" s="42" t="s">
         <v>57</v>
       </c>
       <c r="B35" s="16" t="s">
@@ -4769,7 +4775,7 @@
       </c>
     </row>
     <row r="36" ht="42.75" spans="1:2">
-      <c r="A36" s="40" t="s">
+      <c r="A36" s="42" t="s">
         <v>59</v>
       </c>
       <c r="B36" s="16" t="s">
@@ -4777,7 +4783,7 @@
       </c>
     </row>
     <row r="37" ht="28.5" spans="1:2">
-      <c r="A37" s="40" t="s">
+      <c r="A37" s="42" t="s">
         <v>61</v>
       </c>
       <c r="B37" s="16" t="s">
@@ -4785,7 +4791,7 @@
       </c>
     </row>
     <row r="38" ht="28.5" spans="1:2">
-      <c r="A38" s="40" t="s">
+      <c r="A38" s="42" t="s">
         <v>63</v>
       </c>
       <c r="B38" s="16" t="s">
@@ -4793,7 +4799,7 @@
       </c>
     </row>
     <row r="39" ht="28.5" spans="1:2">
-      <c r="A39" s="40" t="s">
+      <c r="A39" s="42" t="s">
         <v>65</v>
       </c>
       <c r="B39" s="16" t="s">
@@ -4801,7 +4807,7 @@
       </c>
     </row>
     <row r="40" ht="14.25" spans="1:2">
-      <c r="A40" s="40" t="s">
+      <c r="A40" s="42" t="s">
         <v>67</v>
       </c>
       <c r="B40" s="16" t="s">
@@ -4841,707 +4847,707 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="39" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="K3" s="35" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="J4" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="36" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="J5" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="40" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="H6" s="34" t="s">
+      <c r="H6" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="J6" s="34" t="s">
+      <c r="J6" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="K6" s="34" t="s">
+      <c r="K6" s="36" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="36" t="s">
+      <c r="K7" s="38" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="G8" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="34" t="s">
+      <c r="J8" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="K8" s="36" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="H9" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="I9" s="36" t="s">
+      <c r="I9" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J9" s="36" t="s">
+      <c r="J9" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="36" t="s">
+      <c r="K9" s="38" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="10" ht="28.5" customHeight="1" spans="1:11">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="F10" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G10" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="H10" s="34" t="s">
+      <c r="H10" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="I10" s="34" t="s">
+      <c r="I10" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="J10" s="34" t="s">
+      <c r="J10" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="K10" s="34" t="s">
+      <c r="K10" s="36" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="H11" s="36" t="s">
+      <c r="H11" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="I11" s="36" t="s">
+      <c r="I11" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J11" s="36" t="s">
+      <c r="J11" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="K11" s="36" t="s">
+      <c r="K11" s="38" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="34" t="s">
+      <c r="H12" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="I12" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="J12" s="34" t="s">
+      <c r="J12" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="K12" s="34" t="s">
+      <c r="K12" s="36" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="E13" s="36" t="s">
+      <c r="E13" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="36" t="s">
+      <c r="G13" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="36" t="s">
+      <c r="H13" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="I13" s="36" t="s">
+      <c r="I13" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="36" t="s">
+      <c r="J13" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="K13" s="36" t="s">
+      <c r="K13" s="38" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="F14" s="34" t="s">
+      <c r="F14" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="H14" s="34" t="s">
+      <c r="H14" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="I14" s="34" t="s">
+      <c r="I14" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="34" t="s">
+      <c r="J14" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="K14" s="34" t="s">
+      <c r="K14" s="36" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="E15" s="36" t="s">
+      <c r="E15" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="H15" s="36" t="s">
+      <c r="H15" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="I15" s="36" t="s">
+      <c r="I15" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J15" s="36" t="s">
+      <c r="J15" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="K15" s="36" t="s">
+      <c r="K15" s="38" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="E16" s="34" t="s">
+      <c r="E16" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="F16" s="34" t="s">
+      <c r="F16" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="34" t="s">
+      <c r="G16" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="H16" s="34" t="s">
+      <c r="H16" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="34" t="s">
+      <c r="I16" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="J16" s="34" t="s">
+      <c r="J16" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="K16" s="34" t="s">
+      <c r="K16" s="36" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="E17" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="38" t="s">
         <v>151</v>
       </c>
-      <c r="G17" s="36" t="s">
+      <c r="G17" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="36" t="s">
+      <c r="H17" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="I17" s="36" t="s">
+      <c r="I17" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="J17" s="36" t="s">
+      <c r="J17" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="K17" s="36" t="s">
+      <c r="K17" s="38" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D18" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="F18" s="34" t="s">
+      <c r="F18" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="G18" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="34" t="s">
+      <c r="H18" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="I18" s="34" t="s">
+      <c r="I18" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="J18" s="34" t="s">
+      <c r="J18" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="K18" s="34" t="s">
+      <c r="K18" s="36" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="19" ht="28.5" customHeight="1" spans="1:11">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="G19" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="H19" s="36" t="s">
+      <c r="H19" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="I19" s="36" t="s">
+      <c r="I19" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="J19" s="36" t="s">
+      <c r="J19" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="36" t="s">
+      <c r="K19" s="38" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="36" t="s">
         <v>178</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="E20" s="34" t="s">
+      <c r="E20" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="F20" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="G20" s="34" t="s">
+      <c r="G20" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="H20" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I20" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="J20" s="34" t="s">
+      <c r="J20" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="K20" s="34" t="s">
+      <c r="K20" s="36" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="H21" s="36" t="s">
+      <c r="H21" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="I21" s="36" t="s">
+      <c r="I21" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="36" t="s">
+      <c r="K21" s="38" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1" spans="1:11">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="D22" s="34" t="s">
+      <c r="D22" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="E22" s="34" t="s">
+      <c r="E22" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="F22" s="34" t="s">
+      <c r="F22" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="G22" s="34" t="s">
+      <c r="G22" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="I22" s="34" t="s">
+      <c r="I22" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="J22" s="34" t="s">
+      <c r="J22" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="K22" s="34" t="s">
+      <c r="K22" s="36" t="s">
         <v>197</v>
       </c>
     </row>
@@ -5569,7 +5575,7 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="3.625" style="31" customWidth="1"/>
+    <col min="1" max="1" width="3.625" style="33" customWidth="1"/>
     <col min="2" max="2" width="6.625" style="11" customWidth="1"/>
     <col min="3" max="3" width="22.25" style="11" customWidth="1"/>
     <col min="4" max="4" width="24" style="11" customWidth="1"/>
@@ -5585,48 +5591,48 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="35" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="K3" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="L3" s="33" t="s">
+      <c r="L3" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="M3" s="33" t="s">
+      <c r="M3" s="35" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5634,81 +5640,81 @@
       <c r="A4" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="36">
         <v>1</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="36" t="s">
         <v>213</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="36" t="s">
         <v>215</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="J4" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="L4" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="36" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="38">
         <v>2</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="38" t="s">
         <v>223</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="J5" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="K5" s="36" t="s">
+      <c r="K5" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="L5" s="36" t="s">
+      <c r="L5" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="M5" s="36" t="s">
+      <c r="M5" s="38" t="s">
         <v>225</v>
       </c>
     </row>
@@ -5716,81 +5722,81 @@
       <c r="A6" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="36" t="s">
         <v>226</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="36">
         <v>4</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="36" t="s">
         <v>228</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="H6" s="34" t="s">
+      <c r="H6" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="J6" s="34" t="s">
+      <c r="J6" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="K6" s="34" t="s">
+      <c r="K6" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="L6" s="34" t="s">
+      <c r="L6" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="M6" s="34" t="s">
+      <c r="M6" s="36" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="38">
         <v>1</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="38" t="s">
         <v>234</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="K7" s="36" t="s">
+      <c r="K7" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="L7" s="36" t="s">
+      <c r="L7" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="M7" s="36" t="s">
+      <c r="M7" s="38" t="s">
         <v>236</v>
       </c>
     </row>
@@ -5798,81 +5804,81 @@
       <c r="A8" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="36" t="s">
         <v>238</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="36">
         <v>4</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="G8" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="J8" s="34" t="s">
+      <c r="J8" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="K8" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="L8" s="34" t="s">
+      <c r="L8" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="M8" s="36" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="9" ht="28.5" customHeight="1" spans="1:13">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="38" t="s">
         <v>244</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="38">
         <v>1</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="H9" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="I9" s="36" t="s">
+      <c r="I9" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="J9" s="36" t="s">
+      <c r="J9" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="K9" s="36" t="s">
+      <c r="K9" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="L9" s="36" t="s">
+      <c r="L9" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="M9" s="36" t="s">
+      <c r="M9" s="38" t="s">
         <v>249</v>
       </c>
     </row>
@@ -5880,81 +5886,81 @@
       <c r="A10" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="36" t="s">
         <v>250</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="36" t="s">
         <v>251</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="36">
         <v>1</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="F10" s="36" t="s">
         <v>252</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G10" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="H10" s="34" t="s">
+      <c r="H10" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="I10" s="34" t="s">
+      <c r="I10" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="J10" s="34" t="s">
+      <c r="J10" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="K10" s="34" t="s">
+      <c r="K10" s="36" t="s">
         <v>255</v>
       </c>
-      <c r="L10" s="34" t="s">
+      <c r="L10" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="M10" s="34" t="s">
+      <c r="M10" s="36" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="38">
         <v>1</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="H11" s="36" t="s">
+      <c r="H11" s="38" t="s">
         <v>260</v>
       </c>
-      <c r="I11" s="36" t="s">
+      <c r="I11" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="J11" s="36" t="s">
+      <c r="J11" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="K11" s="36" t="s">
+      <c r="K11" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="L11" s="36" t="s">
+      <c r="L11" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="M11" s="36" t="s">
+      <c r="M11" s="38" t="s">
         <v>262</v>
       </c>
     </row>
@@ -5962,81 +5968,81 @@
       <c r="A12" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="36" t="s">
         <v>263</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="36">
         <v>1</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="36" t="s">
         <v>264</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="H12" s="34" t="s">
+      <c r="H12" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="I12" s="36" t="s">
         <v>266</v>
       </c>
-      <c r="J12" s="34" t="s">
+      <c r="J12" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="K12" s="34" t="s">
+      <c r="K12" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="L12" s="34" t="s">
+      <c r="L12" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="M12" s="34" t="s">
+      <c r="M12" s="36" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="38" t="s">
         <v>269</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="38">
         <v>1</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="G13" s="36" t="s">
+      <c r="G13" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="H13" s="36" t="s">
+      <c r="H13" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="I13" s="36" t="s">
+      <c r="I13" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="J13" s="36" t="s">
+      <c r="J13" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="K13" s="36" t="s">
+      <c r="K13" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="L13" s="36" t="s">
+      <c r="L13" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="M13" s="36" t="s">
+      <c r="M13" s="38" t="s">
         <v>274</v>
       </c>
     </row>
@@ -6044,81 +6050,81 @@
       <c r="A14" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="36" t="s">
         <v>275</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="36">
         <v>1</v>
       </c>
-      <c r="F14" s="34" t="s">
+      <c r="F14" s="36" t="s">
         <v>278</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="H14" s="34" t="s">
+      <c r="H14" s="36" t="s">
         <v>279</v>
       </c>
-      <c r="I14" s="34" t="s">
+      <c r="I14" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="J14" s="34" t="s">
+      <c r="J14" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="K14" s="34" t="s">
+      <c r="K14" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="L14" s="34" t="s">
+      <c r="L14" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="M14" s="34" t="s">
+      <c r="M14" s="36" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="15" ht="42.75" customHeight="1" spans="1:13">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="38" t="s">
         <v>275</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="E15" s="36" t="s">
+      <c r="E15" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="H15" s="36" t="s">
+      <c r="H15" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="I15" s="36" t="s">
+      <c r="I15" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="J15" s="36" t="s">
+      <c r="J15" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="K15" s="36" t="s">
+      <c r="K15" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="L15" s="36" t="s">
+      <c r="L15" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="M15" s="36" t="s">
+      <c r="M15" s="38" t="s">
         <v>287</v>
       </c>
     </row>
@@ -6126,81 +6132,81 @@
       <c r="A16" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="36" t="s">
         <v>275</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="36" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="36">
         <v>1</v>
       </c>
-      <c r="F16" s="34" t="s">
+      <c r="F16" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="G16" s="34" t="s">
+      <c r="G16" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="H16" s="34" t="s">
+      <c r="H16" s="36" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="34" t="s">
+      <c r="I16" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="J16" s="34" t="s">
+      <c r="J16" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="K16" s="34" t="s">
+      <c r="K16" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="L16" s="34" t="s">
+      <c r="L16" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="M16" s="34" t="s">
+      <c r="M16" s="36" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="38" t="s">
         <v>295</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="38" t="s">
         <v>296</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="38" t="s">
         <v>297</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="38">
         <v>1</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="G17" s="36" t="s">
+      <c r="G17" s="38" t="s">
         <v>299</v>
       </c>
-      <c r="H17" s="36" t="s">
+      <c r="H17" s="38" t="s">
         <v>300</v>
       </c>
-      <c r="I17" s="36" t="s">
+      <c r="I17" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="J17" s="36" t="s">
+      <c r="J17" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="K17" s="36" t="s">
+      <c r="K17" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="L17" s="36" t="s">
+      <c r="L17" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="M17" s="36" t="s">
+      <c r="M17" s="38" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6208,81 +6214,81 @@
       <c r="A18" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="36" t="s">
         <v>303</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D18" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="36">
         <v>2</v>
       </c>
-      <c r="F18" s="34" t="s">
+      <c r="F18" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="G18" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="H18" s="34" t="s">
+      <c r="H18" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="I18" s="34" t="s">
+      <c r="I18" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="34" t="s">
+      <c r="J18" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="K18" s="34" t="s">
+      <c r="K18" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="L18" s="34" t="s">
+      <c r="L18" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="M18" s="34" t="s">
+      <c r="M18" s="36" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="38" t="s">
         <v>295</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="38" t="s">
         <v>307</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="38" t="s">
         <v>308</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="38">
         <v>1</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="38" t="s">
         <v>309</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="G19" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="H19" s="36" t="s">
+      <c r="H19" s="38" t="s">
         <v>310</v>
       </c>
-      <c r="I19" s="36" t="s">
+      <c r="I19" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="J19" s="36" t="s">
+      <c r="J19" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="K19" s="36" t="s">
+      <c r="K19" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="L19" s="36" t="s">
+      <c r="L19" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="M19" s="36" t="s">
+      <c r="M19" s="38" t="s">
         <v>311</v>
       </c>
     </row>
@@ -6290,81 +6296,81 @@
       <c r="A20" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="36" t="s">
         <v>312</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="36" t="s">
         <v>313</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="36">
         <v>1</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="F20" s="36" t="s">
         <v>315</v>
       </c>
-      <c r="G20" s="34" t="s">
+      <c r="G20" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="H20" s="36" t="s">
         <v>316</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I20" s="36" t="s">
         <v>317</v>
       </c>
-      <c r="J20" s="34" t="s">
+      <c r="J20" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="K20" s="34" t="s">
+      <c r="K20" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="L20" s="34" t="s">
+      <c r="L20" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="M20" s="34" t="s">
+      <c r="M20" s="36" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="38">
         <v>1</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="H21" s="36" t="s">
+      <c r="H21" s="38" t="s">
         <v>323</v>
       </c>
-      <c r="I21" s="36" t="s">
+      <c r="I21" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="K21" s="36" t="s">
+      <c r="K21" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="L21" s="36" t="s">
+      <c r="L21" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="M21" s="36" t="s">
+      <c r="M21" s="38" t="s">
         <v>324</v>
       </c>
     </row>
@@ -6372,81 +6378,81 @@
       <c r="A22" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="D22" s="34" t="s">
+      <c r="D22" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="36">
         <v>1</v>
       </c>
-      <c r="F22" s="34" t="s">
+      <c r="F22" s="36" t="s">
         <v>328</v>
       </c>
-      <c r="G22" s="34" t="s">
+      <c r="G22" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="36" t="s">
         <v>329</v>
       </c>
-      <c r="I22" s="34" t="s">
+      <c r="I22" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="J22" s="34" t="s">
+      <c r="J22" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="K22" s="34" t="s">
+      <c r="K22" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="L22" s="34" t="s">
+      <c r="L22" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="M22" s="34" t="s">
+      <c r="M22" s="36" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A23" s="35" t="s">
+      <c r="A23" s="37" t="s">
         <v>331</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="38" t="s">
         <v>332</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="38" t="s">
         <v>333</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="38" t="s">
         <v>334</v>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="38">
         <v>1</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="38" t="s">
         <v>335</v>
       </c>
-      <c r="G23" s="36" t="s">
+      <c r="G23" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="H23" s="36" t="s">
+      <c r="H23" s="38" t="s">
         <v>336</v>
       </c>
-      <c r="I23" s="36" t="s">
+      <c r="I23" s="38" t="s">
         <v>337</v>
       </c>
-      <c r="J23" s="36" t="s">
+      <c r="J23" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="K23" s="36" t="s">
+      <c r="K23" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="L23" s="36" t="s">
+      <c r="L23" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="M23" s="36" t="s">
+      <c r="M23" s="38" t="s">
         <v>338</v>
       </c>
     </row>
@@ -6454,81 +6460,81 @@
       <c r="A24" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="36" t="s">
         <v>332</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="D24" s="34" t="s">
+      <c r="D24" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="34" t="s">
+      <c r="E24" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="34" t="s">
+      <c r="F24" s="36" t="s">
         <v>341</v>
       </c>
-      <c r="G24" s="34" t="s">
+      <c r="G24" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="H24" s="34" t="s">
+      <c r="H24" s="36" t="s">
         <v>342</v>
       </c>
-      <c r="I24" s="34" t="s">
+      <c r="I24" s="36" t="s">
         <v>343</v>
       </c>
-      <c r="J24" s="34" t="s">
+      <c r="J24" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="K24" s="34" t="s">
+      <c r="K24" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="L24" s="34" t="s">
+      <c r="L24" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="M24" s="34" t="s">
+      <c r="M24" s="36" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="37" t="s">
         <v>345</v>
       </c>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="38" t="s">
         <v>347</v>
       </c>
-      <c r="D25" s="36" t="s">
+      <c r="D25" s="38" t="s">
         <v>348</v>
       </c>
-      <c r="E25" s="36">
+      <c r="E25" s="38">
         <v>1</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="38" t="s">
         <v>349</v>
       </c>
-      <c r="G25" s="36" t="s">
+      <c r="G25" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="H25" s="36" t="s">
+      <c r="H25" s="38" t="s">
         <v>350</v>
       </c>
-      <c r="I25" s="36" t="s">
+      <c r="I25" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="J25" s="36" t="s">
+      <c r="J25" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="L25" s="36" t="s">
+      <c r="L25" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="M25" s="36" t="s">
+      <c r="M25" s="38" t="s">
         <v>351</v>
       </c>
     </row>
@@ -6536,81 +6542,81 @@
       <c r="A26" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" s="36" t="s">
         <v>353</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="36" t="s">
         <v>348</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="36">
         <v>1</v>
       </c>
-      <c r="F26" s="34" t="s">
+      <c r="F26" s="36" t="s">
         <v>354</v>
       </c>
-      <c r="G26" s="34" t="s">
+      <c r="G26" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="H26" s="34" t="s">
+      <c r="H26" s="36" t="s">
         <v>355</v>
       </c>
-      <c r="I26" s="34" t="s">
+      <c r="I26" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="J26" s="34" t="s">
+      <c r="J26" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="K26" s="34" t="s">
+      <c r="K26" s="36" t="s">
         <v>255</v>
       </c>
-      <c r="L26" s="34" t="s">
+      <c r="L26" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="M26" s="34" t="s">
+      <c r="M26" s="36" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="27" ht="28.5" customHeight="1" spans="1:13">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="37" t="s">
         <v>357</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D27" s="36" t="s">
+      <c r="D27" s="38" t="s">
         <v>348</v>
       </c>
-      <c r="E27" s="36">
+      <c r="E27" s="38">
         <v>1</v>
       </c>
-      <c r="F27" s="36" t="s">
+      <c r="F27" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="36" t="s">
+      <c r="G27" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="H27" s="36" t="s">
+      <c r="H27" s="38" t="s">
         <v>360</v>
       </c>
-      <c r="I27" s="36" t="s">
+      <c r="I27" s="38" t="s">
         <v>361</v>
       </c>
-      <c r="J27" s="36" t="s">
+      <c r="J27" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="K27" s="36" t="s">
+      <c r="K27" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="L27" s="36" t="s">
+      <c r="L27" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="M27" s="36" t="s">
+      <c r="M27" s="38" t="s">
         <v>362</v>
       </c>
     </row>
@@ -6618,81 +6624,81 @@
       <c r="A28" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="36" t="s">
         <v>364</v>
       </c>
-      <c r="D28" s="34" t="s">
+      <c r="D28" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="36">
         <v>1</v>
       </c>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="G28" s="34" t="s">
+      <c r="G28" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="36" t="s">
         <v>366</v>
       </c>
-      <c r="I28" s="34" t="s">
+      <c r="I28" s="36" t="s">
         <v>367</v>
       </c>
-      <c r="J28" s="34" t="s">
+      <c r="J28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="L28" s="34" t="s">
+      <c r="L28" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="36" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="29" ht="28.5" customHeight="1" spans="1:13">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="37" t="s">
         <v>369</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="38" t="s">
         <v>370</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="38" t="s">
         <v>371</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="36">
+      <c r="E29" s="38">
         <v>1</v>
       </c>
-      <c r="F29" s="36" t="s">
+      <c r="F29" s="38" t="s">
         <v>372</v>
       </c>
-      <c r="G29" s="36" t="s">
+      <c r="G29" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="H29" s="36" t="s">
+      <c r="H29" s="38" t="s">
         <v>373</v>
       </c>
-      <c r="I29" s="36" t="s">
+      <c r="I29" s="38" t="s">
         <v>374</v>
       </c>
-      <c r="J29" s="36" t="s">
+      <c r="J29" s="38" t="s">
         <v>375</v>
       </c>
-      <c r="K29" s="36" t="s">
+      <c r="K29" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="L29" s="36" t="s">
+      <c r="L29" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="M29" s="36" t="s">
+      <c r="M29" s="38" t="s">
         <v>376</v>
       </c>
     </row>
@@ -6700,81 +6706,81 @@
       <c r="A30" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="36" t="s">
         <v>370</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" s="36" t="s">
         <v>378</v>
       </c>
-      <c r="D30" s="34" t="s">
+      <c r="D30" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="36">
         <v>1</v>
       </c>
-      <c r="F30" s="34" t="s">
+      <c r="F30" s="36" t="s">
         <v>379</v>
       </c>
-      <c r="G30" s="34" t="s">
+      <c r="G30" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="H30" s="34" t="s">
+      <c r="H30" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="I30" s="34" t="s">
+      <c r="I30" s="36" t="s">
         <v>369</v>
       </c>
-      <c r="J30" s="34" t="s">
+      <c r="J30" s="36" t="s">
         <v>375</v>
       </c>
-      <c r="K30" s="34" t="s">
+      <c r="K30" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="L30" s="34" t="s">
+      <c r="L30" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="M30" s="34" t="s">
+      <c r="M30" s="36" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:13">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="37" t="s">
         <v>382</v>
       </c>
-      <c r="B31" s="36" t="s">
+      <c r="B31" s="38" t="s">
         <v>370</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="38" t="s">
         <v>383</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="38">
         <v>1</v>
       </c>
-      <c r="F31" s="36" t="s">
+      <c r="F31" s="38" t="s">
         <v>384</v>
       </c>
-      <c r="G31" s="36" t="s">
+      <c r="G31" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="H31" s="36" t="s">
+      <c r="H31" s="38" t="s">
         <v>385</v>
       </c>
-      <c r="I31" s="36" t="s">
+      <c r="I31" s="38" t="s">
         <v>369</v>
       </c>
-      <c r="J31" s="36" t="s">
+      <c r="J31" s="38" t="s">
         <v>375</v>
       </c>
-      <c r="K31" s="36" t="s">
+      <c r="K31" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="L31" s="36" t="s">
+      <c r="L31" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="M31" s="36" t="s">
+      <c r="M31" s="38" t="s">
         <v>386</v>
       </c>
     </row>
@@ -6782,40 +6788,40 @@
       <c r="A32" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="36" t="s">
         <v>370</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" s="36" t="s">
         <v>388</v>
       </c>
-      <c r="D32" s="34" t="s">
+      <c r="D32" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="34">
+      <c r="E32" s="36">
         <v>1</v>
       </c>
-      <c r="F32" s="34" t="s">
+      <c r="F32" s="36" t="s">
         <v>389</v>
       </c>
-      <c r="G32" s="34" t="s">
+      <c r="G32" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="H32" s="34" t="s">
+      <c r="H32" s="36" t="s">
         <v>390</v>
       </c>
-      <c r="I32" s="34" t="s">
+      <c r="I32" s="36" t="s">
         <v>391</v>
       </c>
-      <c r="J32" s="34" t="s">
+      <c r="J32" s="36" t="s">
         <v>375</v>
       </c>
-      <c r="K32" s="34" t="s">
+      <c r="K32" s="36" t="s">
         <v>248</v>
       </c>
-      <c r="L32" s="34" t="s">
+      <c r="L32" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="M32" s="34" t="s">
+      <c r="M32" s="36" t="s">
         <v>392</v>
       </c>
     </row>
@@ -7264,48 +7270,48 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" spans="1:1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:13">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="J3" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="K3" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="L3" s="28" t="s">
+      <c r="L3" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="M3" s="28" t="s">
+      <c r="M3" s="30" t="s">
         <v>80</v>
       </c>
     </row>
@@ -7351,43 +7357,43 @@
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:13">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="31" t="s">
         <v>450</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="31">
         <v>4</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="31" t="s">
         <v>452</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="31" t="s">
         <v>453</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="K5" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="L5" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="M5" s="29" t="s">
+      <c r="M5" s="31" t="s">
         <v>454</v>
       </c>
     </row>
@@ -7433,43 +7439,43 @@
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:13">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="31">
         <v>1</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="31" t="s">
         <v>460</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="31" t="s">
         <v>461</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="31" t="s">
         <v>462</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="31" t="s">
         <v>463</v>
       </c>
     </row>
@@ -7515,43 +7521,43 @@
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:13">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="31" t="s">
         <v>468</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="31">
         <v>1</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="31" t="s">
         <v>469</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="31" t="s">
         <v>447</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="31" t="s">
         <v>470</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="31" t="s">
         <v>292</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="L9" s="29" t="s">
+      <c r="L9" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M9" s="29" t="s">
+      <c r="M9" s="31" t="s">
         <v>471</v>
       </c>
     </row>
@@ -7597,43 +7603,43 @@
       </c>
     </row>
     <row r="11" ht="42.75" spans="1:13">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="31" t="s">
         <v>475</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="31" t="s">
         <v>476</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="H11" s="31" t="s">
         <v>477</v>
       </c>
-      <c r="I11" s="29" t="s">
+      <c r="I11" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="J11" s="29" t="s">
+      <c r="J11" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="K11" s="29" t="s">
+      <c r="K11" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="L11" s="29" t="s">
+      <c r="L11" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="M11" s="29" t="s">
+      <c r="M11" s="31" t="s">
         <v>478</v>
       </c>
     </row>
@@ -7679,43 +7685,43 @@
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:13">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="31" t="s">
         <v>483</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="31">
         <v>1</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="31" t="s">
         <v>484</v>
       </c>
-      <c r="H13" s="29" t="s">
+      <c r="H13" s="31" t="s">
         <v>485</v>
       </c>
-      <c r="I13" s="29" t="s">
+      <c r="I13" s="31" t="s">
         <v>486</v>
       </c>
-      <c r="J13" s="29" t="s">
+      <c r="J13" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="K13" s="29" t="s">
+      <c r="K13" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="L13" s="29" t="s">
+      <c r="L13" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M13" s="29" t="s">
+      <c r="M13" s="31" t="s">
         <v>487</v>
       </c>
     </row>
@@ -7761,43 +7767,43 @@
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:13">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="31" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="31">
         <v>1</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="31" t="s">
         <v>491</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="31" t="s">
         <v>465</v>
       </c>
-      <c r="H15" s="29" t="s">
+      <c r="H15" s="31" t="s">
         <v>492</v>
       </c>
-      <c r="I15" s="29" t="s">
+      <c r="I15" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="29" t="s">
+      <c r="J15" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="K15" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="L15" s="29" t="s">
+      <c r="L15" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M15" s="29" t="s">
+      <c r="M15" s="31" t="s">
         <v>493</v>
       </c>
     </row>
@@ -7843,43 +7849,43 @@
       </c>
     </row>
     <row r="17" ht="14.25" spans="1:13">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="31" t="s">
         <v>497</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="G17" s="29" t="s">
+      <c r="G17" s="31" t="s">
         <v>465</v>
       </c>
-      <c r="H17" s="29" t="s">
+      <c r="H17" s="31" t="s">
         <v>499</v>
       </c>
-      <c r="I17" s="29" t="s">
+      <c r="I17" s="31" t="s">
         <v>500</v>
       </c>
-      <c r="J17" s="29" t="s">
+      <c r="J17" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="K17" s="29" t="s">
+      <c r="K17" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="L17" s="29" t="s">
+      <c r="L17" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="M17" s="29" t="s">
+      <c r="M17" s="31" t="s">
         <v>501</v>
       </c>
     </row>
@@ -7925,43 +7931,43 @@
       </c>
     </row>
     <row r="19" ht="14.25" spans="1:13">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="31" t="s">
         <v>370</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="31" t="s">
         <v>507</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="31">
         <v>1</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="31" t="s">
         <v>508</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="31" t="s">
         <v>465</v>
       </c>
-      <c r="H19" s="29" t="s">
+      <c r="H19" s="31" t="s">
         <v>509</v>
       </c>
-      <c r="I19" s="29" t="s">
+      <c r="I19" s="31" t="s">
         <v>510</v>
       </c>
-      <c r="J19" s="29" t="s">
+      <c r="J19" s="31" t="s">
         <v>375</v>
       </c>
-      <c r="K19" s="29" t="s">
+      <c r="K19" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="L19" s="29" t="s">
+      <c r="L19" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M19" s="29" t="s">
+      <c r="M19" s="31" t="s">
         <v>511</v>
       </c>
     </row>
@@ -8007,43 +8013,43 @@
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:13">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="31" t="s">
         <v>346</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="31" t="s">
         <v>516</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="31">
         <v>1</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G21" s="31" t="s">
         <v>517</v>
       </c>
-      <c r="H21" s="29" t="s">
+      <c r="H21" s="31" t="s">
         <v>518</v>
       </c>
-      <c r="I21" s="29" t="s">
+      <c r="I21" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="J21" s="29" t="s">
+      <c r="J21" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="K21" s="29" t="s">
+      <c r="K21" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="L21" s="29" t="s">
+      <c r="L21" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M21" s="29" t="s">
+      <c r="M21" s="31" t="s">
         <v>519</v>
       </c>
     </row>
@@ -8145,7 +8151,7 @@
       <c r="M24" s="5"/>
     </row>
     <row r="25" ht="66" customHeight="1" spans="1:13">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="32" t="s">
         <v>528</v>
       </c>
       <c r="B25" s="8"/>
@@ -8177,7 +8183,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.5" style="11" customWidth="1"/>
@@ -8453,234 +8459,294 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:1">
-      <c r="A16" s="18" t="s">
+    <row r="16" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ap-southeast-5</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VPC CIDR</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpc-jkt-dev 10.2.0.0/16</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dev/test 独立站点网络（环境隔离修订 方案 A）</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与马尼拉 10.0.0.0/16、新加坡 10.1.0.0/16 不重叠；2026-09-30 已建成（vpc-k1ano67avx98nr3n1bg5d，Available）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可用区 5a</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vSwitch</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vsw-jkt-dev-app-5a 10.2.0.0/20</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACK 节点子网</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已建成（vsw-k1aaxl1aqbc42ac7yb7ms）；Terway ENIIP 下 Pod IP 直接取自 VPC，本段必须整段进 dev RDS 白名单</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可用区 5b</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vSwitch</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vsw-jkt-dev-app-5b 10.2.16.0/20</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACK 节点子网</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已建成（vsw-k1a1ogs29dvgvqethz27g）；节点池跨 2 个可用区（新加坡坑 A：AzBalance）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可用区 5c</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vSwitch</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vsw-jkt-dev-app-5c 10.2.32.0/20</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACK Pod 子网</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已建成（vsw-k1aj6eby0v5lpwrswov45）；三段 CIDR 是 dev RDS 白名单的唯一来源，禁止追加 10.0 / 10.1 段</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:1">
+      <c r="A20" s="18" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A17" s="19" t="s">
+    <row r="21" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A21" s="19" t="s">
         <v>530</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B21" s="19" t="s">
         <v>562</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C21" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D21" s="19" t="s">
         <v>563</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E21" s="19" t="s">
         <v>564</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F21" s="19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="18" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A18" s="17" t="s">
+    <row r="22" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A22" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B22" s="17" t="s">
         <v>565</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C22" s="17">
         <v>4</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D22" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E22" s="16" t="s">
         <v>566</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F22" s="16" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A19" s="17" t="s">
+    <row r="23" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A23" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B23" s="17" t="s">
         <v>568</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C23" s="17">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D23" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E23" s="16" t="s">
         <v>569</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F23" s="16" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A20" s="17" t="s">
+    <row r="24" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A24" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B24" s="17" t="s">
         <v>570</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C24" s="17">
         <v>4</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D24" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E24" s="16" t="s">
         <v>571</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F24" s="16" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:1">
-      <c r="A22" s="18" t="s">
+    <row r="25" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dev 出网（跨区拉镜像 / 上游 mock）</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1（待核准）</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAT 网关 + EIP</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dev 独立出口，经公网跨区拉马尼拉 ACR EE 镜像（EE 仅在 ap-southeast-6 有实例，且未绑定任何 VPC 内网入口）</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">禁止并入生产 8 个 EIP 的上游 / RDS 白名单池；Phase 2 支出待项目负责人核准（当前可用额度 0.00 USD，暂未创建）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:1">
+      <c r="A27" s="18" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="23" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A23" s="19" t="s">
+    <row r="28" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A28" s="19" t="s">
         <v>530</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B28" s="19" t="s">
         <v>497</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C28" s="19" t="s">
         <v>574</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D28" s="19" t="s">
         <v>575</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E28" s="19" t="s">
         <v>576</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F28" s="19" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="24" ht="42.75" customHeight="1" spans="1:6">
-      <c r="A24" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>577</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>578</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>579</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>580</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A25" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>582</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>578</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>583</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>577</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A26" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>582</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>585</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>586</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="27" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A27" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>582</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>585</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>589</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>590</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="28" ht="42.75" customHeight="1" spans="1:6">
-      <c r="A28" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>587</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>578</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>592</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>593</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="29" ht="28.5" customHeight="1" spans="1:6">
+    <row r="29" ht="42.75" customHeight="1" spans="1:6">
       <c r="A29" s="17" t="s">
         <v>253</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>578</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1" spans="1:6">
@@ -8688,238 +8754,538 @@
         <v>253</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>578</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>597</v>
+        <v>577</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="31" ht="28.5" customHeight="1" spans="1:6">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1" spans="1:6">
       <c r="A31" s="17" t="s">
-        <v>465</v>
+        <v>253</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="C31" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>586</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="32" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A32" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>589</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="33" ht="42.75" customHeight="1" spans="1:6">
+      <c r="A33" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>587</v>
+      </c>
+      <c r="C33" s="17" t="s">
         <v>578</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>579</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>603</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A32" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>605</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>578</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>583</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>602</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="33" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A33" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>605</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>585</v>
       </c>
       <c r="D33" s="17" t="s">
         <v>592</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A34" s="17" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="34" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A34" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>595</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>578</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>596</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>597</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="35" ht="23" customHeight="1" spans="1:6">
+      <c r="A35" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>599</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>578</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>600</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>597</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="36" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A36" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B36" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>579</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>603</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A37" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B37" s="17" t="s">
         <v>605</v>
       </c>
-      <c r="C34" s="17" t="s">
-        <v>585</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>589</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>590</v>
-      </c>
-      <c r="F34" s="16" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" spans="1:1">
-      <c r="A36" s="18" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A37" s="19" t="s">
-        <v>611</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>612</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>613</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>80</v>
+      <c r="C37" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>583</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="38" ht="28.5" customHeight="1" spans="1:6">
       <c r="A38" s="17" t="s">
-        <v>615</v>
+        <v>465</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>333</v>
+        <v>605</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>616</v>
+        <v>585</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" spans="1:6">
       <c r="A39" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>605</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>589</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="40" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sg-jkt-dev-app</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">drop ALL -1/-1（优先级 1）</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.0.0.0/16（马尼拉生产 VPC）</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已生效：拒绝优先于 normal 安全组的默认全放通，dev 节点 / Pod 无法访问生产 VPC 内任意地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sg-jkt-dev-app</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">drop ALL -1/-1（优先级 1）</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.1.0.0/16（新加坡备 VPC）</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已生效：同上，备 region 亦不可达；生产 apiserver 6443 / 10250 顺带被阻断（验收 V11）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sg-jkt-dev-app</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">drop TCP 5432（优先级 1）</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43.118.96.65/32（生产 RDS 公网 IP）</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已生效：堵住 dev 直连生产库公网入口这条最现实的数据外泄路径（验收 V1：nc -zvw3 必须失败）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sg-jkt-dev-app</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accept TCP 443（优先级 10）</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.0.0.0/0，经 dev 自有 NAT 出网</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已生效：跨区拉镜像与上游调用只放行 443，不做全协议放通；目的侧再由生产 ACL 二次收敛</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sg-jkt-dev-app</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accept UDP 53（优先级 10 / 20）</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100.100.2.136/32、100.100.2.138/32，兜底 0.0.0.0/0</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已生效：VPC 内网 DNS 优先，ACR / RDS 等内网 endpoint 解析依赖此项</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雅加达 dev</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sg-jkt-dev-app</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无自定义规则（保持默认）</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入向仅组内互通；生产侧安全组、生产 RDS 白名单、生产 ACR EE 公网 ACL 均未因本次改动（见 jakarta_dev_ledger §3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="1:1">
+      <c r="A47" s="18" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A48" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>614</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A49" s="17" t="s">
+        <v>615</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>616</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>617</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A50" s="17" t="s">
         <v>620</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B50" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C50" s="17" t="s">
         <v>616</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D50" s="17" t="s">
         <v>617</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E50" s="16" t="s">
         <v>621</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F50" s="16" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="40" ht="42.75" customHeight="1" spans="1:6">
-      <c r="A40" s="17" t="s">
+    <row r="51" ht="42.75" customHeight="1" spans="1:6">
+      <c r="A51" s="17" t="s">
         <v>623</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B51" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C51" s="17" t="s">
         <v>624</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D51" s="17" t="s">
         <v>625</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E51" s="16" t="s">
         <v>626</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="F51" s="16" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="41" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A41" s="17" t="s">
+    <row r="52" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A52" s="17" t="s">
         <v>628</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B52" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C52" s="17" t="s">
         <v>630</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D52" s="17" t="s">
         <v>631</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E52" s="16" t="s">
         <v>632</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="F52" s="16" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="42" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A42" s="17" t="s">
+    <row r="53" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A53" s="17" t="s">
         <v>634</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B53" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C53" s="17" t="s">
         <v>635</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D53" s="17" t="s">
         <v>636</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E53" s="16" t="s">
         <v>637</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F53" s="16" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="44" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A44" s="25" t="s">
+    <row r="55" ht="14.25" customHeight="1" spans="1:1">
+      <c r="A55" s="25" t="s">
         <v>639</v>
       </c>
     </row>
+    <row r="56" ht="42.75" customHeight="1" spans="1:6">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明：① 雅加达 dev 网络层（VPC + 3 个 vSwitch + sg-jkt-dev-app 出向规则）已于 2026-09-30 建成并复核，全部资源属 rg-nonprod（rg-aek4hk3prqgqjcy），标签 env=dev / project=new-api / isolation=structural-vpc；② 隔离是结构性的：跨 VPC 不通 + 生产 RDS 公网 5432 出向拒绝 + 无 CEN / 无 VPC 对等连接（实测 DescribeCens=0、ListVpcPeerConnections=0）；namespace 只作组织与 RBAC 边界，不构成网络或数据边界；③ 尚未创建（待支出核准）：dev NAT/EIP、ACK 集群与节点池、dev RDS PG 17.0、Tair、工作负载；RDS 建库参数已用 DryRun 验证通过（SecurityIPList 仅含上述三段 dev CIDR）。实测值与回滚命令见 deploy/jakarta_dev_ledger.md。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A56:F56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/deploy/菲律宾部署方案-v2.3-修订版.xlsx
+++ b/deploy/菲律宾部署方案-v2.3-修订版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22020" windowHeight="13785" activeTab="4"/>
+    <workbookView windowWidth="29700" windowHeight="15660" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="说明与总览" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="1074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="1137">
   <si>
     <t>new-api 菲律宾部署方案 · 部署清单与 5 天冲刺落地计划（2 人全职 + 每日 3 段）</t>
   </si>
@@ -153,13 +153,13 @@
     <t>业务域名（统一口径，需替换为正式域名）</t>
   </si>
   <si>
-    <t>api.likha.com（全表统一；替代原 example-ph.com 示例）</t>
+    <t>www.likha.hk（全表统一；替代原 example-ph.com 示例）</t>
   </si>
   <si>
     <t>运维域名（统一口径）</t>
   </si>
   <si>
-    <t>ops.likha.com</t>
+    <t>ops.likha.hk</t>
   </si>
   <si>
     <t>镜像仓库前缀</t>
@@ -492,7 +492,7 @@
     <t>阿里云国际站 · 域名</t>
   </si>
   <si>
-    <t>注册/确认业务域名与运维域名（统一为 api.likha.com / ops.likha.com）；开启隐私保护与自动续费</t>
+    <t>注册/确认业务域名与运维域名（统一为 www.likha.hk / ops.likha.hk）；开启隐私保护与自动续费</t>
   </si>
   <si>
     <t>若使用既有域名可跳过注册，仅需完成实名与 NS 托管</t>
@@ -567,7 +567,7 @@
     <t>数字证书管理服务</t>
   </si>
   <si>
-    <t>申请 *.likha.com（与「说明与总览」业务域名一致；原示例 *.example-ph.com 不覆盖 api.likha.com，已统一）；要求 TLS 1.2 + 1.3</t>
+    <t>申请 *.likha.hk（与「说明与总览」业务域名一致；原示例 *.example-ph.com 不覆盖 www.likha.hk，已统一）；要求 TLS 1.2 + 1.3</t>
   </si>
   <si>
     <t>签发 1–24h（等待）</t>
@@ -791,7 +791,7 @@
     <t>马尼拉</t>
   </si>
   <si>
-    <t>接入 api.likha.com；CC 阈值对齐 GLOBAL_API_RATE_LIMIT；放行支付回调路径并限定回调源 IP 段</t>
+    <t>接入 www.likha.hk；CC 阈值对齐 GLOBAL_API_RATE_LIMIT；放行支付回调路径并限定回调源 IP 段</t>
   </si>
   <si>
     <t>D4</t>
@@ -1637,6 +1637,9 @@
     <t>VPC CIDR</t>
   </si>
   <si>
+    <t>vpc-newapi-mnl-prod 10.0.0.0/16</t>
+  </si>
+  <si>
     <t>菲律宾主站点网络</t>
   </si>
   <si>
@@ -1685,7 +1688,17 @@
     <t>主备跨可用区</t>
   </si>
   <si>
-    <t>备 region 网络（不含数据库）</t>
+    <t>vpc-newapi-sg-prod 10.1.0.0/16</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>备 region 网络（数据库段已按偏移预留、未挂实例）</t>
+    </r>
   </si>
   <si>
     <t>与马尼拉不重叠</t>
@@ -1697,13 +1710,30 @@
     <t>ALB 与 NAT</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>—；实测 vsw-t4ncxa4gqgamhl0o8e6yq / ap-southeast-1a / 可用 IP 251</t>
+    </r>
+  </si>
+  <si>
     <t>vsw-sg-pub-b 10.1.1.0/24</t>
   </si>
   <si>
     <t>ALB 公共子网（第 2 可用区）</t>
   </si>
   <si>
-    <t>ALB 需跨 2 个可用区，原 v2.0 表缺失本行（已补）</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ALB 需跨 2 个可用区，原 v2.0 表缺失本行（已补）；实测 vsw-t4nhtsfk2z79e1ggvlhdz / ap-southeast-1b / 可用 IP 252</t>
+    </r>
   </si>
   <si>
     <t>vsw-sg-app-a 10.1.16.0/20</t>
@@ -1712,9 +1742,204 @@
     <t>PH 备 Pod</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>—；实测 vsw-t4nbvsnvo4z52sumr9sck / ap-southeast-1a / 可用 IP 4073（已用 19，节点与 Pod 在此段）</t>
+    </r>
+  </si>
+  <si>
     <t>vsw-sg-app-b 10.1.32.0/20</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>跨 2 个可用区；实测 vsw-t4n3dthz1ma6tp7bqor6h / ap-southeast-1b / 可用 IP 4084（已用 8）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>新加坡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可用区 A</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>vSwitch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>vsw-sg-data-a 10.1.48.0/20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>RDS / Tair 私有子网</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2026-09-30 按控制台实测补录（原表缺本行）：vsw-t4nr26kz6gceuz0jm4eqw / ap-southeast-1a / Available，可用 IP 4092 = 段内零实例，属预留段</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可用区 B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>vsw-sg-data-b 10.1.64.0/20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>RDS 备实例候选段</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同上实测补录：vsw-t4n58d6u3iws49o2xovdi / ap-southeast-1b / Available，可用 IP 4092 = 零实例；偏移与马尼拉 vsw-mnl-data-b 同槽</t>
+    </r>
+  </si>
+  <si>
+    <t>雅加达 dev</t>
+  </si>
+  <si>
+    <t>ap-southeast-5</t>
+  </si>
+  <si>
+    <t>vpc-newapi-jkt-dev 10.2.0.0/16</t>
+  </si>
+  <si>
+    <t>dev/test 独立站点网络（环境隔离修订 方案 A）</t>
+  </si>
+  <si>
+    <t>与马尼拉 10.0.0.0/16、新加坡 10.1.0.0/16 不重叠；vpc-k1ano67avx98nr3n1bg5d / Available；命名对齐生产形态 vpc-newapi-&lt;站点&gt;-&lt;环境&gt;</t>
+  </si>
+  <si>
+    <t>可用区 5a</t>
+  </si>
+  <si>
+    <t>vsw-jkt-dev-pub-5a 10.2.0.0/24</t>
+  </si>
+  <si>
+    <t>与马尼拉 vsw-mnl-pub-a、新加坡 vsw-sg-pub-a 同槽（.0/.1）；ALB 需跨 2 个可用区。2026-09-30 偏移对齐重建：vsw-k1at4vt7fg8v4umkh9lg3</t>
+  </si>
+  <si>
+    <t>可用区 5b</t>
+  </si>
+  <si>
+    <t>vsw-jkt-dev-pub-5b 10.2.1.0/24</t>
+  </si>
+  <si>
+    <t>第 2 可用区入口段。偏移对齐重建：vsw-k1aqa1ose29nuq92hcvyt</t>
+  </si>
+  <si>
+    <t>vsw-jkt-dev-app-5a 10.2.16.0/20</t>
+  </si>
+  <si>
+    <t>ACK 节点子网</t>
+  </si>
+  <si>
+    <t>Terway ENIIP 下 Pod IP 直接取自本段，整段必须进 dev RDS 白名单；与马尼拉 vsw-mnl-app-a 同槽。偏移对齐重建：vsw-k1agmhxtf974bmzbjlnkp</t>
+  </si>
+  <si>
+    <t>vsw-jkt-dev-app-5b 10.2.32.0/20</t>
+  </si>
+  <si>
+    <t>节点池跨 2 个可用区（新加坡坑 A：AzBalance）；白名单来源段。偏移对齐重建：vsw-k1aoupd0er378rku728d3</t>
+  </si>
+  <si>
+    <t>可用区 5c</t>
+  </si>
+  <si>
+    <t>vsw-jkt-dev-app-5c 10.2.80.0/20</t>
+  </si>
+  <si>
+    <t>ACK 节点子网（第 3 可用区）</t>
+  </si>
+  <si>
+    <t>第 3 可用区扩展段（雅加达实测 3 个 AZ，生产两站点仅 2 个，故统一追加在尾部）；白名单来源段。偏移对齐重建：vsw-k1an7x32b5qjtsmklelkt</t>
+  </si>
+  <si>
+    <t>vsw-jkt-dev-data-5a 10.2.48.0/20</t>
+  </si>
+  <si>
+    <t>RDS / Tair 私有子网</t>
+  </si>
+  <si>
+    <t>dev RDS PostgreSQL 17.0 主实例与 Tair 绑定此段，数据库不分配公网地址；与马尼拉 vsw-mnl-data-a 同槽，RDS DryRun 已按本段通过。偏移对齐重建：vsw-k1a9u8pkwwkc6z0x6g0kc</t>
+  </si>
+  <si>
+    <t>vsw-jkt-dev-data-5b 10.2.64.0/20</t>
+  </si>
+  <si>
+    <t>多可用区/备实例候选段，主备跨 AZ 时用；与马尼拉 vsw-mnl-data-b 同槽。偏移对齐重建：vsw-k1auat3gn6iagfg7by4sz</t>
+  </si>
+  <si>
     <t>EIP 规划（本次出口直出上游，不启用 GA；白名单 = 下列 8 个 EIP）</t>
   </si>
   <si>
@@ -1751,6 +1976,21 @@
     <t>仅放行该 EIP，禁止 0.0.0.0/0</t>
   </si>
   <si>
+    <t>dev 出网（跨区拉镜像 / 上游 mock）</t>
+  </si>
+  <si>
+    <t>1（待核准）</t>
+  </si>
+  <si>
+    <t>NAT 网关 + EIP</t>
+  </si>
+  <si>
+    <t>dev 独立出口，经公网跨区拉马尼拉 ACR EE 镜像（EE 仅在 ap-southeast-6 有实例，且未绑定任何 VPC 内网入口）</t>
+  </si>
+  <si>
+    <t>禁止并入生产 8 个 EIP 的上游 / RDS 白名单池；Phase 2 支出待项目负责人核准（当前可用额度 0.00 USD，暂未创建）</t>
+  </si>
+  <si>
     <t>安全组规则（最小开放原则；入向禁止 0.0.0.0/0，仅放行 WAF / DCDN 回源段与对端 CIDR）</t>
   </si>
   <si>
@@ -1862,6 +2102,57 @@
     <t>接管期调用上游 AI 供应商</t>
   </si>
   <si>
+    <t>sg-jkt-dev-app</t>
+  </si>
+  <si>
+    <t>drop ALL -1/-1（优先级 1）</t>
+  </si>
+  <si>
+    <t>10.0.0.0/16（马尼拉生产 VPC）</t>
+  </si>
+  <si>
+    <t>已生效：拒绝优先于 normal 安全组的默认全放通，dev 节点 / Pod 无法访问生产 VPC 内任意地址</t>
+  </si>
+  <si>
+    <t>10.1.0.0/16（新加坡备 VPC）</t>
+  </si>
+  <si>
+    <t>已生效：同上，备 region 亦不可达；生产 apiserver 6443 / 10250 顺带被阻断（验收 V11）</t>
+  </si>
+  <si>
+    <t>drop TCP 5432（优先级 1）</t>
+  </si>
+  <si>
+    <t>43.118.96.65/32（生产 RDS 公网 IP）</t>
+  </si>
+  <si>
+    <t>已生效：堵住 dev 直连生产库公网入口这条最现实的数据外泄路径（验收 V1：nc -zvw3 必须失败）</t>
+  </si>
+  <si>
+    <t>accept TCP 443（优先级 10）</t>
+  </si>
+  <si>
+    <t>0.0.0.0/0，经 dev 自有 NAT 出网</t>
+  </si>
+  <si>
+    <t>已生效：跨区拉镜像与上游调用只放行 443，不做全协议放通；目的侧再由生产 ACL 二次收敛</t>
+  </si>
+  <si>
+    <t>accept UDP 53（优先级 10 / 20）</t>
+  </si>
+  <si>
+    <t>100.100.2.136/32、100.100.2.138/32，兜底 0.0.0.0/0</t>
+  </si>
+  <si>
+    <t>已生效：VPC 内网 DNS 优先，ACR / RDS 等内网 endpoint 解析依赖此项</t>
+  </si>
+  <si>
+    <t>无自定义规则（保持默认）</t>
+  </si>
+  <si>
+    <t>入向仅组内互通；生产侧安全组、生产 RDS 白名单、生产 ACR EE 公网 ACL 均未因本次改动（见 jakarta_dev_ledger §3）</t>
+  </si>
+  <si>
     <t>凭据与密钥（KMS 托管，禁止落库落 Git）</t>
   </si>
   <si>
@@ -1952,6 +2243,9 @@
     <t>说明：① 原 v2.0 中 sg-mnl-alb / sg-sg-alb 入向为 0.0.0.0/0，可被直连 ALB 公网 IP 绕过 WAF，本版已收敛为 WAF / DCDN 回源段；② 跨 VPC 对端无法以安全组表达，相关规则改为 CIDR /32，并由 RDS 公网白名单二次收敛；③ 上游出口保留 0.0.0.0/0 出向为必要放通，由目的侧白名单与出向限速约束。</t>
   </si>
   <si>
+    <t>说明：① 雅加达 dev 网络层（VPC + 7 个 vSwitch：pub×2 / app×3 / data×2 + sg-jkt-dev-app 出向规则）已于 2026-09-30 建成并复核，CIDR 偏移已与马尼拉/新加坡逐槽同构（pub=.0/.1、app=16/32、data=48/64，第 3 可用区追加在 10.2.80.0/20），全部资源属 rg-nonprod（rg-aek4hk3prqgqjcy），标签 env=dev / project=new-api / isolation=structural-vpc；② 隔离是结构性的：跨 VPC 不通 + 生产 RDS 公网 5432 出向拒绝 + 无 CEN / 无 VPC 对等连接（实测 DescribeCens=0、ListVpcPeerConnections=0）；namespace 只作组织与 RBAC 边界，不构成网络或数据边界；③ 尚未创建（待支出核准）：dev NAT/EIP、ACK 集群与节点池、dev RDS PG 17.0、Tair、工作负载；RDS 建库参数已用 DryRun 验证通过（SecurityIPList 仅含 app 三段 10.2.16.0/20、10.2.32.0/20、10.2.80.0/20，实例落在 data-5a 10.2.48.0/20；pub / data 段不加入白名单）。实测值与回滚命令见 deploy/jakarta_dev_ledger.md。</t>
+  </si>
+  <si>
     <t>5 天冲刺排期 · 每天 3 个工作段（S1 上午 09:00–13:00 / S2 下午 14:00–18:00 / S3 晚间 19:00–23:00，晚间段为加班段）· 单人每段上限 4 人时</t>
   </si>
   <si>
@@ -2561,7 +2855,7 @@
     <t>G5</t>
   </si>
   <si>
-    <t>SSL 通配符证书申请（*.likha.com，TLS 1.2+1.3）</t>
+    <t>SSL 通配符证书申请（*.likha.hk，TLS 1.2+1.3）</t>
   </si>
   <si>
     <t>1–24h</t>
@@ -4024,7 +4318,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4050,7 +4344,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4110,7 +4404,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7266,7 +7560,7 @@
     <col min="11" max="11" width="5.125" style="1" customWidth="1"/>
     <col min="12" max="12" width="4.625" style="1" customWidth="1"/>
     <col min="13" max="13" width="67.25" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="14" max="26" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" spans="1:1">
@@ -8183,15 +8477,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.5" style="11" customWidth="1"/>
     <col min="2" max="2" width="20" style="11" customWidth="1"/>
     <col min="3" max="3" width="18" style="11" customWidth="1"/>
     <col min="4" max="4" width="34" style="11" customWidth="1"/>
-    <col min="5" max="5" width="46.9" style="11" customWidth="1"/>
-    <col min="6" max="6" width="34" style="11" customWidth="1"/>
+    <col min="5" max="5" width="38.125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="50.125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1">
@@ -8230,13 +8524,13 @@
         <v>534</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>212</v>
+        <v>535</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:6">
@@ -8244,16 +8538,16 @@
         <v>253</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>450</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>86</v>
@@ -8264,16 +8558,16 @@
         <v>253</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>450</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>233</v>
@@ -8284,16 +8578,16 @@
         <v>253</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>450</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>86</v>
@@ -8304,16 +8598,16 @@
         <v>253</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>450</v>
       </c>
       <c r="D8" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>544</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>543</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>86</v>
@@ -8324,19 +8618,19 @@
         <v>253</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>450</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:6">
@@ -8344,19 +8638,19 @@
         <v>253</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>450</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:6">
@@ -8370,13 +8664,13 @@
         <v>534</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>445</v>
+        <v>552</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:6">
@@ -8384,19 +8678,19 @@
         <v>465</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>450</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>86</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:6">
@@ -8404,19 +8698,19 @@
         <v>465</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>450</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:6">
@@ -8424,19 +8718,19 @@
         <v>465</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>450</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>86</v>
+        <v>563</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:6">
@@ -8444,848 +8738,852 @@
         <v>465</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>450</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="16" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雅加达 dev</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ap-southeast-5</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VPC CIDR</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vpc-jkt-dev 10.2.0.0/16</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dev/test 独立站点网络（环境隔离修订 方案 A）</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">与马尼拉 10.0.0.0/16、新加坡 10.1.0.0/16 不重叠；2026-09-30 已建成（vpc-k1ano67avx98nr3n1bg5d，Available）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雅加达 dev</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可用区 5a</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vSwitch</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vsw-jkt-dev-app-5a 10.2.0.0/20</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACK 节点子网</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已建成（vsw-k1aaxl1aqbc42ac7yb7ms）；Terway ENIIP 下 Pod IP 直接取自 VPC，本段必须整段进 dev RDS 白名单</t>
-        </is>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A16" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>567</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>569</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A17" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="18" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雅加达 dev</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可用区 5b</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vSwitch</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vsw-jkt-dev-app-5b 10.2.16.0/20</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACK 节点子网</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已建成（vsw-k1a1ogs29dvgvqethz27g）；节点池跨 2 个可用区（新加坡坑 A：AzBalance）</t>
-        </is>
+      <c r="A18" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>577</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="19" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雅加达 dev</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可用区 5c</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vSwitch</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vsw-jkt-dev-app-5c 10.2.32.0/20</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACK Pod 子网</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已建成（vsw-k1aj6eby0v5lpwrswov45）；三段 CIDR 是 dev RDS 白名单的唯一来源，禁止追加 10.0 / 10.1 段</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:1">
-      <c r="A20" s="18" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A21" s="19" t="s">
-        <v>530</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>562</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>563</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>80</v>
+      <c r="A19" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>581</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="20" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A20" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>584</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="21" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A21" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>581</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>587</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="22" ht="28.5" customHeight="1" spans="1:6">
       <c r="A22" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>584</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>590</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="23" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A23" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>592</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="24" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A24" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>581</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>596</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="25" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A25" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>584</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>599</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:1">
+      <c r="A26" s="18" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A27" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A28" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>565</v>
-      </c>
-      <c r="C22" s="17">
+      <c r="B28" s="17" t="s">
+        <v>605</v>
+      </c>
+      <c r="C28" s="17">
         <v>4</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D28" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="E22" s="16" t="s">
-        <v>566</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A23" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>568</v>
-      </c>
-      <c r="C23" s="17">
-        <v>1</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>569</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A24" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>570</v>
-      </c>
-      <c r="C24" s="17">
-        <v>4</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>571</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="25" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雅加达 dev</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dev 出网（跨区拉镜像 / 上游 mock）</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1（待核准）</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NAT 网关 + EIP</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dev 独立出口，经公网跨区拉马尼拉 ACR EE 镜像（EE 仅在 ap-southeast-6 有实例，且未绑定任何 VPC 内网入口）</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">禁止并入生产 8 个 EIP 的上游 / RDS 白名单池；Phase 2 支出待项目负责人核准（当前可用额度 0.00 USD，暂未创建）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:1">
-      <c r="A27" s="18" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A28" s="19" t="s">
-        <v>530</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>497</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>574</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>575</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>576</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="29" ht="42.75" customHeight="1" spans="1:6">
+      <c r="E28" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1" spans="1:6">
       <c r="A29" s="17" t="s">
         <v>253</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>577</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>578</v>
+        <v>608</v>
+      </c>
+      <c r="C29" s="17">
+        <v>1</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>579</v>
+        <v>243</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>580</v>
+        <v>609</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>581</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1" spans="1:6">
       <c r="A30" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>610</v>
+      </c>
+      <c r="C30" s="17">
+        <v>4</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>611</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="31" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A31" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>613</v>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1（已建）</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>615</v>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已建成：NAT 网关 ngw-k1aij9gqb72y38kl31vd2（Enhanced，落 pub-5a vsw-k1at4vt7fg8v4umkh9lg3）+ EIP eip-k1ans4dqvvci8x4jx1fx3 = 147.139.170.11（5Mbps PayByTraffic）；SNAT 条目 snat-k1acb22kut2qkwgdx4iub 覆盖 10.2.0.0/16；默认路由 rte-k1akjm3rkrdd62p55brnn 0.0.0.0/0→NatGateway 由系统随 NAT 自动下发。节点内实测出网公网 IP 即该 EIP。</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">禁止并入生产 8 个 EIP 的上游 / RDS 白名单池。NAT 上线使 10.2.0.0/16 首次获得公网可达性，生产 RDS 公网端点由「路由不可达」变为「仅靠安全组拦截」，故已把 43.118.96.65/32 的出向规则由 drop TCP 5432 收紧为 drop ALL（见下方安全组段）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:1">
+      <c r="A33" s="18" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A34" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>620</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>621</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="35" ht="42.75" customHeight="1" spans="1:6">
+      <c r="A35" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="B30" s="17" t="s">
-        <v>582</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>578</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>583</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>577</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A31" s="17" t="s">
+      <c r="B35" s="17" t="s">
+        <v>622</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>624</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>625</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A36" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="B31" s="17" t="s">
-        <v>582</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>585</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>586</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="32" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A32" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>582</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>585</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>589</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>590</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="33" ht="42.75" customHeight="1" spans="1:6">
-      <c r="A33" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>587</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>578</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>592</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>593</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="34" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A34" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>595</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>578</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>596</v>
-      </c>
-      <c r="E34" s="28" t="s">
-        <v>597</v>
-      </c>
-      <c r="F34" s="28" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="35" ht="23" customHeight="1" spans="1:6">
-      <c r="A35" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>599</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>578</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>600</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>597</v>
-      </c>
-      <c r="F35" s="28" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="36" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A36" s="17" t="s">
-        <v>465</v>
-      </c>
       <c r="B36" s="17" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>578</v>
+        <v>623</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>579</v>
+        <v>628</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:6">
       <c r="A37" s="17" t="s">
-        <v>465</v>
+        <v>253</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>605</v>
+        <v>627</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>578</v>
+        <v>630</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>583</v>
+        <v>631</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>606</v>
+        <v>633</v>
       </c>
     </row>
     <row r="38" ht="28.5" customHeight="1" spans="1:6">
       <c r="A38" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>634</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="39" ht="42.75" customHeight="1" spans="1:6">
+      <c r="A39" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>637</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>638</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="40" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A40" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>640</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>623</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>641</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>642</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="41" ht="23" customHeight="1" spans="1:6">
+      <c r="A41" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>644</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>623</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>645</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>642</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="42" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A42" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="B38" s="17" t="s">
-        <v>605</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>585</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>592</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>607</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A39" s="17" t="s">
+      <c r="B42" s="17" t="s">
+        <v>647</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>624</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A43" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="B39" s="17" t="s">
-        <v>605</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>585</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>589</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>590</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="40" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="B43" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>647</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="44" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A44" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>637</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A45" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>634</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="46" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A46" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="47" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A47" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="48" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A48" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">雅加达 dev</t>
+          <t xml:space="preserve">drop ALL -1/-1 + drop TCP 5432（优先级 1）</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="E48" s="16" t="s">
+        <v>662</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">sg-jkt-dev-app</t>
+          <t xml:space="preserve">已生效：堵住 dev 直连生产库公网入口这条最现实的数据外泄路径（验收 V1 实测 BLOCKED）。2026-09-30 随 NAT 上线追加 drop ALL（覆盖全部端口），原 drop TCP 5432 保留作双保险；出向规则数由 7 条增至 8 条。</t>
         </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">出</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">drop ALL -1/-1（优先级 1）</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.0.0.0/16（马尼拉生产 VPC）</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已生效：拒绝优先于 normal 安全组的默认全放通，dev 节点 / Pod 无法访问生产 VPC 内任意地址</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雅加达 dev</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sg-jkt-dev-app</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">出</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">drop ALL -1/-1（优先级 1）</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.1.0.0/16（新加坡备 VPC）</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已生效：同上，备 region 亦不可达；生产 apiserver 6443 / 10250 顺带被阻断（验收 V11）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雅加达 dev</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sg-jkt-dev-app</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">出</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">drop TCP 5432（优先级 1）</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43.118.96.65/32（生产 RDS 公网 IP）</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已生效：堵住 dev 直连生产库公网入口这条最现实的数据外泄路径（验收 V1：nc -zvw3 必须失败）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雅加达 dev</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sg-jkt-dev-app</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">出</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">accept TCP 443（优先级 10）</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.0.0.0/0，经 dev 自有 NAT 出网</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已生效：跨区拉镜像与上游调用只放行 443，不做全协议放通；目的侧再由生产 ACL 二次收敛</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雅加达 dev</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sg-jkt-dev-app</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">出</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">accept UDP 53（优先级 10 / 20）</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100.100.2.136/32、100.100.2.138/32，兜底 0.0.0.0/0</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已生效：VPC 内网 DNS 优先，ACR / RDS 等内网 endpoint 解析依赖此项</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雅加达 dev</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sg-jkt-dev-app</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">无自定义规则（保持默认）</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入向仅组内互通；生产侧安全组、生产 RDS 白名单、生产 ACR EE 公网 ACL 均未因本次改动（见 jakarta_dev_ledger §3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" spans="1:1">
-      <c r="A47" s="18" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A48" s="19" t="s">
-        <v>611</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>612</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>613</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="49" ht="28.5" customHeight="1" spans="1:6">
       <c r="A49" s="17" t="s">
-        <v>615</v>
+        <v>576</v>
       </c>
       <c r="B49" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>664</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>665</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="50" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A50" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>667</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>668</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="51" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A51" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" spans="1:1">
+      <c r="A53" s="18" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A54" s="19" t="s">
+        <v>673</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>674</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>675</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>676</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A55" s="17" t="s">
+        <v>677</v>
+      </c>
+      <c r="B55" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C49" s="17" t="s">
-        <v>616</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>617</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>618</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="50" ht="14.25" customHeight="1" spans="1:6">
-      <c r="A50" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="B50" s="17" t="s">
+      <c r="C55" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>679</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>680</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25" customHeight="1" spans="1:6">
+      <c r="A56" s="17" t="s">
+        <v>682</v>
+      </c>
+      <c r="B56" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C50" s="17" t="s">
-        <v>616</v>
-      </c>
-      <c r="D50" s="17" t="s">
-        <v>617</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>621</v>
-      </c>
-      <c r="F50" s="16" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="51" ht="42.75" customHeight="1" spans="1:6">
-      <c r="A51" s="17" t="s">
-        <v>623</v>
-      </c>
-      <c r="B51" s="17" t="s">
+      <c r="C56" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>679</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>683</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="57" ht="42.75" customHeight="1" spans="1:6">
+      <c r="A57" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="B57" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C51" s="17" t="s">
-        <v>624</v>
-      </c>
-      <c r="D51" s="17" t="s">
-        <v>625</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>626</v>
-      </c>
-      <c r="F51" s="16" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="52" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A52" s="17" t="s">
-        <v>628</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>629</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>630</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>631</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>632</v>
-      </c>
-      <c r="F52" s="16" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="53" ht="28.5" customHeight="1" spans="1:6">
-      <c r="A53" s="17" t="s">
-        <v>634</v>
-      </c>
-      <c r="B53" s="17" t="s">
+      <c r="C57" s="17" t="s">
+        <v>686</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>687</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="58" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A58" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>691</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>692</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>693</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>694</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="59" ht="28.5" customHeight="1" spans="1:6">
+      <c r="A59" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="B59" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C53" s="17" t="s">
-        <v>635</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>636</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>637</v>
-      </c>
-      <c r="F53" s="16" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="55" ht="14.25" customHeight="1" spans="1:1">
-      <c r="A55" s="25" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="56" ht="42.75" customHeight="1" spans="1:6">
-      <c r="A56" s="25" t="inlineStr">
+      <c r="C59" s="17" t="s">
+        <v>697</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>698</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25" customHeight="1" spans="1:1">
+      <c r="A61" s="25" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="62" ht="42.75" customHeight="1" spans="1:1">
+      <c r="A62" s="25" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="40.5" customHeight="true">
+      <c r="A63" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明：① 雅加达 dev 网络层（VPC + 3 个 vSwitch + sg-jkt-dev-app 出向规则）已于 2026-09-30 建成并复核，全部资源属 rg-nonprod（rg-aek4hk3prqgqjcy），标签 env=dev / project=new-api / isolation=structural-vpc；② 隔离是结构性的：跨 VPC 不通 + 生产 RDS 公网 5432 出向拒绝 + 无 CEN / 无 VPC 对等连接（实测 DescribeCens=0、ListVpcPeerConnections=0）；namespace 只作组织与 RBAC 边界，不构成网络或数据边界；③ 尚未创建（待支出核准）：dev NAT/EIP、ACK 集群与节点池、dev RDS PG 17.0、Tair、工作负载；RDS 建库参数已用 DryRun 验证通过（SecurityIPList 仅含上述三段 dev CIDR）。实测值与回滚命令见 deploy/jakarta_dev_ledger.md。</t>
+          <t xml:space="preserve">说明：② Phase 2 计算与数据层实测建成（2026-09-30 18:00–18:35 UTC+8，已产生费用）。ACK：集群 cb0abf5bc06034f7bbdb991752f6f3e62 / ack-newapi-jkt-dev，规格 ack.standard（基础版，集群管理费 0；生产用 ack.pro.small，Pro 约 0.6 USD/h，dev 用 Pro 会撑爆预算），版本 1.35.7-aliyun.1 与生产一致，Terway ENIIP、Service CIDR 172.23.0.0/20（马尼拉 172.21、新加坡 172.22 顺延，保持三站点同构）、ipvs、API Server 仅内网、删除保护已开。节点池 np-jkt-dev-app / npd3cc9d7f0503472f85420d30436269b5 / ESS asg-k1a59qtckc246wh9r3ay，min=1 max=3，机型 g9i/g8ine/g9ae.large，系统盘 cloud_essd 40G，按量，节点无公网 IP（出网走 NAT），无 SSH 密钥（运维入口用云助手）。RDS：pgm-d9j9p421lzx4gw73 / PostgreSQL 17.0 / pg.n2.2c.1m / 20G cloud_essd / Basic / 按量 / Running，落 data-5a vsw-k1a9u8pkwwkc6z0x6g0kc，内网 10.2.54.76:5432，仅 Private 端点未开公网，白名单只有 app 三段 10.2.16.0/20、10.2.32.0/20、10.2.80.0/20。⚠ 费用偏差：原估按 1 台节点，实测伸缩链路 0→1→3→2（autoscaler 因 coredns 跨可用区打散顶到 max，随后回收唯一空节点），稳态为 2 台 ≈132.82 USD/月，加 RDS 43.38 共 ≈176 USD/月 + NAT/EIP，比授权口径高约 66 USD/月；压回 1 台需把节点池收到单可用区（牺牲 AZ 冗余），待负责人定。另：余额 AvailableAmount 0.00 USD 下 EIP/NAT/ACK/RDS 全部下单成功，故 BSS 余额不能作为「能否开按量」的判据。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A63:F63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -9316,12 +9614,12 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:1">
       <c r="A1" s="12" t="s">
-        <v>640</v>
+        <v>703</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="13" t="s">
-        <v>641</v>
+        <v>704</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -9358,18 +9656,18 @@
       <c r="X2" s="9"/>
       <c r="Z2" s="13"/>
       <c r="AB2" s="22" t="s">
-        <v>642</v>
+        <v>705</v>
       </c>
     </row>
     <row r="3" ht="28.5" customHeight="1" spans="1:30">
       <c r="A3" s="14" t="s">
-        <v>643</v>
+        <v>706</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>70</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>644</v>
+        <v>707</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>209</v>
@@ -9378,73 +9676,73 @@
         <v>75</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>645</v>
+        <v>708</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>646</v>
+        <v>709</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>647</v>
+        <v>710</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>648</v>
+        <v>711</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>649</v>
+        <v>712</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>650</v>
+        <v>713</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>651</v>
+        <v>714</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>652</v>
+        <v>715</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>653</v>
+        <v>716</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>654</v>
+        <v>717</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>655</v>
+        <v>718</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>656</v>
+        <v>719</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>657</v>
+        <v>720</v>
       </c>
       <c r="S3" s="14" t="s">
-        <v>658</v>
+        <v>721</v>
       </c>
       <c r="T3" s="14" t="s">
-        <v>659</v>
+        <v>722</v>
       </c>
       <c r="U3" s="14" t="s">
-        <v>660</v>
+        <v>723</v>
       </c>
       <c r="V3" s="14" t="s">
-        <v>661</v>
+        <v>724</v>
       </c>
       <c r="W3" s="14" t="s">
-        <v>662</v>
+        <v>725</v>
       </c>
       <c r="X3" s="14" t="s">
-        <v>663</v>
+        <v>726</v>
       </c>
       <c r="Y3" s="14"/>
       <c r="Z3" s="14"/>
       <c r="AA3" s="14"/>
       <c r="AB3" s="14" t="s">
-        <v>664</v>
+        <v>727</v>
       </c>
       <c r="AC3" s="14" t="s">
-        <v>665</v>
+        <v>728</v>
       </c>
       <c r="AD3" s="14" t="s">
-        <v>666</v>
+        <v>729</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1" spans="1:30">
@@ -9455,13 +9753,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>667</v>
+        <v>730</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>668</v>
+        <v>731</v>
       </c>
       <c r="F4" s="17">
         <v>2</v>
@@ -9540,10 +9838,10 @@
       <c r="Z4" s="17"/>
       <c r="AA4" s="17"/>
       <c r="AB4" s="16" t="s">
-        <v>669</v>
+        <v>732</v>
       </c>
       <c r="AC4" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD4" s="17">
         <f t="shared" ref="AD4:AD59" si="15">IF($H4&lt;$G4,0,$F4/($H4-$G4+1))</f>
@@ -9558,13 +9856,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>671</v>
+        <v>734</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>672</v>
+        <v>735</v>
       </c>
       <c r="F5" s="17">
         <v>1</v>
@@ -9643,10 +9941,10 @@
       <c r="Z5" s="17"/>
       <c r="AA5" s="17"/>
       <c r="AB5" s="16" t="s">
-        <v>673</v>
+        <v>736</v>
       </c>
       <c r="AC5" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD5" s="17">
         <f t="shared" si="15"/>
@@ -9661,13 +9959,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>674</v>
+        <v>737</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>675</v>
+        <v>738</v>
       </c>
       <c r="F6" s="17">
         <v>1</v>
@@ -9746,10 +10044,10 @@
       <c r="Z6" s="17"/>
       <c r="AA6" s="17"/>
       <c r="AB6" s="16" t="s">
-        <v>676</v>
+        <v>739</v>
       </c>
       <c r="AC6" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD6" s="17">
         <f t="shared" si="15"/>
@@ -9764,13 +10062,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>677</v>
+        <v>740</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>678</v>
+        <v>741</v>
       </c>
       <c r="F7" s="17">
         <v>2</v>
@@ -9849,10 +10147,10 @@
       <c r="Z7" s="17"/>
       <c r="AA7" s="17"/>
       <c r="AB7" s="16" t="s">
-        <v>679</v>
+        <v>742</v>
       </c>
       <c r="AC7" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD7" s="17">
         <f t="shared" si="15"/>
@@ -9867,13 +10165,13 @@
         <v>5</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>680</v>
+        <v>743</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>681</v>
+        <v>744</v>
       </c>
       <c r="F8" s="17">
         <v>4</v>
@@ -9952,10 +10250,10 @@
       <c r="Z8" s="17"/>
       <c r="AA8" s="17"/>
       <c r="AB8" s="16" t="s">
-        <v>682</v>
+        <v>745</v>
       </c>
       <c r="AC8" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD8" s="17">
         <f t="shared" si="15"/>
@@ -9970,7 +10268,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>683</v>
+        <v>746</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>218</v>
@@ -10055,10 +10353,10 @@
       <c r="Z9" s="17"/>
       <c r="AA9" s="17"/>
       <c r="AB9" s="16" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="AC9" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD9" s="17">
         <f t="shared" si="15"/>
@@ -10073,7 +10371,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>293</v>
@@ -10158,10 +10456,10 @@
       <c r="Z10" s="17"/>
       <c r="AA10" s="17"/>
       <c r="AB10" s="16" t="s">
-        <v>686</v>
+        <v>749</v>
       </c>
       <c r="AC10" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD10" s="17">
         <f t="shared" si="15"/>
@@ -10176,13 +10474,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>687</v>
+        <v>750</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>688</v>
+        <v>751</v>
       </c>
       <c r="F11" s="17">
         <v>1</v>
@@ -10261,10 +10559,10 @@
       <c r="Z11" s="17"/>
       <c r="AA11" s="17"/>
       <c r="AB11" s="16" t="s">
-        <v>689</v>
+        <v>752</v>
       </c>
       <c r="AC11" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD11" s="17">
         <f t="shared" si="15"/>
@@ -10279,13 +10577,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>690</v>
+        <v>753</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>688</v>
+        <v>751</v>
       </c>
       <c r="F12" s="17">
         <v>2</v>
@@ -10364,10 +10662,10 @@
       <c r="Z12" s="17"/>
       <c r="AA12" s="17"/>
       <c r="AB12" s="16" t="s">
-        <v>691</v>
+        <v>754</v>
       </c>
       <c r="AC12" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD12" s="17">
         <f t="shared" si="15"/>
@@ -10382,13 +10680,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>692</v>
+        <v>755</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>693</v>
+        <v>756</v>
       </c>
       <c r="F13" s="17">
         <v>2</v>
@@ -10467,10 +10765,10 @@
       <c r="Z13" s="17"/>
       <c r="AA13" s="17"/>
       <c r="AB13" s="16" t="s">
-        <v>694</v>
+        <v>757</v>
       </c>
       <c r="AC13" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD13" s="17">
         <f t="shared" si="15"/>
@@ -10485,7 +10783,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>695</v>
+        <v>758</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>218</v>
@@ -10570,10 +10868,10 @@
       <c r="Z14" s="17"/>
       <c r="AA14" s="17"/>
       <c r="AB14" s="16" t="s">
-        <v>696</v>
+        <v>759</v>
       </c>
       <c r="AC14" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD14" s="17">
         <f t="shared" si="15"/>
@@ -10588,13 +10886,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>697</v>
+        <v>760</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>693</v>
+        <v>756</v>
       </c>
       <c r="F15" s="17">
         <v>2</v>
@@ -10673,10 +10971,10 @@
       <c r="Z15" s="17"/>
       <c r="AA15" s="17"/>
       <c r="AB15" s="16" t="s">
-        <v>698</v>
+        <v>761</v>
       </c>
       <c r="AC15" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD15" s="17">
         <f t="shared" si="15"/>
@@ -10691,7 +10989,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>699</v>
+        <v>762</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>293</v>
@@ -10776,10 +11074,10 @@
       <c r="Z16" s="17"/>
       <c r="AA16" s="17"/>
       <c r="AB16" s="16" t="s">
-        <v>700</v>
+        <v>763</v>
       </c>
       <c r="AC16" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD16" s="17">
         <f t="shared" si="15"/>
@@ -10794,13 +11092,13 @@
         <v>14</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>701</v>
+        <v>764</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>702</v>
+        <v>765</v>
       </c>
       <c r="F17" s="17">
         <v>1</v>
@@ -10879,10 +11177,10 @@
       <c r="Z17" s="17"/>
       <c r="AA17" s="17"/>
       <c r="AB17" s="16" t="s">
-        <v>703</v>
+        <v>766</v>
       </c>
       <c r="AC17" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD17" s="17">
         <f t="shared" si="15"/>
@@ -10897,13 +11195,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>704</v>
+        <v>767</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>705</v>
+        <v>768</v>
       </c>
       <c r="F18" s="17">
         <v>1</v>
@@ -10982,10 +11280,10 @@
       <c r="Z18" s="17"/>
       <c r="AA18" s="17"/>
       <c r="AB18" s="16" t="s">
-        <v>706</v>
+        <v>769</v>
       </c>
       <c r="AC18" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD18" s="17">
         <f t="shared" si="15"/>
@@ -11000,13 +11298,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>707</v>
+        <v>770</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>708</v>
+        <v>771</v>
       </c>
       <c r="F19" s="17">
         <v>1</v>
@@ -11085,10 +11383,10 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="17"/>
       <c r="AB19" s="16" t="s">
-        <v>709</v>
+        <v>772</v>
       </c>
       <c r="AC19" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD19" s="17">
         <f t="shared" si="15"/>
@@ -11103,7 +11401,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>710</v>
+        <v>773</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>293</v>
@@ -11188,10 +11486,10 @@
       <c r="Z20" s="17"/>
       <c r="AA20" s="17"/>
       <c r="AB20" s="16" t="s">
-        <v>711</v>
+        <v>774</v>
       </c>
       <c r="AC20" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD20" s="17">
         <f t="shared" si="15"/>
@@ -11206,13 +11504,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>712</v>
+        <v>775</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>713</v>
+        <v>776</v>
       </c>
       <c r="F21" s="17">
         <v>2</v>
@@ -11291,10 +11589,10 @@
       <c r="Z21" s="17"/>
       <c r="AA21" s="17"/>
       <c r="AB21" s="16" t="s">
-        <v>714</v>
+        <v>777</v>
       </c>
       <c r="AC21" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD21" s="17">
         <f t="shared" si="15"/>
@@ -11309,13 +11607,13 @@
         <v>19</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>715</v>
+        <v>778</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>693</v>
+        <v>756</v>
       </c>
       <c r="F22" s="17">
         <v>3</v>
@@ -11394,10 +11692,10 @@
       <c r="Z22" s="17"/>
       <c r="AA22" s="17"/>
       <c r="AB22" s="16" t="s">
-        <v>716</v>
+        <v>779</v>
       </c>
       <c r="AC22" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD22" s="17">
         <f t="shared" si="15"/>
@@ -11412,7 +11710,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>717</v>
+        <v>780</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>218</v>
@@ -11497,10 +11795,10 @@
       <c r="Z23" s="17"/>
       <c r="AA23" s="17"/>
       <c r="AB23" s="16" t="s">
-        <v>718</v>
+        <v>781</v>
       </c>
       <c r="AC23" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD23" s="17">
         <f t="shared" si="15"/>
@@ -11515,7 +11813,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>719</v>
+        <v>782</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>218</v>
@@ -11600,10 +11898,10 @@
       <c r="Z24" s="17"/>
       <c r="AA24" s="17"/>
       <c r="AB24" s="16" t="s">
-        <v>720</v>
+        <v>783</v>
       </c>
       <c r="AC24" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD24" s="17">
         <f t="shared" si="15"/>
@@ -11618,13 +11916,13 @@
         <v>22</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>721</v>
+        <v>784</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>722</v>
+        <v>785</v>
       </c>
       <c r="F25" s="17">
         <v>2</v>
@@ -11703,10 +12001,10 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="17"/>
       <c r="AB25" s="16" t="s">
-        <v>723</v>
+        <v>786</v>
       </c>
       <c r="AC25" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD25" s="17">
         <f t="shared" si="15"/>
@@ -11721,7 +12019,7 @@
         <v>23</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>724</v>
+        <v>787</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>293</v>
@@ -11806,10 +12104,10 @@
       <c r="Z26" s="17"/>
       <c r="AA26" s="17"/>
       <c r="AB26" s="16" t="s">
-        <v>725</v>
+        <v>788</v>
       </c>
       <c r="AC26" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD26" s="17">
         <f t="shared" si="15"/>
@@ -11824,7 +12122,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>726</v>
+        <v>789</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>218</v>
@@ -11909,10 +12207,10 @@
       <c r="Z27" s="17"/>
       <c r="AA27" s="17"/>
       <c r="AB27" s="16" t="s">
-        <v>727</v>
+        <v>790</v>
       </c>
       <c r="AC27" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD27" s="17">
         <f t="shared" si="15"/>
@@ -11927,13 +12225,13 @@
         <v>25</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>728</v>
+        <v>791</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>729</v>
+        <v>792</v>
       </c>
       <c r="F28" s="17">
         <v>2</v>
@@ -12012,10 +12310,10 @@
       <c r="Z28" s="17"/>
       <c r="AA28" s="17"/>
       <c r="AB28" s="16" t="s">
-        <v>730</v>
+        <v>793</v>
       </c>
       <c r="AC28" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD28" s="17">
         <f t="shared" si="15"/>
@@ -12030,7 +12328,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>731</v>
+        <v>794</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>218</v>
@@ -12115,10 +12413,10 @@
       <c r="Z29" s="17"/>
       <c r="AA29" s="17"/>
       <c r="AB29" s="16" t="s">
-        <v>732</v>
+        <v>795</v>
       </c>
       <c r="AC29" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD29" s="17">
         <f t="shared" si="15"/>
@@ -12133,7 +12431,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>733</v>
+        <v>796</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>293</v>
@@ -12218,10 +12516,10 @@
       <c r="Z30" s="17"/>
       <c r="AA30" s="17"/>
       <c r="AB30" s="16" t="s">
-        <v>734</v>
+        <v>797</v>
       </c>
       <c r="AC30" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD30" s="17">
         <f t="shared" si="15"/>
@@ -12236,13 +12534,13 @@
         <v>28</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>735</v>
+        <v>798</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>736</v>
+        <v>799</v>
       </c>
       <c r="F31" s="17">
         <v>2</v>
@@ -12321,10 +12619,10 @@
       <c r="Z31" s="17"/>
       <c r="AA31" s="17"/>
       <c r="AB31" s="16" t="s">
-        <v>737</v>
+        <v>800</v>
       </c>
       <c r="AC31" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD31" s="17">
         <f t="shared" si="15"/>
@@ -12339,7 +12637,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>738</v>
+        <v>801</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>293</v>
@@ -12424,10 +12722,10 @@
       <c r="Z32" s="17"/>
       <c r="AA32" s="17"/>
       <c r="AB32" s="16" t="s">
-        <v>739</v>
+        <v>802</v>
       </c>
       <c r="AC32" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD32" s="17">
         <f t="shared" si="15"/>
@@ -12442,13 +12740,13 @@
         <v>30</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>740</v>
+        <v>803</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>741</v>
+        <v>804</v>
       </c>
       <c r="F33" s="17">
         <v>2</v>
@@ -12527,10 +12825,10 @@
       <c r="Z33" s="17"/>
       <c r="AA33" s="17"/>
       <c r="AB33" s="16" t="s">
-        <v>742</v>
+        <v>805</v>
       </c>
       <c r="AC33" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD33" s="17">
         <f t="shared" si="15"/>
@@ -12545,13 +12843,13 @@
         <v>31</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>743</v>
+        <v>806</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>744</v>
+        <v>807</v>
       </c>
       <c r="F34" s="17">
         <v>3</v>
@@ -12630,10 +12928,10 @@
       <c r="Z34" s="17"/>
       <c r="AA34" s="17"/>
       <c r="AB34" s="16" t="s">
-        <v>745</v>
+        <v>808</v>
       </c>
       <c r="AC34" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD34" s="17">
         <f t="shared" si="15"/>
@@ -12648,7 +12946,7 @@
         <v>32</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>746</v>
+        <v>809</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>218</v>
@@ -12733,10 +13031,10 @@
       <c r="Z35" s="17"/>
       <c r="AA35" s="17"/>
       <c r="AB35" s="16" t="s">
-        <v>747</v>
+        <v>810</v>
       </c>
       <c r="AC35" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD35" s="17">
         <f t="shared" si="15"/>
@@ -12751,13 +13049,13 @@
         <v>33</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>748</v>
+        <v>811</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>749</v>
+        <v>812</v>
       </c>
       <c r="F36" s="17">
         <v>2</v>
@@ -12836,10 +13134,10 @@
       <c r="Z36" s="17"/>
       <c r="AA36" s="17"/>
       <c r="AB36" s="16" t="s">
-        <v>750</v>
+        <v>813</v>
       </c>
       <c r="AC36" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD36" s="17">
         <f t="shared" si="15"/>
@@ -12854,13 +13152,13 @@
         <v>34</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>751</v>
+        <v>814</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>752</v>
+        <v>815</v>
       </c>
       <c r="F37" s="17">
         <v>1</v>
@@ -12939,10 +13237,10 @@
       <c r="Z37" s="17"/>
       <c r="AA37" s="17"/>
       <c r="AB37" s="16" t="s">
-        <v>753</v>
+        <v>816</v>
       </c>
       <c r="AC37" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD37" s="17">
         <f t="shared" si="15"/>
@@ -12957,7 +13255,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>754</v>
+        <v>817</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>218</v>
@@ -13042,10 +13340,10 @@
       <c r="Z38" s="17"/>
       <c r="AA38" s="17"/>
       <c r="AB38" s="16" t="s">
-        <v>755</v>
+        <v>818</v>
       </c>
       <c r="AC38" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD38" s="17">
         <f t="shared" si="15"/>
@@ -13060,13 +13358,13 @@
         <v>36</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>756</v>
+        <v>819</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>757</v>
+        <v>820</v>
       </c>
       <c r="F39" s="17">
         <v>2</v>
@@ -13145,10 +13443,10 @@
       <c r="Z39" s="17"/>
       <c r="AA39" s="17"/>
       <c r="AB39" s="16" t="s">
-        <v>758</v>
+        <v>821</v>
       </c>
       <c r="AC39" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD39" s="17">
         <f t="shared" si="15"/>
@@ -13163,13 +13461,13 @@
         <v>37</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>759</v>
+        <v>822</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>760</v>
+        <v>823</v>
       </c>
       <c r="F40" s="17">
         <v>2</v>
@@ -13248,10 +13546,10 @@
       <c r="Z40" s="17"/>
       <c r="AA40" s="17"/>
       <c r="AB40" s="16" t="s">
-        <v>761</v>
+        <v>824</v>
       </c>
       <c r="AC40" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD40" s="17">
         <f t="shared" si="15"/>
@@ -13266,7 +13564,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>762</v>
+        <v>825</v>
       </c>
       <c r="D41" s="15" t="s">
         <v>293</v>
@@ -13351,10 +13649,10 @@
       <c r="Z41" s="17"/>
       <c r="AA41" s="17"/>
       <c r="AB41" s="16" t="s">
-        <v>763</v>
+        <v>826</v>
       </c>
       <c r="AC41" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD41" s="17">
         <f t="shared" si="15"/>
@@ -13369,7 +13667,7 @@
         <v>39</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>764</v>
+        <v>827</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>293</v>
@@ -13454,10 +13752,10 @@
       <c r="Z42" s="17"/>
       <c r="AA42" s="17"/>
       <c r="AB42" s="16" t="s">
-        <v>765</v>
+        <v>828</v>
       </c>
       <c r="AC42" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD42" s="17">
         <f t="shared" si="15"/>
@@ -13472,13 +13770,13 @@
         <v>40</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>766</v>
+        <v>829</v>
       </c>
       <c r="D43" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>767</v>
+        <v>830</v>
       </c>
       <c r="F43" s="17">
         <v>1</v>
@@ -13557,10 +13855,10 @@
       <c r="Z43" s="17"/>
       <c r="AA43" s="17"/>
       <c r="AB43" s="16" t="s">
-        <v>768</v>
+        <v>831</v>
       </c>
       <c r="AC43" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD43" s="17">
         <f t="shared" si="15"/>
@@ -13575,13 +13873,13 @@
         <v>41</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>769</v>
+        <v>832</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>770</v>
+        <v>833</v>
       </c>
       <c r="F44" s="17">
         <v>3</v>
@@ -13660,10 +13958,10 @@
       <c r="Z44" s="17"/>
       <c r="AA44" s="17"/>
       <c r="AB44" s="16" t="s">
-        <v>771</v>
+        <v>834</v>
       </c>
       <c r="AC44" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD44" s="17">
         <f t="shared" si="15"/>
@@ -13678,13 +13976,13 @@
         <v>42</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>772</v>
+        <v>835</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>773</v>
+        <v>836</v>
       </c>
       <c r="F45" s="17">
         <v>2</v>
@@ -13763,10 +14061,10 @@
       <c r="Z45" s="17"/>
       <c r="AA45" s="17"/>
       <c r="AB45" s="16" t="s">
-        <v>774</v>
+        <v>837</v>
       </c>
       <c r="AC45" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD45" s="17">
         <f t="shared" si="15"/>
@@ -13781,7 +14079,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>775</v>
+        <v>838</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>293</v>
@@ -13866,10 +14164,10 @@
       <c r="Z46" s="17"/>
       <c r="AA46" s="17"/>
       <c r="AB46" s="16" t="s">
-        <v>776</v>
+        <v>839</v>
       </c>
       <c r="AC46" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD46" s="17">
         <f t="shared" si="15"/>
@@ -13884,13 +14182,13 @@
         <v>44</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>777</v>
+        <v>840</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>778</v>
+        <v>841</v>
       </c>
       <c r="F47" s="17">
         <v>3</v>
@@ -13969,10 +14267,10 @@
       <c r="Z47" s="17"/>
       <c r="AA47" s="17"/>
       <c r="AB47" s="16" t="s">
-        <v>779</v>
+        <v>842</v>
       </c>
       <c r="AC47" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD47" s="17">
         <f t="shared" si="15"/>
@@ -13987,13 +14285,13 @@
         <v>45</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>780</v>
+        <v>843</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>781</v>
+        <v>844</v>
       </c>
       <c r="F48" s="17">
         <v>4</v>
@@ -14072,10 +14370,10 @@
       <c r="Z48" s="17"/>
       <c r="AA48" s="17"/>
       <c r="AB48" s="16" t="s">
-        <v>782</v>
+        <v>845</v>
       </c>
       <c r="AC48" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD48" s="17">
         <f t="shared" si="15"/>
@@ -14090,7 +14388,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>783</v>
+        <v>846</v>
       </c>
       <c r="D49" s="15" t="s">
         <v>218</v>
@@ -14175,10 +14473,10 @@
       <c r="Z49" s="17"/>
       <c r="AA49" s="17"/>
       <c r="AB49" s="16" t="s">
-        <v>784</v>
+        <v>847</v>
       </c>
       <c r="AC49" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD49" s="17">
         <f t="shared" si="15"/>
@@ -14193,7 +14491,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>218</v>
@@ -14278,10 +14576,10 @@
       <c r="Z50" s="17"/>
       <c r="AA50" s="17"/>
       <c r="AB50" s="16" t="s">
-        <v>786</v>
+        <v>849</v>
       </c>
       <c r="AC50" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD50" s="17">
         <f t="shared" si="15"/>
@@ -14296,13 +14594,13 @@
         <v>48</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>787</v>
+        <v>850</v>
       </c>
       <c r="D51" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>788</v>
+        <v>851</v>
       </c>
       <c r="F51" s="17">
         <v>1</v>
@@ -14381,10 +14679,10 @@
       <c r="Z51" s="17"/>
       <c r="AA51" s="17"/>
       <c r="AB51" s="16" t="s">
-        <v>789</v>
+        <v>852</v>
       </c>
       <c r="AC51" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD51" s="17">
         <f t="shared" si="15"/>
@@ -14399,13 +14697,13 @@
         <v>49</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>790</v>
+        <v>853</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>791</v>
+        <v>854</v>
       </c>
       <c r="F52" s="17">
         <v>2</v>
@@ -14484,10 +14782,10 @@
       <c r="Z52" s="17"/>
       <c r="AA52" s="17"/>
       <c r="AB52" s="16" t="s">
-        <v>792</v>
+        <v>855</v>
       </c>
       <c r="AC52" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD52" s="17">
         <f t="shared" si="15"/>
@@ -14502,13 +14800,13 @@
         <v>50</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>793</v>
+        <v>856</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>794</v>
+        <v>857</v>
       </c>
       <c r="F53" s="17">
         <v>3</v>
@@ -14587,10 +14885,10 @@
       <c r="Z53" s="17"/>
       <c r="AA53" s="17"/>
       <c r="AB53" s="16" t="s">
-        <v>795</v>
+        <v>858</v>
       </c>
       <c r="AC53" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD53" s="17">
         <f t="shared" si="15"/>
@@ -14605,7 +14903,7 @@
         <v>51</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>796</v>
+        <v>859</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>293</v>
@@ -14690,10 +14988,10 @@
       <c r="Z54" s="17"/>
       <c r="AA54" s="17"/>
       <c r="AB54" s="16" t="s">
-        <v>797</v>
+        <v>860</v>
       </c>
       <c r="AC54" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD54" s="17">
         <f t="shared" si="15"/>
@@ -14708,13 +15006,13 @@
         <v>52</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>798</v>
+        <v>861</v>
       </c>
       <c r="D55" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>799</v>
+        <v>862</v>
       </c>
       <c r="F55" s="17">
         <v>1</v>
@@ -14793,10 +15091,10 @@
       <c r="Z55" s="17"/>
       <c r="AA55" s="17"/>
       <c r="AB55" s="16" t="s">
-        <v>800</v>
+        <v>863</v>
       </c>
       <c r="AC55" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD55" s="17">
         <f t="shared" si="15"/>
@@ -14811,13 +15109,13 @@
         <v>53</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>801</v>
+        <v>864</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>802</v>
+        <v>865</v>
       </c>
       <c r="F56" s="17">
         <v>1</v>
@@ -14896,10 +15194,10 @@
       <c r="Z56" s="17"/>
       <c r="AA56" s="17"/>
       <c r="AB56" s="16" t="s">
-        <v>803</v>
+        <v>866</v>
       </c>
       <c r="AC56" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD56" s="17">
         <f t="shared" si="15"/>
@@ -14914,7 +15212,7 @@
         <v>54</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>804</v>
+        <v>867</v>
       </c>
       <c r="D57" s="15" t="s">
         <v>293</v>
@@ -14999,10 +15297,10 @@
       <c r="Z57" s="17"/>
       <c r="AA57" s="17"/>
       <c r="AB57" s="16" t="s">
-        <v>805</v>
+        <v>868</v>
       </c>
       <c r="AC57" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD57" s="17">
         <f t="shared" si="15"/>
@@ -15017,13 +15315,13 @@
         <v>55</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>806</v>
+        <v>869</v>
       </c>
       <c r="D58" s="15" t="s">
         <v>293</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>807</v>
+        <v>870</v>
       </c>
       <c r="F58" s="17">
         <v>1</v>
@@ -15102,10 +15400,10 @@
       <c r="Z58" s="17"/>
       <c r="AA58" s="17"/>
       <c r="AB58" s="16" t="s">
-        <v>808</v>
+        <v>871</v>
       </c>
       <c r="AC58" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD58" s="17">
         <f t="shared" si="15"/>
@@ -15120,13 +15418,13 @@
         <v>56</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>809</v>
+        <v>872</v>
       </c>
       <c r="D59" s="15" t="s">
         <v>218</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>810</v>
+        <v>873</v>
       </c>
       <c r="F59" s="17">
         <v>1</v>
@@ -15205,10 +15503,10 @@
       <c r="Z59" s="17"/>
       <c r="AA59" s="17"/>
       <c r="AB59" s="16" t="s">
-        <v>811</v>
+        <v>874</v>
       </c>
       <c r="AC59" s="16" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="AD59" s="17">
         <f t="shared" si="15"/>
@@ -15217,57 +15515,57 @@
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:1">
       <c r="A61" s="18" t="s">
-        <v>812</v>
+        <v>875</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1" spans="1:27">
       <c r="A62" s="19" t="s">
-        <v>813</v>
+        <v>876</v>
       </c>
       <c r="J62" s="19" t="s">
-        <v>649</v>
+        <v>712</v>
       </c>
       <c r="K62" s="19" t="s">
-        <v>650</v>
+        <v>713</v>
       </c>
       <c r="L62" s="19" t="s">
-        <v>651</v>
+        <v>714</v>
       </c>
       <c r="M62" s="19" t="s">
-        <v>652</v>
+        <v>715</v>
       </c>
       <c r="N62" s="19" t="s">
-        <v>653</v>
+        <v>716</v>
       </c>
       <c r="O62" s="19" t="s">
-        <v>654</v>
+        <v>717</v>
       </c>
       <c r="P62" s="19" t="s">
-        <v>655</v>
+        <v>718</v>
       </c>
       <c r="Q62" s="19" t="s">
-        <v>656</v>
+        <v>719</v>
       </c>
       <c r="R62" s="19" t="s">
-        <v>657</v>
+        <v>720</v>
       </c>
       <c r="S62" s="19" t="s">
-        <v>658</v>
+        <v>721</v>
       </c>
       <c r="T62" s="19" t="s">
-        <v>659</v>
+        <v>722</v>
       </c>
       <c r="U62" s="19" t="s">
-        <v>660</v>
+        <v>723</v>
       </c>
       <c r="V62" s="19" t="s">
-        <v>661</v>
+        <v>724</v>
       </c>
       <c r="W62" s="19" t="s">
-        <v>662</v>
+        <v>725</v>
       </c>
       <c r="X62" s="19" t="s">
-        <v>663</v>
+        <v>726</v>
       </c>
       <c r="Y62" s="19"/>
       <c r="Z62" s="19"/>
@@ -15411,23 +15709,23 @@
     </row>
     <row r="65" ht="14.25" customHeight="1" spans="1:2">
       <c r="A65" s="23" t="s">
-        <v>814</v>
+        <v>877</v>
       </c>
       <c r="B65" s="23" t="str">
-        <f>IF(COUNTIF(J63:X64,"&gt;4")&gt;0,"存在超载时段，需调整排期","负荷均衡：每人每时段 ≤ 4 人时")</f>
+        <f t="array" ref="B65">IF(COUNTIF(J63:X64,"&gt;4")&gt;0,"存在超载时段，需调整排期","负荷均衡：每人每时段 ≤ 4 人时")</f>
         <v>负荷均衡：每人每时段 ≤ 4 人时</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1" spans="1:5">
       <c r="A66" s="24" t="s">
-        <v>815</v>
+        <v>878</v>
       </c>
       <c r="B66" s="24">
         <f>SUM($F$4:$F$59)</f>
         <v>113</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>816</v>
+        <v>879</v>
       </c>
       <c r="D66" s="24">
         <f>2*5*3*4</f>
@@ -15440,15 +15738,15 @@
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:1">
       <c r="A68" s="18" t="s">
-        <v>817</v>
+        <v>880</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1" spans="1:7">
       <c r="A69" s="19" t="s">
-        <v>818</v>
+        <v>881</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>819</v>
+        <v>882</v>
       </c>
       <c r="C69" s="19" t="s">
         <v>71</v>
@@ -15457,90 +15755,90 @@
         <v>76</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>820</v>
+        <v>883</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>821</v>
+        <v>884</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>822</v>
+        <v>885</v>
       </c>
     </row>
     <row r="70" ht="28.5" customHeight="1" spans="1:7">
       <c r="A70" s="15" t="s">
-        <v>823</v>
+        <v>886</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>824</v>
+        <v>887</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>825</v>
+        <v>888</v>
       </c>
       <c r="D70" s="17" t="s">
         <v>87</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>826</v>
+        <v>889</v>
       </c>
       <c r="F70" s="17" t="s">
-        <v>827</v>
+        <v>890</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>828</v>
+        <v>891</v>
       </c>
     </row>
     <row r="71" ht="42.75" customHeight="1" spans="1:7">
       <c r="A71" s="15" t="s">
-        <v>708</v>
+        <v>771</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>829</v>
+        <v>892</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>830</v>
+        <v>893</v>
       </c>
       <c r="D71" s="17" t="s">
         <v>120</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>832</v>
+        <v>895</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>833</v>
+        <v>896</v>
       </c>
     </row>
     <row r="72" ht="28.5" customHeight="1" spans="1:7">
       <c r="A72" s="15" t="s">
-        <v>834</v>
+        <v>897</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>835</v>
+        <v>898</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>825</v>
+        <v>888</v>
       </c>
       <c r="D72" s="17" t="s">
         <v>102</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="F72" s="17" t="s">
-        <v>836</v>
+        <v>899</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>837</v>
+        <v>900</v>
       </c>
     </row>
     <row r="73" ht="28.5" customHeight="1" spans="1:7">
       <c r="A73" s="15" t="s">
-        <v>838</v>
+        <v>901</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>839</v>
+        <v>902</v>
       </c>
       <c r="C73" s="17" t="s">
         <v>152</v>
@@ -15549,21 +15847,21 @@
         <v>87</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="F73" s="17" t="s">
-        <v>840</v>
+        <v>903</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>841</v>
+        <v>904</v>
       </c>
     </row>
     <row r="74" ht="28.5" customHeight="1" spans="1:7">
       <c r="A74" s="15" t="s">
-        <v>842</v>
+        <v>905</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>843</v>
+        <v>906</v>
       </c>
       <c r="C74" s="17" t="s">
         <v>177</v>
@@ -15572,21 +15870,21 @@
         <v>120</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="F74" s="17" t="s">
-        <v>844</v>
+        <v>907</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>845</v>
+        <v>908</v>
       </c>
     </row>
     <row r="75" ht="57" customHeight="1" spans="1:7">
       <c r="A75" s="15" t="s">
-        <v>675</v>
+        <v>738</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>846</v>
+        <v>909</v>
       </c>
       <c r="C75" s="17" t="s">
         <v>242</v>
@@ -15595,179 +15893,179 @@
         <v>120</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>836</v>
+        <v>899</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>847</v>
+        <v>910</v>
       </c>
     </row>
     <row r="76" ht="28.5" customHeight="1" spans="1:7">
       <c r="A76" s="15" t="s">
-        <v>688</v>
+        <v>751</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>848</v>
+        <v>911</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>849</v>
+        <v>912</v>
       </c>
       <c r="D76" s="17" t="s">
         <v>120</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>836</v>
+        <v>899</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>850</v>
+        <v>913</v>
       </c>
     </row>
     <row r="77" ht="71.25" customHeight="1" spans="1:7">
       <c r="A77" s="15" t="s">
-        <v>851</v>
+        <v>914</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>852</v>
+        <v>915</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>853</v>
+        <v>916</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>854</v>
+        <v>917</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>855</v>
+        <v>918</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>827</v>
+        <v>890</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>856</v>
+        <v>919</v>
       </c>
     </row>
     <row r="78" ht="28.5" customHeight="1" spans="1:7">
       <c r="A78" s="15" t="s">
-        <v>857</v>
+        <v>920</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>858</v>
+        <v>921</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>825</v>
+        <v>888</v>
       </c>
       <c r="D78" s="17" t="s">
         <v>109</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>836</v>
+        <v>899</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>859</v>
+        <v>922</v>
       </c>
     </row>
     <row r="79" ht="57" customHeight="1" spans="1:7">
       <c r="A79" s="15" t="s">
-        <v>860</v>
+        <v>923</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>861</v>
+        <v>924</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>862</v>
+        <v>925</v>
       </c>
       <c r="D79" s="17" t="s">
         <v>120</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>855</v>
+        <v>918</v>
       </c>
       <c r="F79" s="17" t="s">
-        <v>836</v>
+        <v>899</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>863</v>
+        <v>926</v>
       </c>
     </row>
     <row r="80" ht="42.75" customHeight="1" spans="1:7">
       <c r="A80" s="15" t="s">
-        <v>864</v>
+        <v>927</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>865</v>
+        <v>928</v>
       </c>
       <c r="C80" s="17" t="s">
         <v>295</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>854</v>
+        <v>917</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>855</v>
+        <v>918</v>
       </c>
       <c r="F80" s="17" t="s">
-        <v>836</v>
+        <v>899</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>866</v>
+        <v>929</v>
       </c>
     </row>
     <row r="81" ht="42.75" customHeight="1" spans="1:7">
       <c r="A81" s="15" t="s">
-        <v>867</v>
+        <v>930</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>868</v>
+        <v>931</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>869</v>
+        <v>932</v>
       </c>
       <c r="D81" s="17" t="s">
         <v>87</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>855</v>
+        <v>918</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>836</v>
+        <v>899</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>870</v>
+        <v>933</v>
       </c>
     </row>
     <row r="82" ht="42.75" customHeight="1" spans="1:7">
       <c r="A82" s="15" t="s">
-        <v>871</v>
+        <v>934</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>872</v>
+        <v>935</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>873</v>
+        <v>936</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>874</v>
+        <v>937</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>855</v>
+        <v>918</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>836</v>
+        <v>899</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>875</v>
+        <v>938</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1" spans="1:1">
       <c r="A83" s="25" t="s">
-        <v>876</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -15786,12 +16084,12 @@
     <mergeCell ref="A83:AD83"/>
   </mergeCells>
   <conditionalFormatting sqref="J4:X59">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"■■"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J63:X64">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15814,35 +16112,35 @@
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
     <col min="8" max="8" width="34" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="9" max="26" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>877</v>
+        <v>940</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>878</v>
+        <v>941</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>879</v>
+        <v>942</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>880</v>
+        <v>943</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>881</v>
+        <v>944</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>882</v>
+        <v>945</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>665</v>
+        <v>728</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>80</v>
@@ -15850,7 +16148,7 @@
     </row>
     <row r="4" ht="42.75" customHeight="1" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>883</v>
+        <v>946</v>
       </c>
       <c r="B4" s="5">
         <v>-5</v>
@@ -15860,24 +16158,24 @@
         <v>46288</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>884</v>
+        <v>947</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>885</v>
+        <v>948</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>886</v>
+        <v>949</v>
       </c>
     </row>
     <row r="5" ht="28.5" customHeight="1" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>887</v>
+        <v>950</v>
       </c>
       <c r="B5" s="5">
         <v>0</v>
@@ -15887,24 +16185,24 @@
         <v>46293</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>888</v>
+        <v>951</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>889</v>
+        <v>952</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>890</v>
+        <v>953</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>891</v>
+        <v>954</v>
       </c>
     </row>
     <row r="6" ht="42.75" customHeight="1" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>892</v>
+        <v>955</v>
       </c>
       <c r="B6" s="5">
         <v>1</v>
@@ -15914,24 +16212,24 @@
         <v>46294</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>893</v>
+        <v>956</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>894</v>
+        <v>957</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>890</v>
+        <v>953</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>895</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7" ht="42.75" customHeight="1" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>896</v>
+        <v>959</v>
       </c>
       <c r="B7" s="5">
         <v>2</v>
@@ -15941,24 +16239,24 @@
         <v>46295</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>897</v>
+        <v>960</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>898</v>
+        <v>961</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>890</v>
+        <v>953</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>899</v>
+        <v>962</v>
       </c>
     </row>
     <row r="8" ht="42.75" customHeight="1" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>900</v>
+        <v>963</v>
       </c>
       <c r="B8" s="5">
         <v>3</v>
@@ -15968,24 +16266,24 @@
         <v>46296</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>901</v>
+        <v>964</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>902</v>
+        <v>965</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>890</v>
+        <v>953</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>903</v>
+        <v>966</v>
       </c>
     </row>
     <row r="9" ht="28.5" customHeight="1" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>904</v>
+        <v>967</v>
       </c>
       <c r="B9" s="5">
         <v>4</v>
@@ -15995,47 +16293,47 @@
         <v>46297</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>905</v>
+        <v>968</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>906</v>
+        <v>969</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>890</v>
+        <v>953</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>907</v>
+        <v>970</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:1">
       <c r="A11" s="7" t="s">
-        <v>908</v>
+        <v>971</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>909</v>
+        <v>972</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>910</v>
+        <v>973</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>911</v>
+        <v>974</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>912</v>
+        <v>975</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>913</v>
+        <v>976</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>914</v>
+        <v>977</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>915</v>
+        <v>978</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>80</v>
@@ -16043,439 +16341,439 @@
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>916</v>
+        <v>979</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>917</v>
+        <v>980</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>918</v>
+        <v>981</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>87</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>919</v>
+        <v>982</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>920</v>
+        <v>983</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>921</v>
+        <v>984</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>922</v>
+        <v>985</v>
       </c>
     </row>
     <row r="14" ht="42.75" customHeight="1" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>923</v>
+        <v>986</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>924</v>
+        <v>987</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>925</v>
+        <v>988</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>120</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>926</v>
+        <v>989</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>920</v>
+        <v>983</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>927</v>
+        <v>990</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>928</v>
+        <v>991</v>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>929</v>
+        <v>992</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>930</v>
+        <v>993</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>931</v>
+        <v>994</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>854</v>
+        <v>917</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>932</v>
+        <v>995</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>920</v>
+        <v>983</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>933</v>
+        <v>996</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>934</v>
+        <v>997</v>
       </c>
     </row>
     <row r="16" ht="42.75" customHeight="1" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>935</v>
+        <v>998</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>936</v>
+        <v>999</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>937</v>
+        <v>1000</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>87</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>938</v>
+        <v>1001</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>940</v>
+        <v>1003</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>941</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="17" ht="28.5" customHeight="1" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>942</v>
+        <v>1005</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>943</v>
+        <v>1006</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>944</v>
+        <v>1007</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>120</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>945</v>
+        <v>1008</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>946</v>
+        <v>1009</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>947</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="18" ht="57" customHeight="1" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>948</v>
+        <v>1011</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>949</v>
+        <v>1012</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>950</v>
+        <v>1013</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>293</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>951</v>
+        <v>1014</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>952</v>
+        <v>1015</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>953</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="19" ht="42.75" customHeight="1" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>954</v>
+        <v>1017</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>955</v>
+        <v>1018</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>956</v>
+        <v>1019</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>293</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>957</v>
+        <v>1020</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>958</v>
+        <v>1021</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>959</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="20" ht="42.75" customHeight="1" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>960</v>
+        <v>1023</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>961</v>
+        <v>1024</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>962</v>
+        <v>1025</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>218</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>963</v>
+        <v>1026</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>964</v>
+        <v>1027</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>959</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="21" ht="42.75" customHeight="1" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>965</v>
+        <v>1028</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>966</v>
+        <v>1029</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>967</v>
+        <v>1030</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>293</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>968</v>
+        <v>1031</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>969</v>
+        <v>1032</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>970</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="22" ht="42.75" customHeight="1" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>971</v>
+        <v>1034</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>972</v>
+        <v>1035</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>973</v>
+        <v>1036</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>218</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>974</v>
+        <v>1037</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>975</v>
+        <v>1038</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>976</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="23" ht="42.75" customHeight="1" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>977</v>
+        <v>1040</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>978</v>
+        <v>1041</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>979</v>
+        <v>1042</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>293</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>980</v>
+        <v>1043</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>981</v>
+        <v>1044</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>982</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="24" ht="57" customHeight="1" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>983</v>
+        <v>1046</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>984</v>
+        <v>1047</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>985</v>
+        <v>1048</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>986</v>
+        <v>1049</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>987</v>
+        <v>1050</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>988</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="25" ht="42.75" customHeight="1" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>989</v>
+        <v>1052</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>990</v>
+        <v>1053</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>991</v>
+        <v>1054</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>218</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>992</v>
+        <v>1055</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>993</v>
+        <v>1056</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>994</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="26" ht="71.25" customHeight="1" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>995</v>
+        <v>1058</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>996</v>
+        <v>1059</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>997</v>
+        <v>1060</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>998</v>
+        <v>1061</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>999</v>
+        <v>1062</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>920</v>
+        <v>983</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>1000</v>
+        <v>1063</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>1001</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="27" ht="42.75" customHeight="1" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>1002</v>
+        <v>1065</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1003</v>
+        <v>1066</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>1004</v>
+        <v>1067</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>87</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1005</v>
+        <v>1068</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>1006</v>
+        <v>1069</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>1007</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="28" ht="57" customHeight="1" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>1008</v>
+        <v>1071</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>1009</v>
+        <v>1072</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>1010</v>
+        <v>1073</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>87</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>1011</v>
+        <v>1074</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>939</v>
+        <v>1002</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>1012</v>
+        <v>1075</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>1013</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:1">
       <c r="A30" s="7" t="s">
-        <v>1014</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>1015</v>
+        <v>1078</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1016</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:8">
       <c r="A32" s="4" t="s">
-        <v>1017</v>
+        <v>1080</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>1018</v>
+        <v>1081</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -16486,10 +16784,10 @@
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>1019</v>
+        <v>1082</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>1020</v>
+        <v>1083</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -16500,10 +16798,10 @@
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:8">
       <c r="A34" s="4" t="s">
-        <v>1021</v>
+        <v>1084</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>1022</v>
+        <v>1085</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -16514,10 +16812,10 @@
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:8">
       <c r="A35" s="4" t="s">
-        <v>1023</v>
+        <v>1086</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>1024</v>
+        <v>1087</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -16528,10 +16826,10 @@
     </row>
     <row r="36" ht="14.25" customHeight="1" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>1025</v>
+        <v>1088</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>1026</v>
+        <v>1089</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -16542,10 +16840,10 @@
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>1027</v>
+        <v>1090</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>1028</v>
+        <v>1091</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
@@ -16556,10 +16854,10 @@
     </row>
     <row r="38" ht="14.25" customHeight="1" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>1029</v>
+        <v>1092</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>1030</v>
+        <v>1093</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -16570,10 +16868,10 @@
     </row>
     <row r="39" ht="14.25" customHeight="1" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>1031</v>
+        <v>1094</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>1032</v>
+        <v>1095</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -16584,10 +16882,10 @@
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>1033</v>
+        <v>1096</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>1034</v>
+        <v>1097</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -16598,30 +16896,30 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:1">
       <c r="A43" s="7" t="s">
-        <v>1035</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="44" ht="28.5" customHeight="1" spans="1:8">
       <c r="A44" s="3" t="s">
-        <v>1036</v>
+        <v>1099</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1037</v>
+        <v>1100</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1038</v>
+        <v>1101</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>910</v>
+        <v>973</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>1039</v>
+        <v>1102</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1040</v>
+        <v>1103</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>1041</v>
+        <v>1104</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>80</v>
@@ -16632,25 +16930,25 @@
         <v>1</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>1042</v>
+        <v>1105</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>1043</v>
+        <v>1106</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>1044</v>
+        <v>1107</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>87</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>1045</v>
+        <v>1108</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>1046</v>
+        <v>1109</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>1047</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:8">
@@ -16658,22 +16956,22 @@
         <v>2</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>1048</v>
+        <v>1111</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>1049</v>
+        <v>1112</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>1050</v>
+        <v>1113</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>293</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>1045</v>
+        <v>1108</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>1046</v>
+        <v>1109</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>86</v>
@@ -16684,25 +16982,25 @@
         <v>3</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>1051</v>
+        <v>1114</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>1043</v>
+        <v>1106</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>1052</v>
+        <v>1115</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>293</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>1045</v>
+        <v>1108</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>1046</v>
+        <v>1109</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>1053</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="48" ht="28.5" customHeight="1" spans="1:8">
@@ -16710,25 +17008,25 @@
         <v>104</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>1054</v>
+        <v>1117</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>1055</v>
+        <v>1118</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>1056</v>
+        <v>1119</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>218</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>1045</v>
+        <v>1108</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>1046</v>
+        <v>1109</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>1057</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="49" ht="42.75" customHeight="1" spans="1:8">
@@ -16736,25 +17034,25 @@
         <v>5</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>1058</v>
+        <v>1121</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>1059</v>
+        <v>1122</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>1060</v>
+        <v>1123</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>87</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>1061</v>
+        <v>1124</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>1046</v>
+        <v>1109</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>1062</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="50" ht="28.5" customHeight="1" spans="1:8">
@@ -16762,25 +17060,25 @@
         <v>6</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>1063</v>
+        <v>1126</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>1064</v>
+        <v>1127</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>1065</v>
+        <v>1128</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>87</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>1066</v>
+        <v>1129</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>1046</v>
+        <v>1109</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>1067</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="51" ht="28.5" customHeight="1" spans="1:8">
@@ -16788,30 +17086,30 @@
         <v>122</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>1068</v>
+        <v>1131</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>1069</v>
+        <v>1132</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>1070</v>
+        <v>1133</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>87</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>1071</v>
+        <v>1134</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>1046</v>
+        <v>1109</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>1072</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" spans="1:1">
       <c r="A54" s="10" t="s">
-        <v>1073</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>

--- a/deploy/菲律宾部署方案-v2.3-修订版.xlsx
+++ b/deploy/菲律宾部署方案-v2.3-修订版.xlsx
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>v2.3 + 2026-10-08 实况回改（容量口径修订 + 三项遗留决策定案；本次按《阿里云国际站菲律宾部署_详细操作指南-v2.0》2026-10-07 版的云侧实况逐格回改，依据见「修订要点」⑩）</t>
+          <t>v2.3 + 2026-10-08 实况回改 + 2026-10-12 与指南同步（容量口径修订 + 三项遗留决策定案；2026-10-12 按《阿里云国际站菲律宾部署_详细操作指南-v2.0》当日云侧实况逐格回改，依据见「修订要点」⑭）</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>① 工期 5 天 -&gt; 9 天（v2.0 -&gt; v2.1：56 项任务压缩进 8 天/16 时段经 600 次重排无可行解）；② 前置期 T-3 的 0 天改为真实前置 T-5；③ 补 PgBouncer/RDS 代理、cluster-autoscaler、备 region HPA 与 1.5× 接管容量；④ 补 staging/perf、运维访问面、Tair 预热、PITR 演练、连接数预算、Grafana、带宽与成本量化、上游配额盘点；⑤ 安全 3 改（ALB 源收敛为 WAF/DCDN 回源段、支付回调源 IP 白名单、SESSION_SECRET 双密钥轮换）；⑥ 修正证书部署时序、依赖倒挂、J48 负荷公式、门禁计数与编号映射、域名/数据盘/RTT 阈值口径；⑦【v2.2】工期 9 天 -&gt; 5 天：把每天 2 个半天时段改为 3 个工作段（新增 19:00–23:00 晚间加班段），15 时段 × 2 人 × 4 人时 = 120 人时产能，56 项任务在 15 段内重排完成、0 超载；⑧【v2.3】备 region 容量口径改为「本期仅承载 PH 备、不含泰国备」：节点数按 Pod requests 反算并留 ≥ 20% 系统组件余量 → 8 节点，节点池 2–12 改 2–8、配额 96 改 64 vCPU；统一「1.5×」基准为 maxReplicas × 1.5；⑨【2026-09-24 决策定案】三项遗留决策：保留 D4/D5 国庆窗口（不顺延）、T-5 = 2026-09-23 基准不动、本期不增加第 3 人。⑩【2026-10-08 按指南 v2.0（2026-10-07 版）实况回改】共回改 146 格：① 机型 g8i → g9i 首选（三机型列表，实开 g9ae）；② 主站 HPA 4–16 → 4–13、备站接管 16×1.5=24 → 13×1.5=19.5 → 20 副本；PDB minAvailable=3 → 70%；③ 新加坡配额实批按量 96 vCPU、节点池上限 12（v2.3 的 64 vCPU / 8 节点保留为容量下限）；④ RDS 规格 16C64G → pg.n4.2c.2m（2C8G，max_connections=800）；⑤ PgBouncer 自建 → RDS 内置托管池（F10 撤销）；⑥ 日志库 → 马尼拉 ClickHouse 企业版单 AZ（F9），不再购买新加坡 CK；⑦ 凭据链路 → 不使用 KMS/RRSA/ExternalSecret（2026-10-05 裁定），改手工 Opaque Secret；⑧ ECS 节点池付费方式定为按量 PostPaid（F13），成本按实况整机单价重算；⑨ 备站 Pod SQL_MAX_OPEN_CONNS=10（CM 100）；⑩ 伸缩组件实名 ack-goatscaler（非 cluster-autoscaler，观测入口 cm/kube-system/autoscaler-meta）；⑪ 任务 53 收敛口径由「30s × 节点数」改为「≤30 s（与节点数、跨 region 无关）」；⑫ 健康检查路径 /api/status 与全局限流冲突（应改 /readyz 并免限流）；⑬ 落地计划 AC 列按实况回填（21 张已完成 / 8 张部分交付 / 27 张未开始）。</t>
+          <t>① 工期 5 天 -&gt; 9 天（v2.0 -&gt; v2.1：56 项任务压缩进 8 天/16 时段经 600 次重排无可行解）；② 前置期 T-3 的 0 天改为真实前置 T-5；③ 补 PgBouncer/RDS 代理、cluster-autoscaler、备 region HPA 与 1.5× 接管容量；④ 补 staging/perf、运维访问面、Tair 预热、PITR 演练、连接数预算、Grafana、带宽与成本量化、上游配额盘点；⑤ 安全 3 改（ALB 源收敛为 WAF/DCDN 回源段、支付回调源 IP 白名单、SESSION_SECRET 双密钥轮换）；⑥ 修正证书部署时序、依赖倒挂、J48 负荷公式、门禁计数与编号映射、域名/数据盘/RTT 阈值口径；⑦【v2.2】工期 9 天 -&gt; 5 天：把每天 2 个半天时段改为 3 个工作段（新增 19:00–23:00 晚间加班段），15 时段 × 2 人 × 4 人时 = 120 人时产能，56 项任务在 15 段内重排完成、0 超载；⑧【v2.3】备 region 容量口径改为「本期仅承载 PH 备、不含泰国备」：节点数按 Pod requests 反算并留 ≥ 20% 系统组件余量 → 8 节点，节点池 2–12 改 2–8、配额 96 改 64 vCPU；统一「1.5×」基准为 maxReplicas × 1.5；⑨【2026-09-24 决策定案】三项遗留决策：保留 D4/D5 国庆窗口（不顺延）、T-5 = 2026-09-23 基准不动、本期不增加第 3 人。⑩【2026-10-08 按指南 v2.0（2026-10-07 版）实况回改】共回改 146 格：① 机型 g8i → g9i 首选（三机型列表，实开 g9ae）；② 主站 HPA 4–16 → 4–13、备站接管 16×1.5=24 → 13×1.5=19.5 → 20 副本；PDB minAvailable=3 → 70%；③ 新加坡配额实批按量 96 vCPU、节点池上限 12（v2.3 的 64 vCPU / 8 节点保留为容量下限）；④ RDS 规格 16C64G → pg.n4.2c.2m（2C8G，max_connections=800）；⑤ PgBouncer 自建 → RDS 内置托管池（F10 撤销）；⑥ 日志库 → 马尼拉 ClickHouse 企业版单 AZ（F9），不再购买新加坡 CK；⑦ 凭据链路 → 不使用 KMS/RRSA/ExternalSecret（2026-10-05 裁定），改手工 Opaque Secret；⑧ ECS 节点池付费方式定为按量 PostPaid（F13），成本按实况整机单价重算；⑨ 备站 Pod SQL_MAX_OPEN_CONNS=10（CM 100）；⑩ 伸缩组件实名 ack-goatscaler（非 cluster-autoscaler，观测入口 cm/kube-system/autoscaler-meta）；⑪ 任务 53 收敛口径由「30s × 节点数」改为「≤30 s（与节点数、跨 region 无关）」；⑫ 健康检查路径 /api/status 与全局限流冲突（应改 /readyz 并免限流）；⑬ 落地计划 AC 列按实况回填（21 张已完成 / 8 张部分交付 / 27 张未开始）。⑭【2026-10-12 与指南同步】：① G5 证书闭环——实购 Alibaba 品牌 DV 通配符 ali.dv.w（US$207，CertIdentifier=606823-ap-southeast-1，SAN *.likha.hk + likha.hk，链至 DigiCert Global Root G2），原 GlobalSign OV（US$997）已全额退款；⚠ 单张有效期仅 198 天（→ 2027-04-28）且 **AutoReissue=enable**（2026-10-12 经授权 UpdateInstance 开启，GetInstanceDetail 与 ListInstances 双路回读；写前 disable）⇒ 实例级托管续签已开，但 ALB 无 CAS 部署联动（实测 ListDeploymentJob、ListCloudResources(alb) 全空）⇒ 新证书仍须人工换绑两地 HTTPS 监听（2027-03-29 前，动作见 deploy/cert/targets.yaml R1–R4）；② 两地 ALB 443 监听 + 证书 + HTTP→HTTPS 301 已落地并验收（任务 19 V1–V5 全过、任务 25 闭合），requestTimeout 口径 180s → 600s（ALB 硬上限）；③ WAF 仍未接入（账号无实例；版本由「企业版」改为待裁定，2026-10-10 选型建议高级版）；④ GTM 仍挂起（任务 21，2026-09-30 裁定）；⑤ 备站跨区写马尼拉 CK 已实测在位（PUBLIC 端点 + sg_eip 白名单，2026-10-09 复核），原「待裁定」闭合；⑥ 任务 26 观测 4/4 闭环、任务 27 canary V1–V6 全过、任务 53 按更正判据通过；⑦ 镜像前缀按实测 EE 域名更正（B27）。⑮【2026-10-12 WAF 购买决策】：项目负责人裁定本次部署**不购买 WAF 3.0**（暂缓、非取消）——最低档高级版 3,880 元/月 ≈US$556 + 2,000 QPS + 日志服务单独起购，相对当前业务量过高，且实例只能控制台订阅（waf-openapi 无 CreateInstance、CLI 不能报价下单）。连锁更正：任务 20 整体挂起、V1–V4 从上线门禁移出；任务 47「ALB 入向不收敛」失去 WAF 缓解（443 直接暴露公网、无前置 L7 层，收敛与否重开为待裁定）；任务 40 证书部署对象只剩 ALB；任务 48 回调防线确定为两层（应用白名单 + 签名）；任务 52 成本表 WAF 行归零；M3 通过标准去掉 WAF；备站接管后同样无 L7 防护（任务 25 坑 2 转为知情接受风险）；CC 攻击的损失形态改为 HPA 按量扩容 + ALB LCU + 上游 token，故预算 80% 告警与异常突增巡检升为必须项。复评触发条件＝日请求量显著增长 / 出现真实攻击或 CC 事件。依据＝指南 §0.5 F15（2026-10-12 裁定）。</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B25" s="44" t="inlineStr">
         <is>
-          <t>www.likha.hk（全表统一；替代原 example-ph.com 示例）</t>
+          <t>www.likha.hk（全表统一；替代原 example-ph.com 示例）；备站公网入口 sg.likha.hk（2026-10-09 裁定新增，仅接管/直连，不进 GTM 池）</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>registry-vpc.ap-southeast-6.aliyuncs.com/newapi/new-api</t>
+          <t>acr-newapi-mnl-registry-vpc.ap-southeast-6.cr.aliyuncs.com/newapi-prod/new-api（2026-10-12 按指南 F8/§2 更正：ACR 企业版域名带实例名前缀；旧 registry-vpc.ap-southeast-6.aliyuncs.com/newapi/ 为个人版形态，命名空间 newapi 实测不存在）；⚠ 现网主镜像仓库实名 newapi-prod/newapi-master，本行 new-api 属任务 16 未回填的单仓口径待办</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="E13" s="38" t="inlineStr">
         <is>
-          <t>云解析 DNS（旗舰版）、GTM（旗舰版）、DCDN、WAF 3.0（企业版）、SSL 证书、堡垒机 / VPN（**KMS 凭据管家：2026-10-05 裁定不采购**）</t>
+          <t>云解析 DNS（旗舰版）、GTM（旗舰版）、DCDN、WAF 3.0（⏸ 2026-10-12 裁定**本轮不采购**，暂缓非取消；账号无实例，指南 F15）、SSL 证书、堡垒机 / VPN（**KMS 凭据管家：2026-10-05 裁定不采购**）</t>
         </is>
       </c>
       <c r="F13" s="38" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="K13" s="38" t="inlineStr">
         <is>
-          <t>WAF 需企业版；证书需在 D1 前完成签发</t>
+          <t>⏸ 2026-10-12 裁定（指南 F15）：**本次部署不购买 WAF 3.0**（暂缓）——最低档高级版 3,880 元/月 ≈US$556 + 2,000 QPS + 日志服务单独起购，相对当前业务量过高；实例本就只能控制台订阅（waf-openapi 无 CreateInstance、无报价条目）。复评触发＝日请求量增长 / 出现真实攻击或 CC 事件；复评时选型结论仍按 2026-10-10 文档（高级版够用、基础版不可用、日志服务单独起购）。证书 G5 已于 2026-10-12 闭环签发</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
-          <t>私钥**不落 KMS**（2026-10-05 裁定不使用 KMS/凭据管家）：证书私钥由运维手工保管；开启自动续期与 30 天到期告警</t>
+          <t>私钥**不落 KMS**（2026-10-05 裁定不使用 KMS/凭据管家）：证书私钥由运维手工保管；⚠ 2026-10-12 实况：单张有效期仅 198 天（→ 2027-04-28，CA/B 新规）；AutoReissue=enable（2026-10-12 经授权开启并双路回读）⇒ 实例级托管续签已开，但 ALB 无 CAS 部署联动（实测 ListDeploymentJob、ListCloudResources(alb) 全空）⇒ 新证书仍须人工换绑两地 HTTPS 监听（2027-03-29 前，动作见 deploy/cert/targets.yaml R1–R4）；30 天到期告警已在控制台配置（2026-10-12 负责人自配；⚠ CAS 无提醒类 API，故该项无回读证据、配置页截图待补）</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E21" s="38" t="inlineStr">
         <is>
-          <t>分别部署至马尼拉 ALB、新加坡 ALB、WAF、DCDN 域名</t>
+          <t>分别部署至马尼拉 ALB、新加坡 ALB（✅ 两地 443 监听已于 2026-10-12 落地并验收，CertIdentifier=606823-ap-southeast-1）、WAF、DCDN 域名（⏸ 2026-10-12 F15：WAF 本轮不采购、DCDN 未开通 ⇒ 本行部署对象只剩两地 ALB）</t>
         </is>
       </c>
       <c r="F21" s="38" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="K21" s="38" t="inlineStr">
         <is>
-          <t>到期前 30 天自动续期并回归验证</t>
+          <t>⚠ 2026-10-12 更正：AutoReissue=enable（2026-10-12 经授权开启，GetInstanceDetail/ListInstances 双路回读）⇒ 实例级托管续签已开，但 ALB 监听直接引用 CertIdentifier 绑定、无 CAS 部署联动 ⇒ 新证书签发后仍须人工换绑并回归验证（到期 2027-04-28，换绑动作 2027-03-29 前）</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="H9" s="38" t="inlineStr">
         <is>
-          <t>实况：**只有 HTTP:80 一个监听**（443 / 301 待 G5 证书签发）；idleTimeout=60s；requestTimeout=180s；TLS 1.2+1.3；健康检查 GET /api/status @20s（原 6s，2026-10-06 改）**与全局限流 360/180s per client IP 冲突 ⇒ 必须改 /readyz 并免限流（G8）**</t>
+          <t>实况（2026-10-12）：HTTP:80 + HTTPS:443 两监听（443 = lsn-hjl2cz2g9oqvee4eix，证书 606823-ap-southeast-1，tls_cipher_policy_1_2_strict_with_1_3）+ Ingress/new-api-http-redirect（order=1）做 HTTP→HTTPS 301；idleTimeout=60s；requestTimeout=600s（原口径 180s；600 为 ALB 硬上限）；TLS 1.2+1.3；健康检查 GET /api/status @20s（原 6s，2026-10-06 改）**与全局限流 360/180s per client IP 冲突 ⇒ 必须改 /readyz 并免限流（G8）**</t>
         </is>
       </c>
       <c r="I9" s="38" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="D10" s="36" t="inlineStr">
         <is>
-          <t>企业版</t>
+          <t>⏸ 2026-10-12 裁定（F15）：本轮**不采购**（暂缓，非取消）；依据＝指南 §0.5 F15（2026-10-12 裁定）。复评条件＝业务量增长 / 真实攻击或 CC 事件</t>
         </is>
       </c>
       <c r="E10" s="36" t="n">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="H10" s="36" t="inlineStr">
         <is>
-          <t>接入 www.likha.hk；CC 阈值对齐 GLOBAL_API_RATE_LIMIT；放行支付回调路径并限定回调源 IP 段</t>
+          <t>接入 www.likha.hk；CC 阈值对齐 GLOBAL_API_RATE_LIMIT；放行支付回调路径并限定回调源 IP 段 —— ⚠ 2026-10-10 复核：账号无 WAF 实例、任务 20 五步 0 完成；ALB 云原生接入实为 SDK 集成（非透明代理），443 不是前置、且不占「可接入域名数」；选型与判据更正见 deploy/docs/WAF接入_CC攻击分类与计费选型_2026-10-10.md；⚠ 2026-10-12（F15）：本行**整体不执行**——本轮不采购 WAF ⇒ CC 频控只剩应用侧 GLOBAL_API_RATE_LIMIT 360/180s（它只按客户端 IP 计数，正是任务 53 的 429 源头）、回调豁免与 waf-log 投递同时取消，入口层证据链改由 alb-access SLS（sls-newapi-mnl/alb_access）承担</t>
         </is>
       </c>
       <c r="I10" s="36" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="M17" s="38" t="inlineStr">
         <is>
-          <t>菲律宾唯一主库</t>
+          <t>菲律宾唯一主库；⚠ 2026-10-12 实查：PayType=Prepaid 且仅 1 个月，ExpireTime=2026-10-28T16:00:00Z（距当日 16 天），Create/Expire 之间无续费台账 ⇒ 到期前须续费或开自动续费，否则主库停机</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="M20" s="36" t="inlineStr">
         <is>
-          <t>生产建议升级集群版</t>
+          <t>生产建议升级集群版；⚠ 2026-10-12 实查：ChargeType=PrePaid 且仅 1 个月，EndTime=2026-10-28T16:00:00Z（与主库同日到期，无续费台账）</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="H31" s="38" t="inlineStr">
         <is>
-          <t>replicas=1；独立 Service 与 Ingress；canary-weight 5→20→50→100</t>
+          <t>replicas=1；独立 Service 与 Ingress；canary-weight 5→20→50→100 —— ✅ 2026-10-12 已下发，V1–V6 全过（权重 5 生效且可归零）</t>
         </is>
       </c>
       <c r="I31" s="38" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="H35" s="16" t="inlineStr">
         <is>
-          <t>证书部署至 ALB / WAF / DCDN；ALB 层启用 SNI 与域名校验</t>
+          <t>证书部署至 ALB / WAF / DCDN；ALB 层启用 SNI 与域名校验 —— ✅ 2026-10-12：证书 606823-ap-southeast-1 已部署至两地 ALB 443 并通过链校验/SNI（⏸ 2026-10-12 F15：WAF 本轮不采购、DCDN 未启用 ⇒ 本卡部署对象只剩 ALB）</t>
         </is>
       </c>
       <c r="I35" s="16" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>企业版</t>
+          <t>⏸ 2026-10-12 裁定（F15）：本轮**不采购**（与马尼拉同口径，暂缓）；备站接管后同样无 L7 防护，属知情接受风险（任务 25 坑 2）</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>接管时承接 api.example-ph.com 流量；规则与马尼拉保持一致</t>
+          <t>接管时承接 www.likha.hk 流量（备站另有公网入口 sg.likha.hk，2026-10-09 裁定新增，不进 GTM 池）；规则与马尼拉保持一致；⏸ 2026-10-12 F15：两地均不接 WAF ⇒ 接管后无「WAF 规则一致性」校验项，改为两地 ALB 监听/Ingress 规则 diff（任务 34）</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="M15" s="31" t="inlineStr">
         <is>
-          <t>原「备 region 本地日志库」口径已作废（F9）；跨区写 CK 目前只有 VPC 端点、无公网端点 ⇒ 备站跨区写 CK 待裁定</t>
+          <t>原「备 region 本地日志库」口径已作废（F9）；2026-10-09 复核更正：马尼拉 CK 已有 PUBLIC 端点（43.118.97.47）+ 白名单组 sg_eip 含新加坡 4 个 SNAT EIP，备站跨区写已实测通过（任务 29 执行记录 6；与「资源清单-马尼拉」H21 一致）⇒ 原「待裁定」闭合</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="H17" s="31" t="inlineStr">
         <is>
-          <t>alb 入向 80（443 待 G5）；app 入向 3000 仅来自 alb-sg；app 出向允许访问马尼拉 RDS **公网 6432（经托管池，2026-09-29 裁定② 乙路）**；跨区 TLS 用 verify-full + sslrootcert（Secret rds-ca-apse6 挂 /etc/ssl/rds）</t>
+          <t>alb 入向 80,443（443 已于 2026-10-12 落地并验收：lsn-iqn5i233mvv7eu4u6w + 证书 Associated）；app 入向 3000 仅来自 alb-sg；app 出向允许访问马尼拉 RDS **公网 6432（经托管池，2026-09-29 裁定② 乙路）**；跨区 TLS 用 verify-full + sslrootcert（Secret rds-ca-apse6 挂 /etc/ssl/rds）</t>
         </is>
       </c>
       <c r="I17" s="31" t="inlineStr">
@@ -8165,7 +8165,7 @@
     <row r="37" ht="14.25" customHeight="1" s="11">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>安全组规则（最小开放原则；入向禁止 0.0.0.0/0，仅放行 WAF / DCDN 回源段与对端 CIDR）</t>
+          <t>安全组规则（最小开放原则；对端 CIDR 收敛。**⚠ 2026-10-06 定稿例外：ALB 入向保持 0.0.0.0/0 :80,443 不收敛** —— WAF 3.0 走云原生 SDK 接入而非透明代理，未匹配 Host 由 Ingress 规则/catchall 兜底，直连 ALB 公网 IP 属已裁定接受项（任务 47）。⚠ 2026-10-12 F15：WAF 本轮不采购 ⇒ 该例外失去前置 L7 防护层，实际兜底只剩 alb-access 审计 + Ingress Host/catchall + 应用 360/180s 限流；是否改用 ALB ACL 收敛重开为待裁定（任务 47 追加登记 ⑥）</t>
         </is>
       </c>
     </row>
@@ -8448,12 +8448,12 @@
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>WAF 回源 IP 段（新加坡）</t>
+          <t>实况（2026-10-06 裁定，与马尼拉同口径）：保持 0.0.0.0/0 :80,443 不收敛；2026-10-12 两地 ALB 443 已落地；⚠ 2026-10-12 F15：任务 20 裁定不执行 ⇒ 不收敛再无 WAF 缓解（原括注「WAF 3.0 云原生 SDK 接入，待任务 20」作废），与主站同列待裁定</t>
         </is>
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>GTM 接管时的备 region 入口；与主站点一致，禁止 0.0.0.0/0</t>
+          <t>GTM 接管时的备 region 入口；与主站点同口径不收敛（2026-10-06 裁定；原「禁止 0.0.0.0/0」作废）</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
     <row r="65">
       <c r="A65" s="25" t="inlineStr">
         <is>
-          <t>说明：① 原 v2.0 中 sg-mnl-alb / sg-sg-alb 入向为 0.0.0.0/0，可被直连 ALB 公网 IP 绕过 WAF，本版已收敛为 WAF / DCDN 回源段；② 跨 VPC 对端无法以安全组表达，相关规则改为 CIDR /32，并由 RDS 公网白名单二次收敛；③ 上游出口保留 0.0.0.0/0 出向为必要放通，由目的侧白名单与出向限速约束。</t>
+          <t>说明：① 原 v2.0 中 sg-mnl-alb / sg-sg-alb 入向为 0.0.0.0/0，可被直连 ALB 公网 IP 绕过 WAF，该收敛方案于 2026-10-06 裁定作废：ALB 入向保持 0.0.0.0/0 :80,443 不收敛（WAF 3.0 = 云原生 SDK 接入，见任务 47 定稿与风险文档 §8）；② 跨 VPC 对端无法以安全组表达，相关规则改为 CIDR /32，并由 RDS 公网白名单二次收敛；③ 上游出口保留 0.0.0.0/0 出向为必要放通，由目的侧白名单与出向限速约束。</t>
         </is>
       </c>
     </row>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="AC4" s="16" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>部分交付（§0.7 G0：G1/G2/G3/G4/G5/G10/G12 已闭环，G5 于 2026-10-12 签发；G6/G7/G8/G11/G13 仍待闭环）</t>
         </is>
       </c>
       <c r="AD4" s="17">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="AC5" s="16" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>部分交付（G4 NS 已闭环、www.likha.hk 解析在用；ops.likha.hk 现网无记录，见指南 §2 域名表）</t>
         </is>
       </c>
       <c r="AD5" s="17">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="AC6" s="16" t="inlineStr">
         <is>
-          <t>未开始（卡 G5 证书签发）</t>
+          <t>已完成（2026-10-12 实测 4/4 交付，本卡闭合）：① 私钥+全链入 /root/.deploy_secrets/TLS_WILDCARD_{CRT,KEY}（-rw------- root root 6075/1675、leaf 在前、链 3 张、-modulus md5 两侧同为 df343b79775… ⇒ 配对 PASS，执行器 deploy/logs/tls_store_20261012.sh）；② notAfter=2027-04-28 ≥ 今+30 天、SAN 含 *.likha.hk 与 likha.hk、openssl verify OK、CAS CertificateStatus=issued（CertId=606823）；③ 到期告警：控制台由负责人自配（⚠ 无 API 可取证，证据=负责人确认，配置页截图仍欠），另经授权开实例级自动托管续签 UpdateInstance --AutoReissue enable，GetInstanceDetail 与 ListInstances 双路回读均为 enable（写前 disable）；④ 模板落地 deploy/cert/targets.yaml（含现场回读的 ALB/监听 ID）。★ 长期风险如实登记：AutoReissueCount 仍 0、ListTrusteeOrder NotFound、ListDeploymentJob 与 ListCloudResources(alb) 全空 ⇒ ALB 直接绑 CertIdentifier、无 CAS 部署联动 ⇒ 续签后须人工把新 CertId 换绑两地 HTTPS 监听（R1–R4 已写入 targets.yaml，2027-03-29 前执行）。⚠ 另：本轮调试用 bash -x 把私钥正文留在本机会话记录（无远端副本），负责人裁定按「接受」处置，2027-03 续签窗口自然换新；永久规则=处理私钥的脚本禁 -x。</t>
         </is>
       </c>
       <c r="AD6" s="17">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>创建双地域 ACR 企业版并打通 CI 镜像推送</t>
+          <t>创建马尼拉 ACR 企业版（单地域，F8 口径）并打通 CI 镜像推送</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
@@ -11035,7 +11035,7 @@
       <c r="AA19" s="17" t="n"/>
       <c r="AB19" s="16" t="inlineStr">
         <is>
-          <t>两站点均可从各自 VPC 域名拉取镜像</t>
+          <t>主站从马尼拉 VPC 域名拉通（-vpc 端点已关联，实测 5 s）；备站跨区走同一仓库公网域名、同 digest（F8 单地域口径，2026-10-06 两地实测同 SHA）</t>
         </is>
       </c>
       <c r="AC19" s="16" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="AC22" s="16" t="inlineStr">
         <is>
-          <t>部分交付（超时 / 301 / 443 / 证书链 待 G5）</t>
+          <t>已完成（2026-10-12 闭合，V1–V5 全过：443 监听 + 证书链 + TLS 策略 + idle 60 / req 600 + HTTP→HTTPS 301）</t>
         </is>
       </c>
       <c r="AD22" s="17">
@@ -11495,12 +11495,12 @@
       <c r="AA23" s="17" t="n"/>
       <c r="AB23" s="16" t="inlineStr">
         <is>
-          <t>攻击场景被拦截；回调路径放行且源 IP 受限</t>
+          <t>⏸ 2026-10-12 裁定（F15）：本判据不执行——不采购 WAF ⇒「攻击场景被拦截」无判据对象；回调防护改由任务 48 两层验收（应用源 IP 白名单 + 签名校验）</t>
         </is>
       </c>
       <c r="AC23" s="16" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>⏸ 本轮不实施（2026-10-12 裁定 F15：不购买 WAF，暂缓非取消；任务 20 整体挂起，V1–V4 从上线门禁移出；复评条件＝业务量增长 / 真实攻击或 CC 事件）</t>
         </is>
       </c>
       <c r="AD23" s="17">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="AC28" s="16" t="inlineStr">
         <is>
-          <t>部分交付</t>
+          <t>已完成（2026-10-12 闭合：443 lsn-iqn5i233mvv7eu4u6w + 证书 Associated + rule-443-1 Host；sg.likha.hk 502 已修，根因是 443 监听缺 Host 规则落到 fake-svc 默认动作）</t>
         </is>
       </c>
       <c r="AD28" s="17">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="AC29" s="16" t="inlineStr">
         <is>
-          <t>部分交付</t>
+          <t>已完成（2026-10-10 判定 4/4：SLS / ARMS Prometheus / Grafana 工作区 gra-newapi-sg / 云监控站点监控 likha-hk-newapi-status，可用率 100%）</t>
         </is>
       </c>
       <c r="AD29" s="17">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="AC30" s="16" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成（2026-10-12 已下发，V1–V6 全过；限定：5xx 阈值取 e5xx&gt;0 严于卡片口径、触发→推送链路未验属任务 32、alb_access 不含健康检查流量）</t>
         </is>
       </c>
       <c r="AD30" s="17">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="AC31" s="16" t="inlineStr">
         <is>
-          <t>部分交付（V4 会话互通阻塞于任务 25 的 SG ALB）</t>
+          <t>部分交付（V1–V3 ✅；V4 会话互通仍未实测——原「阻塞于任务 25 的 SG ALB」这一前提已随任务 25 于 2026-10-12 闭合而消失）</t>
         </is>
       </c>
       <c r="AD31" s="17">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="AC32" s="16" t="inlineStr">
         <is>
-          <t>未开始（Trade_Not_Support_Async_Pay，余额 0）</t>
+          <t>部分交付（2026-10-12：第 1 步新加坡 Tair r-gs5ltv3m4i3655besh 已实购并接线、备站 Redis 已启用；日志库按 F9 收口马尼拉 CK、跨区写已实测在位；原「余额 0 / Trade_Not_Support_Async_Pay」已解除）</t>
         </is>
       </c>
       <c r="AD32" s="17">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="AC43" s="16" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>部分交付（2026-10-12：证书已部署至两地 ALB 443，链校验与 SNI 通过；WAF 未接入、DCDN 未启用 ⇒ 按 F15（不采购）与未开通，本轮不做，判据收窄为仅 ALB；未闭合项改为「新证书须人工换绑两地 ALB HTTPS 监听（AutoReissue=enable 只保证签出新证，无 CAS 部署联动；2027-03-29 前执行 targets.yaml R1–R4）」）</t>
         </is>
       </c>
       <c r="AD43" s="17">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="AC46" s="16" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>部分交付（HPA 4–13 已在现网、指标 CPU 65，F12/F14 已裁定；单实例容量基线 C 未实测、/readyz 免限流待 G8）</t>
         </is>
       </c>
       <c r="AD46" s="17">
@@ -14600,12 +14600,12 @@
       <c r="AA50" s="17" t="n"/>
       <c r="AB50" s="16" t="inlineStr">
         <is>
-          <t>ALB 入向仅放行 WAF/DCDN 回源段，直连公网 IP 不可达</t>
+          <t>定稿更正（2026-10-06 裁定 A，任务 47）：ALB 入向保持 0.0.0.0/0 :80,443 不收敛（WAF 3.0 = 云原生 SDK 接入）；未匹配 Host 由 Ingress catchall/Host 规则兜底；直连 ALB 公网 IP 可达属已接受风险</t>
         </is>
       </c>
       <c r="AC50" s="16" t="inlineStr">
         <is>
-          <t>部分交付（SNI / 443 待 G5）</t>
+          <t>已完成（2026-10-12：两地 ALB 均有 443 监听，SNI 与 Host 兜底规则已落地；「源收敛」分支按 2026-10-06 定稿改为不收敛）</t>
         </is>
       </c>
       <c r="AD50" s="17">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="AC56" s="16" t="inlineStr">
         <is>
-          <t>部分交付（渠道 / 改价端到端未执行）</t>
+          <t>已完成（2026-10-06 实测通过；按更正判据，渠道热更新/改价端到端不属本卡）</t>
         </is>
       </c>
       <c r="AD56" s="17">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>部分达成（2026-10-12：网络底座 / ACK / RDS / Tair / CK / OSS / ACR / 备份策略 / NS 复核均已完成；G0 未整体闭环，「双地域 ACR」按 F8 改单地域）</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>部分达成（2026-10-12：节点池 4 台跨 2 AZ、手工 Opaque Secret、master 迁移幂等、马尼拉 ALB+健康检查、托管 PgBouncer、运维访问面均已完成）</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -16677,7 +16677,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>stable 4 副本跨 AZ Ready（PDB 70% + HPA 4–13 + Pod 反亲和）、canary Deployment 就绪、PH 备 Deployment/Service 就绪（⚠ 2026-10-06 实况：V4 会话互通阻塞于 SG ALB ⇒ 记为**部分交付**）、新加坡 ACK 集群与节点池创建完成、GTM 实例/地址池/健康探测生效（先只挂马尼拉）、安全组与数据库白名单逐条核对通过、staging/perf 环境跑通最小三数据库冒烟</t>
+          <t>stable 4 副本跨 AZ Ready（PDB 70% + HPA 4–13 + Pod 反亲和）、canary Deployment 就绪（✅ 2026-10-12 V1–V6 全过）、PH 备 Deployment/Service 就绪（⚠ 实况：任务 25 的 SG ALB 已于 2026-10-12 闭合，V4 会话互通仍未实测 ⇒ 仍记**部分交付**）、新加坡 ACK 集群与节点池创建完成、GTM 实例/地址池/健康探测生效（先只挂马尼拉；⚠ 任务 21 2026-09-30 裁定挂起，仍未创建）、安全组与数据库白名单逐条核对通过、staging/perf 环境跑通最小三数据库冒烟</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>部分达成（2026-10-12：stable 副本/PDB/HPA、canary V1–V6、新加坡 ACK 与 ALB（含 443+TLS）、安全组与白名单核对已完成；GTM 仍挂起、任务 28 V4 未实测、staging/perf 未建）</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>WAF 3.0 接入 + CC 策略生效、灰度发布演练（5→20→50→100 与回滚）通过、备 region 公网读写马尼拉主库成功（连接 RTT ≤ 70 ms）、备 region 接管演练与主库切换演练通过、容量压测达标（并发 SSE 1500 / 管理面 800 QPS）、**ack-goatscaler 配置就绪（扩节点动作未实测）**、新加坡 ALB 就绪、SLS/ARMS/Grafana/站点拨测可见、上线前安全核查无高危项、备 region 链路拨测与告警生效</t>
+          <t>WAF 3.0 接入 + CC 策略生效（⏸ 2026-10-12 F15：本轮不采购 WAF ⇒ 该项从 M3 通过标准移除，入口层无 L7 防护为知情接受缺口）、灰度发布演练（5→20→50→100 与回滚）通过、备 region 公网读写马尼拉主库成功（连接 RTT ≤ 70 ms）、备 region 接管演练与主库切换演练通过、容量压测达标（并发 SSE 1500 / 管理面 800 QPS）、**ack-goatscaler 配置就绪（扩节点动作未实测）**、新加坡 ALB 就绪、SLS/ARMS/Grafana/站点拨测可见、上线前安全核查无高危项、备 region 链路拨测与告警生效</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>未开始（⏸ 2026-10-12 F15：WAF 本轮不采购，该项已从 M3 判据移除；灰度/接管/主库切换演练与压测均未执行；观测面任务 26 已于 2026-10-10 4/4 闭环、新加坡 ALB 已就绪）</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">

--- a/deploy/菲律宾部署方案-v2.3-修订版.xlsx
+++ b/deploy/菲律宾部署方案-v2.3-修订版.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>① 工期 5 天 -&gt; 9 天（v2.0 -&gt; v2.1：56 项任务压缩进 8 天/16 时段经 600 次重排无可行解）；② 前置期 T-3 的 0 天改为真实前置 T-5；③ 补 PgBouncer/RDS 代理、cluster-autoscaler、备 region HPA 与 1.5× 接管容量；④ 补 staging/perf、运维访问面、Tair 预热、PITR 演练、连接数预算、Grafana、带宽与成本量化、上游配额盘点；⑤ 安全 3 改（ALB 源收敛为 WAF/DCDN 回源段、支付回调源 IP 白名单、SESSION_SECRET 双密钥轮换）；⑥ 修正证书部署时序、依赖倒挂、J48 负荷公式、门禁计数与编号映射、域名/数据盘/RTT 阈值口径；⑦【v2.2】工期 9 天 -&gt; 5 天：把每天 2 个半天时段改为 3 个工作段（新增 19:00–23:00 晚间加班段），15 时段 × 2 人 × 4 人时 = 120 人时产能，56 项任务在 15 段内重排完成、0 超载；⑧【v2.3】备 region 容量口径改为「本期仅承载 PH 备、不含泰国备」：节点数按 Pod requests 反算并留 ≥ 20% 系统组件余量 → 8 节点，节点池 2–12 改 2–8、配额 96 改 64 vCPU；统一「1.5×」基准为 maxReplicas × 1.5；⑨【2026-09-24 决策定案】三项遗留决策：保留 D4/D5 国庆窗口（不顺延）、T-5 = 2026-09-23 基准不动、本期不增加第 3 人。⑩【2026-10-08 按指南 v2.0（2026-10-07 版）实况回改】共回改 146 格：① 机型 g8i → g9i 首选（三机型列表，实开 g9ae）；② 主站 HPA 4–16 → 4–13、备站接管 16×1.5=24 → 13×1.5=19.5 → 20 副本；PDB minAvailable=3 → 70%；③ 新加坡配额实批按量 96 vCPU、节点池上限 12（v2.3 的 64 vCPU / 8 节点保留为容量下限）；④ RDS 规格 16C64G → pg.n4.2c.2m（2C8G，max_connections=800）；⑤ PgBouncer 自建 → RDS 内置托管池（F10 撤销）；⑥ 日志库 → 马尼拉 ClickHouse 企业版单 AZ（F9），不再购买新加坡 CK；⑦ 凭据链路 → 不使用 KMS/RRSA/ExternalSecret（2026-10-05 裁定），改手工 Opaque Secret；⑧ ECS 节点池付费方式定为按量 PostPaid（F13），成本按实况整机单价重算；⑨ 备站 Pod SQL_MAX_OPEN_CONNS=10（CM 100）；⑩ 伸缩组件实名 ack-goatscaler（非 cluster-autoscaler，观测入口 cm/kube-system/autoscaler-meta）；⑪ 任务 53 收敛口径由「30s × 节点数」改为「≤30 s（与节点数、跨 region 无关）」；⑫ 健康检查路径 /api/status 与全局限流冲突（应改 /readyz 并免限流）；⑬ 落地计划 AC 列按实况回填（21 张已完成 / 8 张部分交付 / 27 张未开始）。⑭【2026-10-12 与指南同步】：① G5 证书闭环——实购 Alibaba 品牌 DV 通配符 ali.dv.w（US$207，CertIdentifier=606823-ap-southeast-1，SAN *.likha.hk + likha.hk，链至 DigiCert Global Root G2），原 GlobalSign OV（US$997）已全额退款；⚠ 单张有效期仅 198 天（→ 2027-04-28）且 **AutoReissue=enable**（2026-10-12 经授权 UpdateInstance 开启，GetInstanceDetail 与 ListInstances 双路回读；写前 disable）⇒ 实例级托管续签已开，但 ALB 无 CAS 部署联动（实测 ListDeploymentJob、ListCloudResources(alb) 全空）⇒ 新证书仍须人工换绑两地 HTTPS 监听（2027-03-29 前，动作见 deploy/cert/targets.yaml R1–R4）；② 两地 ALB 443 监听 + 证书 + HTTP→HTTPS 301 已落地并验收（任务 19 V1–V5 全过、任务 25 闭合），requestTimeout 口径 180s → 600s（ALB 硬上限）；③ WAF 仍未接入（账号无实例；版本由「企业版」改为待裁定，2026-10-10 选型建议高级版）；④ GTM 仍挂起（任务 21，2026-09-30 裁定）；⑤ 备站跨区写马尼拉 CK 已实测在位（PUBLIC 端点 + sg_eip 白名单，2026-10-09 复核），原「待裁定」闭合；⑥ 任务 26 观测 4/4 闭环、任务 27 canary V1–V6 全过、任务 53 按更正判据通过；⑦ 镜像前缀按实测 EE 域名更正（B27）。⑮【2026-10-12 WAF 购买决策】：项目负责人裁定本次部署**不购买 WAF 3.0**（暂缓、非取消）——最低档高级版 3,880 元/月 ≈US$556 + 2,000 QPS + 日志服务单独起购，相对当前业务量过高，且实例只能控制台订阅（waf-openapi 无 CreateInstance、CLI 不能报价下单）。连锁更正：任务 20 整体挂起、V1–V4 从上线门禁移出；任务 47「ALB 入向不收敛」失去 WAF 缓解（443 直接暴露公网、无前置 L7 层，收敛与否重开为待裁定）；任务 40 证书部署对象只剩 ALB；任务 48 回调防线确定为两层（应用白名单 + 签名）；任务 52 成本表 WAF 行归零；M3 通过标准去掉 WAF；备站接管后同样无 L7 防护（任务 25 坑 2 转为知情接受风险）；CC 攻击的损失形态改为 HPA 按量扩容 + ALB LCU + 上游 token，故预算 80% 告警与异常突增巡检升为必须项。复评触发条件＝日请求量显著增长 / 出现真实攻击或 CC 事件。依据＝指南 §0.5 F15（2026-10-12 裁定）。</t>
+          <t>① 工期 5 天 -&gt; 9 天（v2.0 -&gt; v2.1：56 项任务压缩进 8 天/16 时段经 600 次重排无可行解）；② 前置期 T-3 的 0 天改为真实前置 T-5；③ 补 PgBouncer/RDS 代理、cluster-autoscaler、备 region HPA 与 1.5× 接管容量；④ 补 staging/perf、运维访问面、Tair 预热、PITR 演练、连接数预算、Grafana、带宽与成本量化、上游配额盘点；⑤ 安全 3 改（ALB 源收敛为 WAF/DCDN 回源段、支付回调源 IP 白名单、SESSION_SECRET 双密钥轮换）；⑥ 修正证书部署时序、依赖倒挂、J48 负荷公式、门禁计数与编号映射、域名/数据盘/RTT 阈值口径；⑦【v2.2】工期 9 天 -&gt; 5 天：把每天 2 个半天时段改为 3 个工作段（新增 19:00–23:00 晚间加班段），15 时段 × 2 人 × 4 人时 = 120 人时产能，56 项任务在 15 段内重排完成、0 超载；⑧【v2.3】备 region 容量口径改为「本期仅承载 PH 备、不含泰国备」：节点数按 Pod requests 反算并留 ≥ 20% 系统组件余量 → 8 节点，节点池 2–12 改 2–8、配额 96 改 64 vCPU；统一「1.5×」基准为 maxReplicas × 1.5；⑨【2026-09-24 决策定案】三项遗留决策：保留 D4/D5 国庆窗口（不顺延）、T-5 = 2026-09-23 基准不动、本期不增加第 3 人。⑩【2026-10-08 按指南 v2.0（2026-10-07 版）实况回改】共回改 146 格：① 机型 g8i → g9i 首选（三机型列表，实开 g9ae）；② 主站 HPA 4–16 → 4–13、备站接管 16×1.5=24 → 13×1.5=19.5 → 20 副本；PDB minAvailable=3 → 70%；③ 新加坡配额实批按量 96 vCPU、节点池上限 12（v2.3 的 64 vCPU / 8 节点保留为容量下限）；④ RDS 规格 16C64G → pg.n4.2c.2m（2C8G，max_connections=800）；⑤ PgBouncer 自建 → RDS 内置托管池（F10 撤销）；⑥ 日志库 → 马尼拉 ClickHouse 企业版单 AZ（F9），不再购买新加坡 CK；⑦ 凭据链路 → 不使用 KMS/RRSA/ExternalSecret（2026-10-05 裁定），改手工 Opaque Secret；⑧ ECS 节点池付费方式定为按量 PostPaid（F13），成本按实况整机单价重算；⑨ 备站 Pod SQL_MAX_OPEN_CONNS=10（CM 100）；⑩ 伸缩组件实名 ack-goatscaler（非 cluster-autoscaler，观测入口 cm/kube-system/autoscaler-meta）；⑪ 任务 53 收敛口径由「30s × 节点数」改为「≤30 s（与节点数、跨 region 无关）」；⑫ 健康检查路径 /api/status 与全局限流冲突（应改 /readyz 并免限流）；⑬ 落地计划 AC 列按实况回填（21 张已完成 / 8 张部分交付 / 27 张未开始）。⑭【2026-10-12 与指南同步】：① G5 证书闭环——实购 Alibaba 品牌 DV 通配符 ali.dv.w（US$207，CertIdentifier=606823-ap-southeast-1，SAN *.likha.hk + likha.hk，链至 DigiCert Global Root G2），原 GlobalSign OV（US$997）已全额退款；⚠ 单张有效期仅 198 天（→ 2027-04-28）且 **AutoReissue=enable**（2026-10-12 经授权 UpdateInstance 开启，GetInstanceDetail 与 ListInstances 双路回读；写前 disable）⇒ 实例级托管续签已开，但不代表 443 自动续上：监听只认 AlbConfig 钉死的 CertificateId（ACK 原文「Listener 不会使用自动发现证书，优先使用 AlbConfig 指定的证书」），且 ALB 是 ServiceManagedResource（直调 OpenAPI 换绑实测 3/3 被拒）⇒ 新证签发后须改 AlbConfig 再 apply（2027-03-29 前，deploy/cert/targets.yaml R1–R4；免人工的两条改法见指南任务 3 卡 ★ 段）；② 两地 ALB 443 监听 + 证书 + HTTP→HTTPS 301 已落地并验收（任务 19 V1–V5 全过、任务 25 闭合），requestTimeout 口径 180s → 600s（ALB 硬上限）；③ WAF 仍未接入（账号无实例；版本由「企业版」改为待裁定，2026-10-10 选型建议高级版）；④ GTM 仍挂起（任务 21，2026-09-30 裁定）；⑤ 备站跨区写马尼拉 CK 已实测在位（PUBLIC 端点 + sg_eip 白名单，2026-10-09 复核），原「待裁定」闭合；⑥ 任务 26 观测 4/4 闭环、任务 27 canary V1–V6 全过、任务 53 按更正判据通过；⑦ 镜像前缀按实测 EE 域名更正（B27）。⑮【2026-10-12 WAF 购买决策】：项目负责人裁定本次部署**不购买 WAF 3.0**（暂缓、非取消）——最低档高级版 3,880 元/月 ≈US$556 + 2,000 QPS + 日志服务单独起购，相对当前业务量过高，且实例只能控制台订阅（waf-openapi 无 CreateInstance、CLI 不能报价下单）。连锁更正：任务 20 整体挂起、V1–V4 从上线门禁移出；任务 47「ALB 入向不收敛」失去 WAF 缓解（443 直接暴露公网、无前置 L7 层，收敛与否重开为待裁定）；任务 40 证书部署对象只剩 ALB；任务 48 回调防线确定为两层（应用白名单 + 签名）；任务 52 成本表 WAF 行归零；M3 通过标准去掉 WAF；备站接管后同样无 L7 防护（任务 25 坑 2 转为知情接受风险）；CC 攻击的损失形态改为 HPA 按量扩容 + ALB LCU + 上游 token，故预算 80% 告警与异常突增巡检升为必须项。复评触发条件＝日请求量显著增长 / 出现真实攻击或 CC 事件。依据＝指南 §0.5 F15（2026-10-12 裁定）。</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
-          <t>私钥**不落 KMS**（2026-10-05 裁定不使用 KMS/凭据管家）：证书私钥由运维手工保管；⚠ 2026-10-12 实况：单张有效期仅 198 天（→ 2027-04-28，CA/B 新规）；AutoReissue=enable（2026-10-12 经授权开启并双路回读）⇒ 实例级托管续签已开，但 ALB 无 CAS 部署联动（实测 ListDeploymentJob、ListCloudResources(alb) 全空）⇒ 新证书仍须人工换绑两地 HTTPS 监听（2027-03-29 前，动作见 deploy/cert/targets.yaml R1–R4）；30 天到期告警已在控制台配置（2026-10-12 负责人自配；⚠ CAS 无提醒类 API，故该项无回读证据、配置页截图待补）</t>
+          <t>私钥**不落 KMS**（2026-10-05 裁定不使用 KMS/凭据管家）：证书私钥由运维手工保管；⚠ 2026-10-12 实况：单张有效期仅 198 天（→ 2027-04-28，CA/B 新规）；AutoReissue=enable（2026-10-12 经授权开启并双路回读）⇒ 实例级托管续签已开，但不代表 443 自动续上：监听只认 AlbConfig 钉死的 CertificateId（ACK 原文「Listener 不会使用自动发现证书，优先使用 AlbConfig 指定的证书」），且 ALB 是 ServiceManagedResource（直调 OpenAPI 换绑实测 3/3 被拒）⇒ 新证签发后须改 AlbConfig 再 apply（2027-03-29 前，deploy/cert/targets.yaml R1–R4；免人工的两条改法见指南任务 3 卡 ★ 段）；30 天到期告警已在控制台配置（2026-10-12 负责人自配；⚠ CAS 无提醒类 API，故该项无回读证据、配置页截图待补）</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="K21" s="38" t="inlineStr">
         <is>
-          <t>⚠ 2026-10-12 更正：AutoReissue=enable（2026-10-12 经授权开启，GetInstanceDetail/ListInstances 双路回读）⇒ 实例级托管续签已开，但 ALB 监听直接引用 CertIdentifier 绑定、无 CAS 部署联动 ⇒ 新证书签发后仍须人工换绑并回归验证（到期 2027-04-28，换绑动作 2027-03-29 前）</t>
+          <t>⚠ 2026-10-12 更正：AutoReissue=enable（2026-10-12 经授权开启，GetInstanceDetail/ListInstances 双路回读）⇒ 实例级托管续签已开，但监听只认 AlbConfig 钉死的 CertificateId（且 ALB 为 ServiceManagedResource，直调 OpenAPI 换绑被拒）⇒ 新证书签发后须改 AlbConfig 再 apply 并回归验证（到期 2027-04-28，动作 2027-03-29 前）</t>
         </is>
       </c>
     </row>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="AC6" s="16" t="inlineStr">
         <is>
-          <t>已完成（2026-10-12 实测 4/4 交付，本卡闭合）：① 私钥+全链入 /root/.deploy_secrets/TLS_WILDCARD_{CRT,KEY}（-rw------- root root 6075/1675、leaf 在前、链 3 张、-modulus md5 两侧同为 df343b79775… ⇒ 配对 PASS，执行器 deploy/logs/tls_store_20261012.sh）；② notAfter=2027-04-28 ≥ 今+30 天、SAN 含 *.likha.hk 与 likha.hk、openssl verify OK、CAS CertificateStatus=issued（CertId=606823）；③ 到期告警：控制台由负责人自配（⚠ 无 API 可取证，证据=负责人确认，配置页截图仍欠），另经授权开实例级自动托管续签 UpdateInstance --AutoReissue enable，GetInstanceDetail 与 ListInstances 双路回读均为 enable（写前 disable）；④ 模板落地 deploy/cert/targets.yaml（含现场回读的 ALB/监听 ID）。★ 长期风险如实登记：AutoReissueCount 仍 0、ListTrusteeOrder NotFound、ListDeploymentJob 与 ListCloudResources(alb) 全空 ⇒ ALB 直接绑 CertIdentifier、无 CAS 部署联动 ⇒ 续签后须人工把新 CertId 换绑两地 HTTPS 监听（R1–R4 已写入 targets.yaml，2027-03-29 前执行）。⚠ 另：本轮调试用 bash -x 把私钥正文留在本机会话记录（无远端副本），负责人裁定按「接受」处置，2027-03 续签窗口自然换新；永久规则=处理私钥的脚本禁 -x。</t>
+          <t>已完成（2026-10-12 实测 4/4 交付，本卡闭合）：① 私钥+全链入 /root/.deploy_secrets/TLS_WILDCARD_{CRT,KEY}（-rw------- root root 6075/1675、leaf 在前、链 3 张、-modulus md5 两侧同为 df343b79775… ⇒ 配对 PASS，执行器 deploy/logs/tls_store_20261012.sh）；② notAfter=2027-04-28 ≥ 今+30 天、SAN 含 *.likha.hk 与 likha.hk、openssl verify OK、CAS CertificateStatus=issued（CertId=606823）；③ 到期告警：控制台由负责人自配（⚠ 无 API 可取证，证据=负责人确认，配置页截图仍欠），另经授权开实例级自动托管续签 UpdateInstance --AutoReissue enable，GetInstanceDetail 与 ListInstances 双路回读均为 enable（写前 disable）；④ 模板落地 deploy/cert/targets.yaml（含现场回读的 ALB/监听 ID）。★ 长期风险如实登记（2026-10-12 二次取证订正）：AutoReissueCount 仍 0、ListTrusteeOrder NotFound；早前据 ListCloudResources --CloudName alb 的 Total=0 判「CAS 无部署联动」是**参数用错的假阴性**（--CloudName 是云厂商，ALB 属 --CloudProduct；正确调用实测到两地监听已在 CAS 登记 Id=37274711/37274712，但那是资源可见性、不是"托管会自动写入"）。真实结论由控制面语义决定：监听只认 AlbConfig 钉死的 CertificateId（ACK 原文「Listener 不会使用自动发现证书，优先使用 AlbConfig 指定的证书」；两地实测各只绑 1 张、无多证书兜底），而 ALB 是 ServiceManagedResource（直调 UpdateListenerAttribute 实测 3/3 被拒）⇒ 换绑的唯一通道是**改 AlbConfig 再 apply**（R1–R4 已按此订正，2027-03-29 前执行）。免人工改法（双证共存 / Secret 自动触发）与两条未证风险见指南任务 3 卡 ★ 段。⚠ 另：本轮调试用 bash -x 把私钥正文留在本机会话记录（无远端副本），负责人裁定按「接受」处置，2027-03 续签窗口自然换新；永久规则=处理私钥的脚本禁 -x。</t>
         </is>
       </c>
       <c r="AD6" s="17">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="AC43" s="16" t="inlineStr">
         <is>
-          <t>部分交付（2026-10-12：证书已部署至两地 ALB 443，链校验与 SNI 通过；WAF 未接入、DCDN 未启用 ⇒ 按 F15（不采购）与未开通，本轮不做，判据收窄为仅 ALB；未闭合项改为「新证书须人工换绑两地 ALB HTTPS 监听（AutoReissue=enable 只保证签出新证，无 CAS 部署联动；2027-03-29 前执行 targets.yaml R1–R4）」）</t>
+          <t>部分交付（2026-10-12：证书已部署至两地 ALB 443，链校验与 SNI 通过；WAF 未接入、DCDN 未启用 ⇒ 按 F15（不采购）与未开通，本轮不做，判据收窄为仅 ALB；未闭合项改为「新证书须改 AlbConfig 再 apply 才会换绑（AutoReissue=enable 只保证 CAS 签出新证；ALB 为 ServiceManagedResource，直调 OpenAPI 被拒；2027-03-29 前执行 targets.yaml R1–R4）」）</t>
         </is>
       </c>
       <c r="AD43" s="17">

--- a/deploy/菲律宾部署方案-v2.3-修订版.xlsx
+++ b/deploy/菲律宾部署方案-v2.3-修订版.xlsx
@@ -15630,7 +15630,11 @@
         <f>IF(AND($G59&lt;=15,$H59&gt;=15),"■■","")</f>
         <v/>
       </c>
-      <c r="Y59" s="17" t="n"/>
+      <c r="Y59" s="17" t="inlineStr">
+        <is>
+          <t>⏸ 2026-10-13 负责人裁定：本卡挂起 · 按需再做（8 个固定 EIP 已于 Day1 任务 6/12 建成并提交上游，台账留存备用；重启触发条件＝① Day4 正式发布前确定使用的渠道中存在需上游 IP 白名单者（企业专属 / Azure OpenAI / 自建上游）、② 任一渠道稳定 403 或间歇失败且排除 SNAT/EIP 侧、③ 上游主动要求提交和回执；详见指南任务 56 卡）</t>
+        </is>
+      </c>
       <c r="Z59" s="17" t="n"/>
       <c r="AA59" s="17" t="n"/>
       <c r="AB59" s="16" t="inlineStr">
@@ -15640,7 +15644,7 @@
       </c>
       <c r="AC59" s="16" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>⏸ 挂起 · 按需再做（2026-10-13 裁定：暂不执行，不进执行队列，不阻塞 M3）</t>
         </is>
       </c>
       <c r="AD59" s="17">

--- a/deploy/菲律宾部署方案-v2.3-修订版.xlsx
+++ b/deploy/菲律宾部署方案-v2.3-修订版.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>① 工期 5 天 -&gt; 9 天（v2.0 -&gt; v2.1：56 项任务压缩进 8 天/16 时段经 600 次重排无可行解）；② 前置期 T-3 的 0 天改为真实前置 T-5；③ 补 PgBouncer/RDS 代理、cluster-autoscaler、备 region HPA 与 1.5× 接管容量；④ 补 staging/perf、运维访问面、Tair 预热、PITR 演练、连接数预算、Grafana、带宽与成本量化、上游配额盘点；⑤ 安全 3 改（ALB 源收敛为 WAF/DCDN 回源段、支付回调源 IP 白名单、SESSION_SECRET 双密钥轮换）；⑥ 修正证书部署时序、依赖倒挂、J48 负荷公式、门禁计数与编号映射、域名/数据盘/RTT 阈值口径；⑦【v2.2】工期 9 天 -&gt; 5 天：把每天 2 个半天时段改为 3 个工作段（新增 19:00–23:00 晚间加班段），15 时段 × 2 人 × 4 人时 = 120 人时产能，56 项任务在 15 段内重排完成、0 超载；⑧【v2.3】备 region 容量口径改为「本期仅承载 PH 备、不含泰国备」：节点数按 Pod requests 反算并留 ≥ 20% 系统组件余量 → 8 节点，节点池 2–12 改 2–8、配额 96 改 64 vCPU；统一「1.5×」基准为 maxReplicas × 1.5；⑨【2026-09-24 决策定案】三项遗留决策：保留 D4/D5 国庆窗口（不顺延）、T-5 = 2026-09-23 基准不动、本期不增加第 3 人。⑩【2026-10-08 按指南 v2.0（2026-10-07 版）实况回改】共回改 146 格：① 机型 g8i → g9i 首选（三机型列表，实开 g9ae）；② 主站 HPA 4–16 → 4–13、备站接管 16×1.5=24 → 13×1.5=19.5 → 20 副本；PDB minAvailable=3 → 70%；③ 新加坡配额实批按量 96 vCPU、节点池上限 12（v2.3 的 64 vCPU / 8 节点保留为容量下限）；④ RDS 规格 16C64G → pg.n4.2c.2m（2C8G，max_connections=800）；⑤ PgBouncer 自建 → RDS 内置托管池（F10 撤销）；⑥ 日志库 → 马尼拉 ClickHouse 企业版单 AZ（F9），不再购买新加坡 CK；⑦ 凭据链路 → 不使用 KMS/RRSA/ExternalSecret（2026-10-05 裁定），改手工 Opaque Secret；⑧ ECS 节点池付费方式定为按量 PostPaid（F13），成本按实况整机单价重算；⑨ 备站 Pod SQL_MAX_OPEN_CONNS=10（CM 100）；⑩ 伸缩组件实名 ack-goatscaler（非 cluster-autoscaler，观测入口 cm/kube-system/autoscaler-meta）；⑪ 任务 53 收敛口径由「30s × 节点数」改为「≤30 s（与节点数、跨 region 无关）」；⑫ 健康检查路径 /api/status 与全局限流冲突（应改 /readyz 并免限流）；⑬ 落地计划 AC 列按实况回填（21 张已完成 / 8 张部分交付 / 27 张未开始）。⑭【2026-10-12 与指南同步】：① G5 证书闭环——实购 Alibaba 品牌 DV 通配符 ali.dv.w（US$207，CertIdentifier=606823-ap-southeast-1，SAN *.likha.hk + likha.hk，链至 DigiCert Global Root G2），原 GlobalSign OV（US$997）已全额退款；⚠ 单张有效期仅 198 天（→ 2027-04-28）且 **AutoReissue=enable**（2026-10-12 经授权 UpdateInstance 开启，GetInstanceDetail 与 ListInstances 双路回读；写前 disable）⇒ 实例级托管续签已开，但不代表 443 自动续上：监听只认 AlbConfig 钉死的 CertificateId（ACK 原文「Listener 不会使用自动发现证书，优先使用 AlbConfig 指定的证书」），且 ALB 是 ServiceManagedResource（直调 OpenAPI 换绑实测 3/3 被拒）⇒ 新证签发后须改 AlbConfig 再 apply（2027-03-29 前，deploy/cert/targets.yaml R1–R4；免人工的两条改法见指南任务 3 卡 ★ 段）；② 两地 ALB 443 监听 + 证书 + HTTP→HTTPS 301 已落地并验收（任务 19 V1–V5 全过、任务 25 闭合），requestTimeout 口径 180s → 600s（ALB 硬上限）；③ WAF 仍未接入（账号无实例；版本由「企业版」改为待裁定，2026-10-10 选型建议高级版）；④ GTM 仍挂起（任务 21，2026-09-30 裁定）；⑤ 备站跨区写马尼拉 CK 已实测在位（PUBLIC 端点 + sg_eip 白名单，2026-10-09 复核），原「待裁定」闭合；⑥ 任务 26 观测 4/4 闭环、任务 27 canary V1–V6 全过、任务 53 按更正判据通过；⑦ 镜像前缀按实测 EE 域名更正（B27）。⑮【2026-10-12 WAF 购买决策】：项目负责人裁定本次部署**不购买 WAF 3.0**（暂缓、非取消）——最低档高级版 3,880 元/月 ≈US$556 + 2,000 QPS + 日志服务单独起购，相对当前业务量过高，且实例只能控制台订阅（waf-openapi 无 CreateInstance、CLI 不能报价下单）。连锁更正：任务 20 整体挂起、V1–V4 从上线门禁移出；任务 47「ALB 入向不收敛」失去 WAF 缓解（443 直接暴露公网、无前置 L7 层，收敛与否重开为待裁定）；任务 40 证书部署对象只剩 ALB；任务 48 回调防线确定为两层（应用白名单 + 签名）；任务 52 成本表 WAF 行归零；M3 通过标准去掉 WAF；备站接管后同样无 L7 防护（任务 25 坑 2 转为知情接受风险）；CC 攻击的损失形态改为 HPA 按量扩容 + ALB LCU + 上游 token，故预算 80% 告警与异常突增巡检升为必须项。复评触发条件＝日请求量显著增长 / 出现真实攻击或 CC 事件。依据＝指南 §0.5 F15（2026-10-12 裁定）。</t>
+          <t>① 工期 5 天 -&gt; 9 天（v2.0 -&gt; v2.1：56 项任务压缩进 8 天/16 时段经 600 次重排无可行解）；② 前置期 T-3 的 0 天改为真实前置 T-5；③ 补 PgBouncer/RDS 代理、cluster-autoscaler、备 region HPA 与 1.5× 接管容量；④ 补 staging/perf、运维访问面、Tair 预热、PITR 演练、连接数预算、Grafana、带宽与成本量化、上游配额盘点；⑤ 安全 3 改（ALB 源收敛为 WAF/DCDN 回源段、支付回调源 IP 白名单、SESSION_SECRET 双密钥轮换）；⑥ 修正证书部署时序、依赖倒挂、J48 负荷公式、门禁计数与编号映射、域名/数据盘/RTT 阈值口径；⑦【v2.2】工期 9 天 -&gt; 5 天：把每天 2 个半天时段改为 3 个工作段（新增 19:00–23:00 晚间加班段），15 时段 × 2 人 × 4 人时 = 120 人时产能，56 项任务在 15 段内重排完成、0 超载；⑧【v2.3】备 region 容量口径改为「本期仅承载 PH 备、不含泰国备」：节点数按 Pod requests 反算并留 ≥ 20% 系统组件余量 → 8 节点，节点池 2–12 改 2–8、配额 96 改 64 vCPU；统一「1.5×」基准为 maxReplicas × 1.5；⑨【2026-09-24 决策定案】三项遗留决策：保留 D4/D5 国庆窗口（不顺延）、T-5 = 2026-09-23 基准不动、本期不增加第 3 人。⑩【2026-10-08 按指南 v2.0（2026-10-07 版）实况回改】共回改 146 格：① 机型 g8i → g9i 首选（三机型列表，实开 g9ae）；② 主站 HPA 4–16 → 4–13、备站接管 16×1.5=24 → 13×1.5=19.5 → 20 副本；PDB minAvailable=3 → 70%；③ 新加坡配额实批按量 96 vCPU、节点池上限 12（v2.3 的 64 vCPU / 8 节点保留为容量下限）；④ RDS 规格 16C64G → pg.n4.2c.2m（2C8G，max_connections=800）；⑤ PgBouncer 自建 → RDS 内置托管池（F10 撤销）；⑥ 日志库 → 马尼拉 ClickHouse 企业版单 AZ（F9），不再购买新加坡 CK；⑦ 凭据链路 → 不使用 KMS/RRSA/ExternalSecret（2026-10-05 裁定），改手工 Opaque Secret；⑧ ECS 节点池付费方式定为按量 PostPaid（F13），成本按实况整机单价重算；⑨ 备站 Pod SQL_MAX_OPEN_CONNS=10（CM 100）；⑩ 伸缩组件实名 ack-goatscaler（非 cluster-autoscaler，观测入口 cm/kube-system/autoscaler-meta）；⑪ 任务 53 收敛口径由「30s × 节点数」改为「≤30 s（与节点数、跨 region 无关）」；⑫ 健康检查路径 /api/status 与全局限流冲突（应改 /readyz 并免限流）；⑬ 落地计划 AC 列按实况回填（21 张已完成 / 8 张部分交付 / 27 张未开始）。⑭【2026-10-12 与指南同步】：① G5 证书闭环——实购 Alibaba 品牌 DV 通配符 ali.dv.w（US$207，CertIdentifier=606823-ap-southeast-1，SAN *.likha.hk + likha.hk，链至 DigiCert Global Root G2），原 GlobalSign OV（US$997）已全额退款；⚠ 单张有效期仅 198 天（→ 2027-04-28）且 **AutoReissue=enable**（2026-10-12 经授权 UpdateInstance 开启，GetInstanceDetail 与 ListInstances 双路回读；写前 disable）⇒ 实例级托管续签已开，但不代表 443 自动续上：监听只认 AlbConfig 钉死的 CertificateId（ACK 原文「Listener 不会使用自动发现证书，优先使用 AlbConfig 指定的证书」），且 ALB 是 ServiceManagedResource（直调 OpenAPI 换绑实测 3/3 被拒）⇒ ★ 2026-10-15 路② 已落地两地（Secret/new-api-tls + 锚定 Ingress new-api-tls-anchor），443 同域名出证来源 = Ingress spec.tls 的 Secret（实测压住 AlbConfig 钉死证，钉死证保留未撤）⇒ 新证签发后必须**刷 Secret**（deploy/cert/targets.yaml R5 = 必需路径），只改 AlbConfig 不再足以恢复 443（2027-03-29 前，targets.yaml R1–R5；机制取证与落地验收见指南任务 3 卡 ★ 段）。⚠ 刷 Secret 的执行器尚未实现 ⇒ 现阶段续签仍需人工；② 两地 ALB 443 监听 + 证书 + HTTP→HTTPS 301 已落地并验收（任务 19 V1–V5 全过、任务 25 闭合），requestTimeout 口径 180s → 600s（ALB 硬上限）；③ WAF 仍未接入（账号无实例；版本由「企业版」改为待裁定，2026-10-10 选型建议高级版）；④ GTM 仍挂起（任务 21，2026-09-30 裁定）；⑤ 备站跨区写马尼拉 CK 已实测在位（PUBLIC 端点 + sg_eip 白名单，2026-10-09 复核），原「待裁定」闭合；⑥ 任务 26 观测 4/4 闭环、任务 27 canary V1–V6 全过、任务 53 按更正判据通过；⑦ 镜像前缀按实测 EE 域名更正（B27）。⑮【2026-10-12 WAF 购买决策】：项目负责人裁定本次部署**不购买 WAF 3.0**（暂缓、非取消）——最低档高级版 3,880 元/月 ≈US$556 + 2,000 QPS + 日志服务单独起购，相对当前业务量过高，且实例只能控制台订阅（waf-openapi 无 CreateInstance、CLI 不能报价下单）。连锁更正：任务 20 整体挂起、V1–V4 从上线门禁移出；任务 47「ALB 入向不收敛」失去 WAF 缓解（443 直接暴露公网、无前置 L7 层，收敛与否重开为待裁定）；任务 40 证书部署对象只剩 ALB；任务 48 回调防线确定为两层（应用白名单 + 签名）；任务 52 成本表 WAF 行归零；M3 通过标准去掉 WAF；备站接管后同样无 L7 防护（任务 25 坑 2 转为知情接受风险）；CC 攻击的损失形态改为 HPA 按量扩容 + ALB LCU + 上游 token，故预算 80% 告警与异常突增巡检升为必须项。复评触发条件＝日请求量显著增长 / 出现真实攻击或 CC 事件。依据＝指南 §0.5 F15（2026-10-12 裁定）。</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
-          <t>私钥**不落 KMS**（2026-10-05 裁定不使用 KMS/凭据管家）：证书私钥由运维手工保管；⚠ 2026-10-12 实况：单张有效期仅 198 天（→ 2027-04-28，CA/B 新规）；AutoReissue=enable（2026-10-12 经授权开启并双路回读）⇒ 实例级托管续签已开，但不代表 443 自动续上：监听只认 AlbConfig 钉死的 CertificateId（ACK 原文「Listener 不会使用自动发现证书，优先使用 AlbConfig 指定的证书」），且 ALB 是 ServiceManagedResource（直调 OpenAPI 换绑实测 3/3 被拒）⇒ 新证签发后须改 AlbConfig 再 apply（2027-03-29 前，deploy/cert/targets.yaml R1–R4；免人工的两条改法见指南任务 3 卡 ★ 段）；30 天到期告警已在控制台配置（2026-10-12 负责人自配；⚠ CAS 无提醒类 API，故该项无回读证据、配置页截图待补）</t>
+          <t>私钥**不落 KMS**（2026-10-05 裁定不使用 KMS/凭据管家）：证书私钥由运维手工保管；⚠ 2026-10-12 实况：单张有效期仅 198 天（→ 2027-04-28，CA/B 新规）；AutoReissue=enable（2026-10-12 经授权开启并双路回读）⇒ 实例级托管续签已开，但不代表 443 自动续上：监听只认 AlbConfig 钉死的 CertificateId（ACK 原文「Listener 不会使用自动发现证书，优先使用 AlbConfig 指定的证书」），且 ALB 是 ServiceManagedResource（直调 OpenAPI 换绑实测 3/3 被拒）⇒ ★ 2026-10-15 路② 已落地两地（Secret/new-api-tls + 锚定 Ingress new-api-tls-anchor），443 同域名出证来源 = Ingress spec.tls 的 Secret（实测压住 AlbConfig 钉死证，钉死证保留未撤）⇒ 新证签发后必须**刷 Secret**（deploy/cert/targets.yaml R5 = 必需路径），只改 AlbConfig 不再足以恢复 443（2027-03-29 前，targets.yaml R1–R5；机制取证与落地验收见指南任务 3 卡 ★ 段）。⚠ 刷 Secret 的执行器尚未实现 ⇒ 现阶段续签仍需人工；30 天到期告警已在控制台配置（2026-10-12 负责人自配；⚠ CAS 无提醒类 API，故该项无回读证据、配置页截图待补）</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="K21" s="38" t="inlineStr">
         <is>
-          <t>⚠ 2026-10-12 更正：AutoReissue=enable（2026-10-12 经授权开启，GetInstanceDetail/ListInstances 双路回读）⇒ 实例级托管续签已开，但监听只认 AlbConfig 钉死的 CertificateId（且 ALB 为 ServiceManagedResource，直调 OpenAPI 换绑被拒）⇒ 新证书签发后须改 AlbConfig 再 apply 并回归验证（到期 2027-04-28，动作 2027-03-29 前）</t>
+          <t>⚠ 2026-10-12 更正：AutoReissue=enable（2026-10-12 经授权开启，GetInstanceDetail/ListInstances 双路回读）⇒ 实例级托管续签已开，但监听只认 AlbConfig 钉死的 CertificateId（且 ALB 为 ServiceManagedResource，直调 OpenAPI 换绑被拒）⇒ ★ 2026-10-15 路② 已落地：443 出证来源改为 Ingress spec.tls 的 Secret（同域名压住 AlbConfig 钉死证，已实测）⇒ 新证书签发后须刷两地 TLS Secret（targets.yaml R5）并回归验证（到期 2027-04-28，动作 2027-03-29 前）；只改 AlbConfig 不再足以换绑，刷 Secret 的执行器尚未实现 ⇒ 现阶段仍需人工</t>
         </is>
       </c>
     </row>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="AC6" s="16" t="inlineStr">
         <is>
-          <t>已完成（2026-10-12 实测 4/4 交付，本卡闭合）：① 私钥+全链入 /root/.deploy_secrets/TLS_WILDCARD_{CRT,KEY}（-rw------- root root 6075/1675、leaf 在前、链 3 张、-modulus md5 两侧同为 df343b79775… ⇒ 配对 PASS，执行器 deploy/logs/tls_store_20261012.sh）；② notAfter=2027-04-28 ≥ 今+30 天、SAN 含 *.likha.hk 与 likha.hk、openssl verify OK、CAS CertificateStatus=issued（CertId=606823）；③ 到期告警：控制台由负责人自配（⚠ 无 API 可取证，证据=负责人确认，配置页截图仍欠），另经授权开实例级自动托管续签 UpdateInstance --AutoReissue enable，GetInstanceDetail 与 ListInstances 双路回读均为 enable（写前 disable）；④ 模板落地 deploy/cert/targets.yaml（含现场回读的 ALB/监听 ID）。★ 长期风险如实登记（2026-10-12 二次取证订正）：AutoReissueCount 仍 0、ListTrusteeOrder NotFound；早前据 ListCloudResources --CloudName alb 的 Total=0 判「CAS 无部署联动」是**参数用错的假阴性**（--CloudName 是云厂商，ALB 属 --CloudProduct；正确调用实测到两地监听已在 CAS 登记 Id=37274711/37274712，但那是资源可见性、不是"托管会自动写入"）。真实结论由控制面语义决定：监听只认 AlbConfig 钉死的 CertificateId（ACK 原文「Listener 不会使用自动发现证书，优先使用 AlbConfig 指定的证书」；两地实测各只绑 1 张、无多证书兜底），而 ALB 是 ServiceManagedResource（直调 UpdateListenerAttribute 实测 3/3 被拒）⇒ 换绑的唯一通道是**改 AlbConfig 再 apply**（R1–R4 已按此订正，2027-03-29 前执行）。免人工改法（双证共存 / Secret 自动触发）与两条未证风险见指南任务 3 卡 ★ 段。⚠ 另：本轮调试用 bash -x 把私钥正文留在本机会话记录（无远端副本），负责人裁定按「接受」处置，2027-03 续签窗口自然换新；永久规则=处理私钥的脚本禁 -x。</t>
+          <t>已完成（2026-10-12 实测 4/4 交付，本卡闭合）：① 私钥+全链入 /root/.deploy_secrets/TLS_WILDCARD_{CRT,KEY}（-rw------- root root 6075/1675、leaf 在前、链 3 张、-modulus md5 两侧同为 df343b79775… ⇒ 配对 PASS，执行器 deploy/logs/tls_store_20261012.sh）；② notAfter=2027-04-28 ≥ 今+30 天、SAN 含 *.likha.hk 与 likha.hk、openssl verify OK、CAS CertificateStatus=issued（CertId=606823）；③ 到期告警：控制台由负责人自配（⚠ 无 API 可取证，证据=负责人确认，配置页截图仍欠），另经授权开实例级自动托管续签 UpdateInstance --AutoReissue enable，GetInstanceDetail 与 ListInstances 双路回读均为 enable（写前 disable）；④ 模板落地 deploy/cert/targets.yaml（含现场回读的 ALB/监听 ID）。★ 长期风险如实登记（2026-10-12 二次取证订正）：AutoReissueCount 仍 0、ListTrusteeOrder NotFound；早前据 ListCloudResources --CloudName alb 的 Total=0 判「CAS 无部署联动」是**参数用错的假阴性**（--CloudName 是云厂商，ALB 属 --CloudProduct；正确调用实测到两地监听已在 CAS 登记 Id=37274711/37274712，但那是资源可见性、不是"托管会自动写入"）。真实结论由控制面语义决定：监听只认 AlbConfig 钉死的 CertificateId（ACK 原文「Listener 不会使用自动发现证书，优先使用 AlbConfig 指定的证书」；两地实测各只绑 1 张、无多证书兜底），而 ALB 是 ServiceManagedResource（直调 UpdateListenerAttribute 实测 3/3 被拒）⇒ 当时的换绑通道是**改 AlbConfig 再 apply**（R1–R4 已按此订正）。★ 2026-10-15 路② 落地两地，该"唯一通道"口径**反转**：两地各建 Secret/new-api-tls（生产真证进 etcd）+ 锚定 Ingress new-api-tls-anchor（deploy/manifests/ingress-alb-tls-anchor.yaml，只承载 spec.tls、host 无 DNS 记录），实测同域名出证来源 = Secret ⇒ **续签必须刷 Secret**（targets.yaml 新增 R5 = 必需路径），只改 AlbConfig 不再足以恢复 443。验收（回写前重跑复现）：两地 cert_count=2（Secret 证 IsDefault=false + 钉死证仍 true）、SNI 10/10 serial 与基线逐字一致（换来源不换证书）、业务码不变、sg 原 4 条 RuleId 逐字未动、既有业务 Ingress rv 全未变。⚠ 未兑现：刷 Secret 的执行器尚未实现（G1）⇒ 现阶段续签仍需人工；「Secret 证已过期时是否仍优先」（G2）与「续签后私钥是否不变」（G3）未证。落地通道＝甲（ECS RunCommand 下发；正文可被 ActionTrail 留存 90 天与 DescribeInvocations 回读），属一次性放行，常态化需再裁定。⚠ 另：本轮调试用 bash -x 把私钥正文留在本机会话记录（无远端副本），负责人裁定按「接受」处置，2027-03 续签窗口自然换新；永久规则=处理私钥的脚本禁 -x。</t>
         </is>
       </c>
       <c r="AD6" s="17">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="AC43" s="16" t="inlineStr">
         <is>
-          <t>部分交付（2026-10-12：证书已部署至两地 ALB 443，链校验与 SNI 通过；WAF 未接入、DCDN 未启用 ⇒ 按 F15（不采购）与未开通，本轮不做，判据收窄为仅 ALB；未闭合项改为「新证书须改 AlbConfig 再 apply 才会换绑（AutoReissue=enable 只保证 CAS 签出新证；ALB 为 ServiceManagedResource，直调 OpenAPI 被拒；2027-03-29 前执行 targets.yaml R1–R4）」）</t>
+          <t>部分交付（2026-10-12：证书已部署至两地 ALB 443，链校验与 SNI 通过；WAF 未接入、DCDN 未启用 ⇒ 按 F15（不采购）与未开通，本轮不做，判据收窄为仅 ALB；未闭合项（2026-10-15 更新）「新证书须**刷两地 TLS Secret**（targets.yaml R5）才会换绑 —— 路② 已落地、443 出证来源 = Secret；AutoReissue=enable 只保证 CAS 签出新证，ALB 为 ServiceManagedResource 直调 OpenAPI 被拒，改 AlbConfig（R2）已降为次要动作；2027-03-29 前执行 targets.yaml R1–R5」）</t>
         </is>
       </c>
       <c r="AD43" s="17">
